--- a/ventas_ml_historico.xlsx
+++ b/ventas_ml_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -423,7 +423,7 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -632,28 +632,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000015920405788</v>
+        <v>2000015932875024</v>
       </c>
       <c r="B2" t="n">
-        <v>2000012446018577</v>
+        <v>2000012459011895</v>
       </c>
       <c r="C2" t="n">
-        <v>46825928963</v>
+        <v>46831837021</v>
       </c>
       <c r="D2" t="n">
-        <v>154112621330</v>
+        <v>153516147611</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RODIBERTOROBLESALEJANDRO</t>
+          <t>LOAN2137132</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000015920405788</v>
+        <v>2000015932875024</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-10T07:55:11.000-04:00</t>
+          <t>2026-04-11T01:57:33.000-04:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -680,28 +680,28 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>462</v>
+        <v>134.55</v>
       </c>
       <c r="N2" t="n">
-        <v>66.98999999999999</v>
+        <v>13.46</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>119.2</v>
+        <v>64</v>
       </c>
       <c r="Q2" t="n">
-        <v>59.6</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>59.6</v>
+        <v>32</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>462</v>
+        <v>134.55</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MLM2381238905</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -733,16 +733,16 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>462</v>
+        <v>134.55</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>293.59</v>
+        <v>76.91</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>66.98999999999999</v>
+        <v>13.46</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -759,28 +759,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000015919255616</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2000012444792845</v>
-      </c>
+        <v>2000015932632586</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>46825583586</v>
+        <v>46831736271</v>
       </c>
       <c r="D3" t="n">
-        <v>153344481991</v>
+        <v>153514027567</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MARTHACANDELARIALOPEZCORDOVA</t>
+          <t>ERVINEDUARDO RAMÍREZVZLA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000015919255616</v>
+        <v>2000015932632586</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-10T02:48:35.000-04:00</t>
+          <t>2026-04-11T00:54:31.000-04:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,28 +805,28 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>204.71</v>
+        <v>570.86</v>
       </c>
       <c r="N3" t="n">
-        <v>29.68</v>
+        <v>111.32</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>65.5</v>
       </c>
       <c r="R3" t="n">
-        <v>56</v>
+        <v>63.5</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>204.71</v>
+        <v>570.86</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -840,12 +838,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>BR-KZNU-9NOO</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -860,16 +858,16 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>204.71</v>
+        <v>570.86</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>100.5</v>
+        <v>342.37</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -878,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>29.68</v>
+        <v>111.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -886,26 +884,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000015918864062</v>
+        <v>2000015932009672</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46825132377</v>
+        <v>46831746812</v>
       </c>
       <c r="D4" t="n">
-        <v>154084595658</v>
+        <v>153507878875</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALEJANDRO3654</t>
+          <t>PLER973318</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000015918864062</v>
+        <v>2000015932009672</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-10T00:54:13.000-04:00</t>
+          <t>2026-04-10T23:10:48.000-04:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,28 +930,28 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>198.75</v>
+        <v>429</v>
       </c>
       <c r="N4" t="n">
-        <v>28.82</v>
+        <v>62.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>47</v>
+        <v>26.40000000000001</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>198.75</v>
+        <v>429</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -965,12 +963,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>76825709097220</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM4762499328</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -985,16 +983,16 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>198.75</v>
+        <v>429</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>117.94</v>
+        <v>260.36</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1003,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>28.82</v>
+        <v>62.2</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1011,28 +1009,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2000015918735504</v>
+        <v>2000015931967972</v>
       </c>
       <c r="B5" t="n">
-        <v>2000012444242337</v>
+        <v>2000012458078981</v>
       </c>
       <c r="C5" t="n">
-        <v>46825081431</v>
+        <v>46831734526</v>
       </c>
       <c r="D5" t="n">
-        <v>154083285822</v>
+        <v>154254282856</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JLPACHECOS</t>
+          <t>HECTORPETITHECTORPETIT</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000015918735504</v>
+        <v>2000015931967972</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-10T00:31:16.000-04:00</t>
+          <t>2026-04-10T23:07:11.000-04:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,28 +1057,28 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>427.5</v>
+        <v>827.64</v>
       </c>
       <c r="N5" t="n">
-        <v>64.12</v>
+        <v>120.01</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>135.2</v>
+        <v>169</v>
       </c>
       <c r="Q5" t="n">
-        <v>67.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="R5" t="n">
-        <v>67.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>427.5</v>
+        <v>827.64</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1092,12 +1090,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>A18/A38</t>
+          <t>76532580917858</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MLM3442935972</t>
+          <t>MLM4545490694</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1112,16 +1110,16 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>427.5</v>
+        <v>827.64</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>257.09</v>
+        <v>548.21</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1130,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>64.12</v>
+        <v>120.01</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1138,28 +1136,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000015918564930</v>
+        <v>2000015931930082</v>
       </c>
       <c r="B6" t="n">
-        <v>2000012444063601</v>
+        <v>2000012457998119</v>
       </c>
       <c r="C6" t="n">
-        <v>46825008245</v>
+        <v>46831420445</v>
       </c>
       <c r="D6" t="n">
-        <v>154081820206</v>
+        <v>154253338188</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OSCARCOLOTL</t>
+          <t>CARLOSALFONZ</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000015918564930</v>
+        <v>2000015931930082</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-10T00:03:34.000-04:00</t>
+          <t>2026-04-10T22:55:27.000-04:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1186,28 +1184,28 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>164.45</v>
+        <v>3158.4</v>
       </c>
       <c r="N6" t="n">
-        <v>16.44</v>
+        <v>457.97</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>164.45</v>
+        <v>3158.4</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1219,17 +1217,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>76867668365155</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4762499740</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1239,16 +1237,16 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>164.45</v>
+        <v>3158.4</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>101.13</v>
+        <v>2319.54</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1257,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.44</v>
+        <v>457.97</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1265,28 +1263,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2000015915026216</v>
+        <v>2000015931187904</v>
       </c>
       <c r="B7" t="n">
-        <v>2000012440383505</v>
+        <v>2000012457258861</v>
       </c>
       <c r="C7" t="n">
-        <v>46823711622</v>
+        <v>46831390290</v>
       </c>
       <c r="D7" t="n">
-        <v>154052836286</v>
+        <v>154246400496</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAKE9550997</t>
+          <t>PEÑAHERNAN20221106222959</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000015915026216</v>
+        <v>2000015931187904</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-09T19:18:46.000-04:00</t>
+          <t>2026-04-10T21:46:13.000-04:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1313,28 +1311,28 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>234</v>
+        <v>925.3</v>
       </c>
       <c r="N7" t="n">
-        <v>23.4</v>
+        <v>92.53</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>275</v>
+        <v>190</v>
       </c>
       <c r="Q7" t="n">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="R7" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>234</v>
+        <v>925.3</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1346,17 +1344,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>75045745678283</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MLM3813363284</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1366,16 +1364,16 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>234</v>
+        <v>925.3</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>189.42</v>
+        <v>654.02</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1384,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.4</v>
+        <v>92.53</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1392,36 +1390,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2000015914539400</v>
+        <v>2000015930234104</v>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>46823497086</v>
+        <v>46830673091</v>
       </c>
       <c r="D8" t="n">
-        <v>153301992033</v>
+        <v>153488743041</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VNUSROJIBLANK12</t>
+          <t>BOAL6432084</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000015914539400</v>
+        <v>2000015930234104</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-09T18:47:34.000-04:00</t>
+          <t>2026-04-10T20:22:43.000-04:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1438,28 +1436,28 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>713</v>
+        <v>285</v>
       </c>
       <c r="N8" t="n">
-        <v>103.38</v>
+        <v>55.58</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="Q8" t="n">
-        <v>84.5</v>
+        <v>39</v>
       </c>
       <c r="R8" t="n">
-        <v>41.5</v>
+        <v>59</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>713</v>
+        <v>285</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1471,12 +1469,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>73239400752399</t>
+          <t>77343215226889</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MLM3488485454</t>
+          <t>MLM5098643766</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,16 +1489,16 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>713</v>
+        <v>285</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>460.58</v>
+        <v>164.62</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1509,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>103.38</v>
+        <v>55.58</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1517,28 +1515,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2000015914254952</v>
+        <v>2000015929551932</v>
       </c>
       <c r="B9" t="n">
-        <v>2000012439581533</v>
+        <v>2000012455537231</v>
       </c>
       <c r="C9" t="n">
-        <v>46823083335</v>
+        <v>46830373077</v>
       </c>
       <c r="D9" t="n">
-        <v>153298477411</v>
+        <v>153480488965</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GA20240622001650</t>
+          <t>SOPORIESLAVERGAZONA817</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2000015914254952</v>
+        <v>2000015929551932</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-09T18:26:50.000-04:00</t>
+          <t>2026-04-10T19:30:38.000-04:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1562,31 +1560,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>322</v>
+        <v>795.24</v>
       </c>
       <c r="N9" t="n">
-        <v>31.4</v>
+        <v>115.31</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>160</v>
+        <v>445</v>
       </c>
       <c r="Q9" t="n">
-        <v>80</v>
+        <v>222.5</v>
       </c>
       <c r="R9" t="n">
-        <v>80</v>
+        <v>222.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>322</v>
+        <v>795.24</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1598,17 +1596,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>72141399181305</t>
+          <t>76825905347021</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MLM2289340133</t>
+          <t>MLM4762473244</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1618,16 +1616,16 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>161</v>
+        <v>795.24</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>150.05</v>
+        <v>385.45</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1636,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>62.8</v>
+        <v>115.31</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1644,28 +1642,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000015913353944</v>
+        <v>2000015929481304</v>
       </c>
       <c r="B10" t="n">
-        <v>2000012438644843</v>
+        <v>2000012455454135</v>
       </c>
       <c r="C10" t="n">
-        <v>46822944206</v>
+        <v>46830337829</v>
       </c>
       <c r="D10" t="n">
-        <v>153287496709</v>
+        <v>154225963480</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ESCI899332</t>
+          <t>VALERIAMARIASADAGARZA</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000015913353944</v>
+        <v>2000015929481304</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-09T17:23:20.000-04:00</t>
+          <t>2026-04-10T19:24:38.000-04:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1692,28 +1690,28 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="N10" t="n">
-        <v>16.44</v>
+        <v>42.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>64</v>
+        <v>104.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="R10" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1725,17 +1723,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1745,16 +1743,16 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>101.13</v>
+        <v>120.85</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1763,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.44</v>
+        <v>42.75</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1771,28 +1769,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2000015911947458</v>
+        <v>2000015927409710</v>
       </c>
       <c r="B11" t="n">
-        <v>2000012437174517</v>
+        <v>2000012453315257</v>
       </c>
       <c r="C11" t="n">
-        <v>46822254216</v>
+        <v>46829644948</v>
       </c>
       <c r="D11" t="n">
-        <v>154016435366</v>
+        <v>154195281014</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>BIOTECVO</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000015911947458</v>
+        <v>2000015927409710</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T16:40:07.000-04:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1816,31 +1814,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>294.5</v>
+        <v>475</v>
       </c>
       <c r="N11" t="n">
-        <v>42.7</v>
+        <v>42.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>152</v>
+        <v>209.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>76</v>
+        <v>104.8</v>
       </c>
       <c r="R11" t="n">
-        <v>76</v>
+        <v>104.8</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>294.5</v>
+        <v>475</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1852,17 +1850,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>AUDMORNEGM-921pack</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MLM3356978052</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1872,16 +1870,16 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>294.5</v>
+        <v>237.5</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>149.14</v>
+        <v>241.7</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1890,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>42.7</v>
+        <v>85.5</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1898,28 +1896,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2000015911947456</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2000012437174517</v>
-      </c>
+        <v>2000015926465502</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>46822254216</v>
+        <v>46828912925</v>
       </c>
       <c r="D12" t="n">
-        <v>154016462860</v>
+        <v>154183216410</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>JACOBOMIGUEL20230130120239</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000015911947456</v>
+        <v>2000015926465502</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T15:28:10.000-04:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1946,28 +1942,28 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>294.5</v>
+        <v>109.8</v>
       </c>
       <c r="N12" t="n">
-        <v>42.7</v>
+        <v>13.18</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="Q12" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="R12" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>294.5</v>
+        <v>109.8</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1979,17 +1975,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>76720994758426</t>
+          <t>SOPMORDEFMH-70B</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MLM5115426106</t>
+          <t>MLM3357068774</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1999,16 +1995,16 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>294.5</v>
+        <v>109.8</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>225.14</v>
+        <v>46.68</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2017,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>42.7</v>
+        <v>13.18</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2025,28 +2021,26 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2000015911035950</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2000012436224727</v>
-      </c>
+        <v>2000015925898954</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>46821806098</v>
+        <v>46828618943</v>
       </c>
       <c r="D13" t="n">
-        <v>154008453720</v>
+        <v>154176812930</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HLALTAMIRANO</t>
+          <t>MEDINAVIANEY20220808095244</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2000015911035950</v>
+        <v>2000015925898954</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-09T14:44:05.000-04:00</t>
+          <t>2026-04-10T14:44:48.000-04:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2073,28 +2067,28 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>560.5</v>
+        <v>122</v>
       </c>
       <c r="N13" t="n">
-        <v>109.3</v>
+        <v>12.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.5</v>
+        <v>121</v>
       </c>
       <c r="R13" t="n">
-        <v>65.5</v>
+        <v>32</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>560.5</v>
+        <v>122</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2106,17 +2100,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>76126320655919</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM4676748386</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2126,16 +2120,16 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>560.5</v>
+        <v>122</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>334.96</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2144,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>109.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2152,26 +2146,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2000015910487320</v>
-      </c>
-      <c r="B14" t="inlineStr"/>
+        <v>2000015925292404</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2000012451099821</v>
+      </c>
       <c r="C14" t="n">
-        <v>46821271897</v>
+        <v>46828589732</v>
       </c>
       <c r="D14" t="n">
-        <v>153258785401</v>
+        <v>154170422818</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ENLACESS</t>
+          <t>VECE1241164</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000015910487320</v>
+        <v>2000015925292404</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-09T14:10:04.000-04:00</t>
+          <t>2026-04-10T14:00:29.000-04:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2198,28 +2194,28 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>134.55</v>
+        <v>925.3</v>
       </c>
       <c r="N14" t="n">
-        <v>13.46</v>
+        <v>92.53</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>99</v>
+        <v>190</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R14" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>134.55</v>
+        <v>925.3</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2231,12 +2227,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2251,16 +2247,16 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>134.55</v>
+        <v>925.3</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>76.91</v>
+        <v>654.02</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2269,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>13.46</v>
+        <v>92.53</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2277,28 +2273,28 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2000015909133456</v>
+        <v>2000015924881136</v>
       </c>
       <c r="B15" t="n">
-        <v>2000012434212221</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C15" t="n">
-        <v>46820912508</v>
+        <v>46828113793</v>
       </c>
       <c r="D15" t="n">
-        <v>153993729394</v>
+        <v>154166302560</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ULY5205</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000015909133456</v>
+        <v>2000015924881136</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-09T12:45:26.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2325,28 +2321,28 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="N15" t="n">
-        <v>31.18</v>
+        <v>22.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>64</v>
+        <v>285.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>189.52</v>
       </c>
       <c r="R15" t="n">
-        <v>32</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2358,12 +2354,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>BOCMORROK405</t>
+          <t>BOCMORROSMOR-410</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2378,16 +2374,16 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>108.72</v>
+        <v>184.57</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2396,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>31.18</v>
+        <v>22.8</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2404,28 +2400,28 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2000015901141806</v>
+        <v>2000015924881134</v>
       </c>
       <c r="B16" t="n">
-        <v>2000012425847369</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C16" t="n">
-        <v>46816833391</v>
+        <v>46828113793</v>
       </c>
       <c r="D16" t="n">
-        <v>153164140863</v>
+        <v>153420099615</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PC20241019154452</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000015901141806</v>
+        <v>2000015924881134</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-08T21:27:21.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2452,28 +2448,28 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>167.9</v>
+        <v>228</v>
       </c>
       <c r="N16" t="n">
-        <v>25.18</v>
+        <v>22.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>166</v>
+        <v>285.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>134</v>
+        <v>189.52</v>
       </c>
       <c r="R16" t="n">
-        <v>32</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>167.9</v>
+        <v>228</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2485,12 +2481,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>CARMORDEFP-203</t>
+          <t>BOCMORAZUMOR-410</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MLM1912930539</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2505,16 +2501,16 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>167.9</v>
+        <v>228</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>18.7</v>
+        <v>184.57</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2523,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2531,28 +2527,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2000015900479830</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2000012425150469</v>
-      </c>
+        <v>2000015923571686</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>46816813562</v>
+        <v>46827760364</v>
       </c>
       <c r="D17" t="n">
-        <v>153903764628</v>
+        <v>153405868355</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GOJE20240421120542</t>
+          <t>VAZQUEZSARA20230812202049</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2000015900479830</v>
+        <v>2000015923571686</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-08T20:46:39.000-04:00</t>
+          <t>2026-04-10T11:59:16.000-04:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2579,28 +2573,28 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>164.45</v>
+        <v>185</v>
       </c>
       <c r="N17" t="n">
-        <v>16.44</v>
+        <v>27.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R17" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>164.45</v>
+        <v>185</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2612,12 +2606,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>MULMORNEGmc-5848c</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM3357041104</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2632,16 +2626,16 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>164.45</v>
+        <v>185</v>
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>101.13</v>
+        <v>102.5</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2650,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.44</v>
+        <v>27.75</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2658,28 +2652,28 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2000015898605836</v>
+        <v>2000015922863610</v>
       </c>
       <c r="B18" t="n">
-        <v>2000012423204427</v>
+        <v>2000012448562543</v>
       </c>
       <c r="C18" t="n">
-        <v>46815701425</v>
+        <v>46827137585</v>
       </c>
       <c r="D18" t="n">
-        <v>153887348360</v>
+        <v>153396288659</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JG20241208202301</t>
+          <t>JORFERK</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000015898605836</v>
+        <v>2000015922863610</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-08T18:56:03.000-04:00</t>
+          <t>2026-04-10T11:07:52.000-04:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2706,28 +2700,28 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>164.45</v>
+        <v>713</v>
       </c>
       <c r="N18" t="n">
-        <v>16.44</v>
+        <v>103.38</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="R18" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>164.45</v>
+        <v>713</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2739,17 +2733,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>73239381698389</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM3488449480</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2759,16 +2753,16 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>164.45</v>
+        <v>713</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>101.13</v>
+        <v>460.58</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2777,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>16.44</v>
+        <v>103.38</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2785,28 +2779,28 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000015897678942</v>
+        <v>2000015921193538</v>
       </c>
       <c r="B19" t="n">
-        <v>2000012422238933</v>
+        <v>2000012426900403</v>
       </c>
       <c r="C19" t="n">
-        <v>46815285151</v>
+        <v>46826592416</v>
       </c>
       <c r="D19" t="n">
-        <v>153133108857</v>
+        <v>153376320777</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PIAD3222701</t>
+          <t>ALONDRAVIZUET</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2000015897678942</v>
+        <v>2000015921193538</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-08T17:58:14.000-04:00</t>
+          <t>2026-04-10T09:05:19.000-04:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2833,28 +2827,28 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>840</v>
+        <v>954</v>
       </c>
       <c r="N19" t="n">
-        <v>121.8</v>
+        <v>138.33</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="Q19" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="R19" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>840</v>
+        <v>954</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2866,12 +2860,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>72368155667130</t>
+          <t>76825869750536</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MLM2090316531</t>
+          <t>MLM4762485780</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2886,27 +2880,2307 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>840</v>
+        <v>954</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
+        <v>634.3200000000001</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>138.33</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2000015920405788</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2000012446018577</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46825928963</v>
+      </c>
+      <c r="D20" t="n">
+        <v>154112621330</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RODIBERTOROBLESALEJANDRO</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2000015920405788</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-04-10T07:55:11.000-04:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>462</v>
+      </c>
+      <c r="N20" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>462</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>75287834715773</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>MLM2381238905</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>462</v>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>293.59</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2000015919255616</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2000012444792845</v>
+      </c>
+      <c r="C21" t="n">
+        <v>46825583586</v>
+      </c>
+      <c r="D21" t="n">
+        <v>153344481991</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MARTHACANDELARIALOPEZCORDOVA</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2000015919255616</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-04-10T02:48:35.000-04:00</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>204.71</v>
+      </c>
+      <c r="N21" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>204.71</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>BR-KZNU-9NOO</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>MLM1904582897</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>204.71</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2000015918864062</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>46825132377</v>
+      </c>
+      <c r="D22" t="n">
+        <v>154084595658</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ALEJANDRO3654</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2000015918864062</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:54:13.000-04:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>34</v>
+      </c>
+      <c r="R22" t="n">
+        <v>47</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NN-TJ55-EIRE</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>MLM1904582897</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="n">
+        <v>117.94</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2000015918735504</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2000012444242337</v>
+      </c>
+      <c r="C23" t="n">
+        <v>46825081431</v>
+      </c>
+      <c r="D23" t="n">
+        <v>154083285822</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>JLPACHECOS</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2000015918735504</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:31:16.000-04:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>A18/A38</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>MLM3442935972</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2000012444063601</v>
+      </c>
+      <c r="C24" t="n">
+        <v>46825008245</v>
+      </c>
+      <c r="D24" t="n">
+        <v>154081820206</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OSCARCOLOTL</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:03:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N24" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>32</v>
+      </c>
+      <c r="R24" t="n">
+        <v>32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2000012440383505</v>
+      </c>
+      <c r="C25" t="n">
+        <v>46823711622</v>
+      </c>
+      <c r="D25" t="n">
+        <v>154052836286</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAKE9550997</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-04-09T19:18:46.000-04:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>234</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>221</v>
+      </c>
+      <c r="R25" t="n">
+        <v>54</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>234</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>75045745678283</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>MLM3813363284</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>234</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>189.42</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>46823497086</v>
+      </c>
+      <c r="D26" t="n">
+        <v>153301992033</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>VNUSROJIBLANK12</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:47:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>713</v>
+      </c>
+      <c r="N26" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>713</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>73239400752399</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>MLM3488485454</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>713</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>460.58</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2000012439581533</v>
+      </c>
+      <c r="C27" t="n">
+        <v>46823083335</v>
+      </c>
+      <c r="D27" t="n">
+        <v>153298477411</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GA20240622001650</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:26:50.000-04:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>322</v>
+      </c>
+      <c r="N27" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>80</v>
+      </c>
+      <c r="R27" t="n">
+        <v>80</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>322</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>72141399181305</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>MLM2289340133</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>161</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>150.05</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2000012438644843</v>
+      </c>
+      <c r="C28" t="n">
+        <v>46822944206</v>
+      </c>
+      <c r="D28" t="n">
+        <v>153287496709</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ESCI899332</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-04-09T17:23:20.000-04:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N28" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>32</v>
+      </c>
+      <c r="R28" t="n">
+        <v>32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C29" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D29" t="n">
+        <v>154016462860</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>76</v>
+      </c>
+      <c r="R29" t="n">
+        <v>76</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>76720994758426</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>MLM5115426106</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C30" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D30" t="n">
+        <v>154016435366</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>76</v>
+      </c>
+      <c r="R30" t="n">
+        <v>76</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>AUDMORNEGM-921pack</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>MLM3356978052</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>149.14</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2000012436224727</v>
+      </c>
+      <c r="C31" t="n">
+        <v>46821806098</v>
+      </c>
+      <c r="D31" t="n">
+        <v>154008453720</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>HLALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:44:05.000-04:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>74725206008902</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>MLM3712202158</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>46821271897</v>
+      </c>
+      <c r="D32" t="n">
+        <v>153258785401</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ENLACESS</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:10:04.000-04:00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>32</v>
+      </c>
+      <c r="R32" t="n">
+        <v>67</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>75961290041531</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>MLM4318429096</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2000012434212221</v>
+      </c>
+      <c r="C33" t="n">
+        <v>46820912508</v>
+      </c>
+      <c r="D33" t="n">
+        <v>153993729394</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ULY5205</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-04-09T12:45:26.000-04:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>189</v>
+      </c>
+      <c r="N33" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>32</v>
+      </c>
+      <c r="R33" t="n">
+        <v>32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>189</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>BOCMORROK405</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>MLM2972698110</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>189</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2000012425847369</v>
+      </c>
+      <c r="C34" t="n">
+        <v>46816833391</v>
+      </c>
+      <c r="D34" t="n">
+        <v>153164140863</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PC20241019154452</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-04-08T21:27:21.000-04:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="N34" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>134</v>
+      </c>
+      <c r="R34" t="n">
+        <v>32</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>CARMORDEFP-203</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>MLM1912930539</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2000012425150469</v>
+      </c>
+      <c r="C35" t="n">
+        <v>46816813562</v>
+      </c>
+      <c r="D35" t="n">
+        <v>153903764628</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GOJE20240421120542</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-04-08T20:46:39.000-04:00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N35" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>32</v>
+      </c>
+      <c r="R35" t="n">
+        <v>32</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2000012423204427</v>
+      </c>
+      <c r="C36" t="n">
+        <v>46815701425</v>
+      </c>
+      <c r="D36" t="n">
+        <v>153887348360</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JG20241208202301</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-04-08T18:56:03.000-04:00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N36" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>32</v>
+      </c>
+      <c r="R36" t="n">
+        <v>32</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2000012422238933</v>
+      </c>
+      <c r="C37" t="n">
+        <v>46815285151</v>
+      </c>
+      <c r="D37" t="n">
+        <v>153133108857</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PIAD3222701</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-04-08T17:58:14.000-04:00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>840</v>
+      </c>
+      <c r="N37" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>840</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>72368155667130</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>MLM2090316531</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>840</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="n">
         <v>557.67</v>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>121.8</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AI37" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ventas_ml_historico.xlsx
+++ b/ventas_ml_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -632,28 +632,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000015932875024</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2000012459011895</v>
-      </c>
+        <v>2000015945008650</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>46831837021</v>
+        <v>46837630090</v>
       </c>
       <c r="D2" t="n">
-        <v>153516147611</v>
+        <v>154412117972</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LOAN2137132</t>
+          <t>TONO5981002</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000015932875024</v>
+        <v>2000015945008650</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-11T01:57:33.000-04:00</t>
+          <t>2026-04-12T05:17:26.000-04:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -680,28 +678,28 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>134.55</v>
+        <v>886.34</v>
       </c>
       <c r="N2" t="n">
-        <v>13.46</v>
+        <v>88.63</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="Q2" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R2" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>134.55</v>
+        <v>886.34</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -713,12 +711,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -733,16 +731,16 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>134.55</v>
+        <v>886.34</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>76.91</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -751,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>13.46</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -759,26 +757,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000015932632586</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
+        <v>2000015944827404</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2000012471530373</v>
+      </c>
       <c r="C3" t="n">
-        <v>46831736271</v>
+        <v>46837277205</v>
       </c>
       <c r="D3" t="n">
-        <v>153514027567</v>
+        <v>153662197883</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ERVINEDUARDO RAMÍREZVZLA</t>
+          <t>JESSICAMIRTALADELENROA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000015932632586</v>
+        <v>2000015944827404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-11T00:54:31.000-04:00</t>
+          <t>2026-04-12T02:47:16.000-04:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -805,28 +805,28 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>570.86</v>
+        <v>204</v>
       </c>
       <c r="N3" t="n">
-        <v>111.32</v>
+        <v>33.66</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>129</v>
+        <v>76.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>65.5</v>
+        <v>41.27</v>
       </c>
       <c r="R3" t="n">
-        <v>63.5</v>
+        <v>34.99999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>570.86</v>
+        <v>204</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -838,12 +838,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>BOCMORAZU405</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -858,16 +858,16 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>570.86</v>
+        <v>204</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>342.37</v>
+        <v>110.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>111.32</v>
+        <v>33.66</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -884,26 +884,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000015932009672</v>
+        <v>2000015944791160</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46831746812</v>
+        <v>46837546532</v>
       </c>
       <c r="D4" t="n">
-        <v>153507878875</v>
+        <v>153662234221</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PLER973318</t>
+          <t>RA20241216152952</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000015932009672</v>
+        <v>2000015944791160</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-10T23:10:48.000-04:00</t>
+          <t>2026-04-12T02:43:18.000-04:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,28 +930,28 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>429</v>
+        <v>202.65</v>
       </c>
       <c r="N4" t="n">
-        <v>62.2</v>
+        <v>33.44</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="Q4" t="n">
-        <v>67.59999999999999</v>
+        <v>125</v>
       </c>
       <c r="R4" t="n">
-        <v>26.40000000000001</v>
+        <v>38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>429</v>
+        <v>202.65</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>76825709097220</t>
+          <t>PX-SJL9-BCN0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MLM4762499328</t>
+          <t>MLM2082055833</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -983,16 +983,16 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
+          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>429</v>
+        <v>202.65</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>260.36</v>
+        <v>112.86</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>62.2</v>
+        <v>33.44</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1009,28 +1009,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2000015931967972</v>
+        <v>2000015944554586</v>
       </c>
       <c r="B5" t="n">
-        <v>2000012458078981</v>
+        <v>2000012471236369</v>
       </c>
       <c r="C5" t="n">
-        <v>46831734526</v>
+        <v>46837165917</v>
       </c>
       <c r="D5" t="n">
-        <v>154254282856</v>
+        <v>154406778626</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HECTORPETITHECTORPETIT</t>
+          <t>JUANANGELDUEÑASRINCON</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000015931967972</v>
+        <v>2000015944554586</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-10T23:07:11.000-04:00</t>
+          <t>2026-04-12T01:07:15.000-04:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,28 +1057,28 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>827.64</v>
+        <v>134.55</v>
       </c>
       <c r="N5" t="n">
-        <v>120.01</v>
+        <v>13.46</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="Q5" t="n">
-        <v>84.5</v>
+        <v>32</v>
       </c>
       <c r="R5" t="n">
-        <v>84.5</v>
+        <v>32</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>827.64</v>
+        <v>134.55</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1090,17 +1090,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>76532580917858</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MLM4545490694</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1110,16 +1110,16 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>827.64</v>
+        <v>134.55</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>548.21</v>
+        <v>76.91</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>120.01</v>
+        <v>13.46</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1136,38 +1136,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000015931930082</v>
+        <v>2000015944520040</v>
       </c>
       <c r="B6" t="n">
-        <v>2000012457998119</v>
+        <v>2000012471190691</v>
       </c>
       <c r="C6" t="n">
-        <v>46831420445</v>
+        <v>46837150907</v>
       </c>
       <c r="D6" t="n">
-        <v>154253338188</v>
+        <v>153658671197</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CARLOSALFONZ</t>
+          <t>GUJU6869975</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000015931930082</v>
+        <v>2000015944520040</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-10T22:55:27.000-04:00</t>
+          <t>2026-04-12T00:57:45.000-04:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>3158.4</v>
+        <v>886.34</v>
       </c>
       <c r="N6" t="n">
-        <v>457.97</v>
+        <v>88.63</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3158.4</v>
+        <v>886.34</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1217,17 +1217,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>76867668365155</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MLM4762499740</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1237,16 +1237,16 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>3158.4</v>
+        <v>886.34</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>2319.54</v>
+        <v>622.48</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>457.97</v>
+        <v>88.63</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1263,28 +1263,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2000015931187904</v>
+        <v>2000015944439726</v>
       </c>
       <c r="B7" t="n">
-        <v>2000012457258861</v>
+        <v>2000012471123715</v>
       </c>
       <c r="C7" t="n">
-        <v>46831390290</v>
+        <v>46837123631</v>
       </c>
       <c r="D7" t="n">
-        <v>154246400496</v>
+        <v>154405486928</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PEÑAHERNAN20221106222959</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000015931187904</v>
+        <v>2000015944439726</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-10T21:46:13.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,28 +1311,28 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="N7" t="n">
-        <v>92.53</v>
+        <v>31.04</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="R7" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1344,17 +1344,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>Blanco K073</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1364,16 +1364,16 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>654.02</v>
+        <v>157.18</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>92.53</v>
+        <v>31.04</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1390,36 +1390,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2000015930234104</v>
-      </c>
-      <c r="B8" t="inlineStr"/>
+        <v>2000015944444922</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2000012471123715</v>
+      </c>
       <c r="C8" t="n">
-        <v>46830673091</v>
+        <v>46837123631</v>
       </c>
       <c r="D8" t="n">
-        <v>153488743041</v>
+        <v>154405351746</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BOAL6432084</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000015930234104</v>
+        <v>2000015944444922</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-10T20:22:43.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1436,28 +1438,28 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>285</v>
+        <v>206.95</v>
       </c>
       <c r="N8" t="n">
-        <v>55.58</v>
+        <v>31.04</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="R8" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>285</v>
+        <v>206.95</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1469,12 +1471,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>77343215226889</t>
+          <t>Azul K073</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MLM5098643766</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1489,16 +1491,16 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>285</v>
+        <v>206.95</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>164.62</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1507,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>55.58</v>
+        <v>31.04</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1515,28 +1517,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2000015929551932</v>
+        <v>2000015944248160</v>
       </c>
       <c r="B9" t="n">
-        <v>2000012455537231</v>
+        <v>2000012470820489</v>
       </c>
       <c r="C9" t="n">
-        <v>46830373077</v>
+        <v>46837041551</v>
       </c>
       <c r="D9" t="n">
-        <v>153480488965</v>
+        <v>154403287242</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SOPORIESLAVERGAZONA817</t>
+          <t>JUANCARLOSCARMONAALFARO</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2000015929551932</v>
+        <v>2000015944248160</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-10T19:30:38.000-04:00</t>
+          <t>2026-04-11T23:59:26.000-04:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1563,28 +1565,28 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>795.24</v>
+        <v>204.71</v>
       </c>
       <c r="N9" t="n">
-        <v>115.31</v>
+        <v>29.68</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>445</v>
+        <v>105.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>222.5</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>222.5</v>
+        <v>38</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>795.24</v>
+        <v>204.71</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1596,12 +1598,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>76825905347021</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MLM4762473244</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1616,16 +1618,16 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>795.24</v>
+        <v>204.71</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>385.45</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1634,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>115.31</v>
+        <v>29.68</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1642,28 +1644,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000015929481304</v>
+        <v>2000015942032840</v>
       </c>
       <c r="B10" t="n">
-        <v>2000012455454135</v>
+        <v>2000012468587881</v>
       </c>
       <c r="C10" t="n">
-        <v>46830337829</v>
+        <v>46836369178</v>
       </c>
       <c r="D10" t="n">
-        <v>154225963480</v>
+        <v>154378603064</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VALERIAMARIASADAGARZA</t>
+          <t>JOELLDJ</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000015929481304</v>
+        <v>2000015942032840</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-10T19:24:38.000-04:00</t>
+          <t>2026-04-11T19:53:08.000-04:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1690,28 +1692,28 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>237.5</v>
+        <v>700</v>
       </c>
       <c r="N10" t="n">
-        <v>42.75</v>
+        <v>101.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>104.8</v>
+        <v>169</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.4</v>
+        <v>84.5</v>
       </c>
       <c r="R10" t="n">
-        <v>52.4</v>
+        <v>84.5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>237.5</v>
+        <v>700</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1723,17 +1725,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM4388568286</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1743,16 +1745,16 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>237.5</v>
+        <v>700</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>120.85</v>
+        <v>450.63</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1761,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>42.75</v>
+        <v>101.5</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1769,28 +1771,26 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2000015927409710</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2000012453315257</v>
-      </c>
+        <v>2000015941753476</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>46829644948</v>
+        <v>46836259542</v>
       </c>
       <c r="D11" t="n">
-        <v>154195281014</v>
+        <v>153627775865</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BIOTECVO</t>
+          <t>NOYOLAIVAN20231112183250</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000015927409710</v>
+        <v>2000015941753476</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-10T16:40:07.000-04:00</t>
+          <t>2026-04-11T19:31:35.000-04:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1814,31 +1814,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>475</v>
+        <v>189</v>
       </c>
       <c r="N11" t="n">
-        <v>42.75</v>
+        <v>31.18</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>209.6</v>
+        <v>109</v>
       </c>
       <c r="Q11" t="n">
-        <v>104.8</v>
+        <v>32</v>
       </c>
       <c r="R11" t="n">
-        <v>104.8</v>
+        <v>77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>475</v>
+        <v>189</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1870,16 +1870,16 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>241.7</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>85.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1896,26 +1896,28 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2000015926465502</v>
-      </c>
-      <c r="B12" t="inlineStr"/>
+        <v>2000015941686260</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2000012468221695</v>
+      </c>
       <c r="C12" t="n">
-        <v>46828912925</v>
+        <v>46836215454</v>
       </c>
       <c r="D12" t="n">
-        <v>154183216410</v>
+        <v>154373847452</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JACOBOMIGUEL20230130120239</t>
+          <t>CAAN8167043</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000015926465502</v>
+        <v>2000015941686260</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-10T15:28:10.000-04:00</t>
+          <t>2026-04-11T19:23:01.000-04:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1942,28 +1944,28 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>109.8</v>
+        <v>134.55</v>
       </c>
       <c r="N12" t="n">
-        <v>13.18</v>
+        <v>13.46</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>109.8</v>
+        <v>134.55</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1975,12 +1977,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOPMORDEFMH-70B</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MLM3357068774</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1995,16 +1997,16 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>109.8</v>
+        <v>134.55</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>46.68</v>
+        <v>76.91</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2013,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>13.18</v>
+        <v>13.46</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2021,26 +2023,26 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2000015925898954</v>
+        <v>2000015941054478</v>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>46828618943</v>
+        <v>46835940590</v>
       </c>
       <c r="D13" t="n">
-        <v>154176812930</v>
+        <v>154365172508</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MEDINAVIANEY20220808095244</t>
+          <t>L20260220145454</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2000015925898954</v>
+        <v>2000015941054478</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-10T14:44:48.000-04:00</t>
+          <t>2026-04-11T18:29:38.000-04:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2067,28 +2069,28 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>122</v>
+        <v>886.34</v>
       </c>
       <c r="N13" t="n">
-        <v>12.2</v>
+        <v>88.63</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="Q13" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="R13" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>122</v>
+        <v>886.34</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2100,12 +2102,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>76126320655919</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>MLM4676748386</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2120,16 +2122,16 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>122</v>
+        <v>886.34</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>622.48</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2138,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>88.63</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2146,28 +2148,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2000015925292404</v>
+        <v>2000015940863248</v>
       </c>
       <c r="B14" t="n">
-        <v>2000012451099821</v>
+        <v>2000012467360959</v>
       </c>
       <c r="C14" t="n">
-        <v>46828589732</v>
+        <v>46835581697</v>
       </c>
       <c r="D14" t="n">
-        <v>154170422818</v>
+        <v>154362231108</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VECE1241164</t>
+          <t>JOSMANUELHERNNDEZMRQUEZ</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000015925292404</v>
+        <v>2000015940863248</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-10T14:00:29.000-04:00</t>
+          <t>2026-04-11T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2191,31 +2193,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>925.3</v>
+        <v>4095</v>
       </c>
       <c r="N14" t="n">
-        <v>92.53</v>
+        <v>197.92</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>190</v>
+        <v>570</v>
       </c>
       <c r="Q14" t="n">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="R14" t="n">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>925.3</v>
+        <v>4095</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2227,17 +2229,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2247,16 +2249,16 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>925.3</v>
+        <v>1365</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>654.02</v>
+        <v>2845.58</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2265,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>92.53</v>
+        <v>593.76</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2273,28 +2275,26 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2000015924881136</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2000012450675355</v>
-      </c>
+        <v>2000015935667022</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>46828113793</v>
+        <v>46833482066</v>
       </c>
       <c r="D15" t="n">
-        <v>154166302560</v>
+        <v>153550074671</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>MARCOPEMA</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000015924881136</v>
+        <v>2000015935667022</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-11T10:56:27.000-04:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2321,28 +2321,28 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="N15" t="n">
-        <v>22.8</v>
+        <v>88.63</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>285.52</v>
+        <v>137</v>
       </c>
       <c r="Q15" t="n">
-        <v>189.52</v>
+        <v>95</v>
       </c>
       <c r="R15" t="n">
-        <v>95.99999999999997</v>
+        <v>42</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2354,17 +2354,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>BOCMORROSMOR-410</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2374,16 +2374,16 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>184.57</v>
+        <v>622.48</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>22.8</v>
+        <v>88.63</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2400,28 +2400,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2000015924881134</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2000012450675355</v>
-      </c>
+        <v>2000015932827654</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>46828113793</v>
+        <v>46831838345</v>
       </c>
       <c r="D16" t="n">
-        <v>153420099615</v>
+        <v>154262740072</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>ROJASDAVID20210814233921</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000015924881134</v>
+        <v>2000015932827654</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-11T01:59:07.000-04:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2448,28 +2446,28 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="N16" t="n">
-        <v>22.8</v>
+        <v>88.63</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>285.52</v>
+        <v>125</v>
       </c>
       <c r="Q16" t="n">
-        <v>189.52</v>
+        <v>95</v>
       </c>
       <c r="R16" t="n">
-        <v>95.99999999999997</v>
+        <v>30</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2481,17 +2479,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>BOCMORAZUMOR-410</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2501,16 +2499,16 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>184.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2519,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2527,26 +2525,28 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2000015923571686</v>
-      </c>
-      <c r="B17" t="inlineStr"/>
+        <v>2000015932875024</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2000012459011895</v>
+      </c>
       <c r="C17" t="n">
-        <v>46827760364</v>
+        <v>46831837021</v>
       </c>
       <c r="D17" t="n">
-        <v>153405868355</v>
+        <v>153516147611</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VAZQUEZSARA20230812202049</t>
+          <t>LOAN2137132</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2000015923571686</v>
+        <v>2000015932875024</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-10T11:59:16.000-04:00</t>
+          <t>2026-04-11T01:57:33.000-04:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2573,28 +2573,28 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>185</v>
+        <v>134.55</v>
       </c>
       <c r="N17" t="n">
-        <v>27.75</v>
+        <v>13.46</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="Q17" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>185</v>
+        <v>134.55</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>MULMORNEGmc-5848c</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>MLM3357041104</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2626,16 +2626,16 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>185</v>
+        <v>134.55</v>
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>102.5</v>
+        <v>76.91</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>27.75</v>
+        <v>13.46</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2652,28 +2652,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2000015922863610</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2000012448562543</v>
-      </c>
+        <v>2000015932632586</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>46827137585</v>
+        <v>46831736271</v>
       </c>
       <c r="D18" t="n">
-        <v>153396288659</v>
+        <v>153514027567</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JORFERK</t>
+          <t>ERVINEDUARDO RAMÍREZVZLA</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000015922863610</v>
+        <v>2000015932632586</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-10T11:07:52.000-04:00</t>
+          <t>2026-04-11T00:54:31.000-04:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2700,28 +2698,28 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>713</v>
+        <v>570.86</v>
       </c>
       <c r="N18" t="n">
-        <v>103.38</v>
+        <v>111.32</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="Q18" t="n">
-        <v>84.5</v>
+        <v>65.5</v>
       </c>
       <c r="R18" t="n">
-        <v>84.5</v>
+        <v>63.5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>713</v>
+        <v>570.86</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2733,12 +2731,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>73239381698389</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MLM3488449480</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2753,16 +2751,16 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>713</v>
+        <v>570.86</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>460.58</v>
+        <v>342.37</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2771,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>103.38</v>
+        <v>111.32</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2779,28 +2777,26 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000015921193538</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2000012426900403</v>
-      </c>
+        <v>2000015932009672</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>46826592416</v>
+        <v>46831746812</v>
       </c>
       <c r="D19" t="n">
-        <v>153376320777</v>
+        <v>153507878875</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALONDRAVIZUET</t>
+          <t>PLER973318</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2000015921193538</v>
+        <v>2000015932009672</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-10T09:05:19.000-04:00</t>
+          <t>2026-04-10T23:10:48.000-04:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2827,28 +2823,28 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>954</v>
+        <v>429</v>
       </c>
       <c r="N19" t="n">
-        <v>138.33</v>
+        <v>62.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="Q19" t="n">
-        <v>95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>95</v>
+        <v>26.40000000000001</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>954</v>
+        <v>429</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2860,12 +2856,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>76825869750536</t>
+          <t>76825709097220</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MLM4762485780</t>
+          <t>MLM4762499328</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2880,16 +2876,16 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
+          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>954</v>
+        <v>429</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>634.3200000000001</v>
+        <v>260.36</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2898,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>138.33</v>
+        <v>62.2</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2906,28 +2902,28 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000015920405788</v>
+        <v>2000015931967972</v>
       </c>
       <c r="B20" t="n">
-        <v>2000012446018577</v>
+        <v>2000012458078981</v>
       </c>
       <c r="C20" t="n">
-        <v>46825928963</v>
+        <v>46831734526</v>
       </c>
       <c r="D20" t="n">
-        <v>154112621330</v>
+        <v>154254282856</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RODIBERTOROBLESALEJANDRO</t>
+          <t>HECTORPETITHECTORPETIT</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000015920405788</v>
+        <v>2000015931967972</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-10T07:55:11.000-04:00</t>
+          <t>2026-04-10T23:07:11.000-04:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2954,28 +2950,28 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>462</v>
+        <v>827.64</v>
       </c>
       <c r="N20" t="n">
-        <v>66.98999999999999</v>
+        <v>120.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>119.2</v>
+        <v>169</v>
       </c>
       <c r="Q20" t="n">
-        <v>59.6</v>
+        <v>84.5</v>
       </c>
       <c r="R20" t="n">
-        <v>59.6</v>
+        <v>84.5</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>462</v>
+        <v>827.64</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2987,12 +2983,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>76532580917858</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>MLM2381238905</t>
+          <t>MLM4545490694</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3007,16 +3003,16 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
+          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>462</v>
+        <v>827.64</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>293.59</v>
+        <v>548.21</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3025,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>66.98999999999999</v>
+        <v>120.01</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3033,28 +3029,28 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2000015919255616</v>
+        <v>2000015931930082</v>
       </c>
       <c r="B21" t="n">
-        <v>2000012444792845</v>
+        <v>2000012457998119</v>
       </c>
       <c r="C21" t="n">
-        <v>46825583586</v>
+        <v>46831420445</v>
       </c>
       <c r="D21" t="n">
-        <v>153344481991</v>
+        <v>154253338188</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MARTHACANDELARIALOPEZCORDOVA</t>
+          <t>CARLOSALFONZ</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2000015919255616</v>
+        <v>2000015931930082</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-10T02:48:35.000-04:00</t>
+          <t>2026-04-10T22:55:27.000-04:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3081,28 +3077,28 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>204.71</v>
+        <v>3158.4</v>
       </c>
       <c r="N21" t="n">
-        <v>29.68</v>
+        <v>457.97</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="R21" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>204.71</v>
+        <v>3158.4</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3114,12 +3110,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>BR-KZNU-9NOO</t>
+          <t>76867668365155</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM4762499740</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3134,16 +3130,16 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>204.71</v>
+        <v>3158.4</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>100.5</v>
+        <v>2319.54</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3152,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>29.68</v>
+        <v>457.97</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3160,26 +3156,28 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2000015918864062</v>
-      </c>
-      <c r="B22" t="inlineStr"/>
+        <v>2000015931187904</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2000012457258861</v>
+      </c>
       <c r="C22" t="n">
-        <v>46825132377</v>
+        <v>46831390290</v>
       </c>
       <c r="D22" t="n">
-        <v>154084595658</v>
+        <v>154246400496</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ALEJANDRO3654</t>
+          <t>PEÑAHERNAN20221106222959</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000015918864062</v>
+        <v>2000015931187904</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-10T00:54:13.000-04:00</t>
+          <t>2026-04-10T21:46:13.000-04:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3206,28 +3204,28 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>198.75</v>
+        <v>925.3</v>
       </c>
       <c r="N22" t="n">
-        <v>28.82</v>
+        <v>92.53</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="R22" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>198.75</v>
+        <v>925.3</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3239,17 +3237,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3259,16 +3257,16 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>198.75</v>
+        <v>925.3</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>117.94</v>
+        <v>654.02</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3277,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>28.82</v>
+        <v>92.53</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3285,38 +3283,36 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2000015918735504</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2000012444242337</v>
-      </c>
+        <v>2000015930234104</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>46825081431</v>
+        <v>46830673091</v>
       </c>
       <c r="D23" t="n">
-        <v>154083285822</v>
+        <v>153488743041</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JLPACHECOS</t>
+          <t>BOAL6432084</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2000015918735504</v>
+        <v>2000015930234104</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-10T00:31:16.000-04:00</t>
+          <t>2026-04-10T20:22:43.000-04:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3333,28 +3329,28 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>427.5</v>
+        <v>285</v>
       </c>
       <c r="N23" t="n">
-        <v>64.12</v>
+        <v>55.58</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>135.2</v>
+        <v>98</v>
       </c>
       <c r="Q23" t="n">
-        <v>67.59999999999999</v>
+        <v>39</v>
       </c>
       <c r="R23" t="n">
-        <v>67.59999999999999</v>
+        <v>59</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>427.5</v>
+        <v>285</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3366,12 +3362,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>A18/A38</t>
+          <t>77343215226889</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>MLM3442935972</t>
+          <t>MLM5098643766</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3386,16 +3382,16 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>427.5</v>
+        <v>285</v>
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>257.09</v>
+        <v>164.62</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3404,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>64.12</v>
+        <v>55.58</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3412,28 +3408,28 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2000015918564930</v>
+        <v>2000015929551932</v>
       </c>
       <c r="B24" t="n">
-        <v>2000012444063601</v>
+        <v>2000012455537231</v>
       </c>
       <c r="C24" t="n">
-        <v>46825008245</v>
+        <v>46830373077</v>
       </c>
       <c r="D24" t="n">
-        <v>154081820206</v>
+        <v>153480488965</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OSCARCOLOTL</t>
+          <t>SOPORIESLAVERGAZONA817</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000015918564930</v>
+        <v>2000015929551932</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-10T00:03:34.000-04:00</t>
+          <t>2026-04-10T19:30:38.000-04:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3460,28 +3456,28 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>164.45</v>
+        <v>795.24</v>
       </c>
       <c r="N24" t="n">
-        <v>16.44</v>
+        <v>115.31</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>64</v>
+        <v>445</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>222.5</v>
       </c>
       <c r="R24" t="n">
-        <v>32</v>
+        <v>222.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>164.45</v>
+        <v>795.24</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3493,17 +3489,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>76825905347021</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4762473244</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3513,16 +3509,16 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>164.45</v>
+        <v>795.24</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>101.13</v>
+        <v>385.45</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3531,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.44</v>
+        <v>115.31</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3539,28 +3535,28 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2000015915026216</v>
+        <v>2000015929481304</v>
       </c>
       <c r="B25" t="n">
-        <v>2000012440383505</v>
+        <v>2000012455454135</v>
       </c>
       <c r="C25" t="n">
-        <v>46823711622</v>
+        <v>46830337829</v>
       </c>
       <c r="D25" t="n">
-        <v>154052836286</v>
+        <v>154225963480</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAKE9550997</t>
+          <t>VALERIAMARIASADAGARZA</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2000015915026216</v>
+        <v>2000015929481304</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-09T19:18:46.000-04:00</t>
+          <t>2026-04-10T19:24:38.000-04:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3587,28 +3583,28 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>234</v>
+        <v>237.5</v>
       </c>
       <c r="N25" t="n">
-        <v>23.4</v>
+        <v>42.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>275</v>
+        <v>104.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>221</v>
+        <v>52.4</v>
       </c>
       <c r="R25" t="n">
-        <v>54</v>
+        <v>52.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>234</v>
+        <v>237.5</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3620,12 +3616,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>75045745678283</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MLM3813363284</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3640,16 +3636,16 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>234</v>
+        <v>237.5</v>
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>189.42</v>
+        <v>120.85</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3658,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>23.4</v>
+        <v>42.75</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3666,26 +3662,28 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2000015914539400</v>
-      </c>
-      <c r="B26" t="inlineStr"/>
+        <v>2000015927409710</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2000012453315257</v>
+      </c>
       <c r="C26" t="n">
-        <v>46823497086</v>
+        <v>46829644948</v>
       </c>
       <c r="D26" t="n">
-        <v>153301992033</v>
+        <v>154195281014</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VNUSROJIBLANK12</t>
+          <t>BIOTECVO</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2000015914539400</v>
+        <v>2000015927409710</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-09T18:47:34.000-04:00</t>
+          <t>2026-04-10T16:40:07.000-04:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3709,31 +3707,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>713</v>
+        <v>475</v>
       </c>
       <c r="N26" t="n">
-        <v>103.38</v>
+        <v>42.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>126</v>
+        <v>209.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>84.5</v>
+        <v>104.8</v>
       </c>
       <c r="R26" t="n">
-        <v>41.5</v>
+        <v>104.8</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>713</v>
+        <v>475</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -3745,12 +3743,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>73239400752399</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MLM3488485454</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3765,16 +3763,16 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>713</v>
+        <v>237.5</v>
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>460.58</v>
+        <v>241.7</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3783,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>103.38</v>
+        <v>85.5</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3791,28 +3789,26 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2000015914254952</v>
-      </c>
-      <c r="B27" t="n">
-        <v>2000012439581533</v>
-      </c>
+        <v>2000015926465502</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>46823083335</v>
+        <v>46828912925</v>
       </c>
       <c r="D27" t="n">
-        <v>153298477411</v>
+        <v>154183216410</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GA20240622001650</t>
+          <t>JACOBOMIGUEL20230130120239</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2000015914254952</v>
+        <v>2000015926465502</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-09T18:26:50.000-04:00</t>
+          <t>2026-04-10T15:28:10.000-04:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3836,31 +3832,31 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>322</v>
+        <v>109.8</v>
       </c>
       <c r="N27" t="n">
-        <v>31.4</v>
+        <v>13.18</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="Q27" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R27" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>322</v>
+        <v>109.8</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3872,12 +3868,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>72141399181305</t>
+          <t>SOPMORDEFMH-70B</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>MLM2289340133</t>
+          <t>MLM3357068774</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3892,16 +3888,16 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>161</v>
+        <v>109.8</v>
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>150.05</v>
+        <v>46.68</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3910,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>62.8</v>
+        <v>13.18</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3918,28 +3914,26 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2000015913353944</v>
-      </c>
-      <c r="B28" t="n">
-        <v>2000012438644843</v>
-      </c>
+        <v>2000015925898954</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>46822944206</v>
+        <v>46828618943</v>
       </c>
       <c r="D28" t="n">
-        <v>153287496709</v>
+        <v>154176812930</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ESCI899332</t>
+          <t>MEDINAVIANEY20220808095244</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2000015913353944</v>
+        <v>2000015925898954</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-09T17:23:20.000-04:00</t>
+          <t>2026-04-10T14:44:48.000-04:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3966,19 +3960,19 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>164.45</v>
+        <v>122</v>
       </c>
       <c r="N28" t="n">
-        <v>16.44</v>
+        <v>12.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="R28" t="n">
         <v>32</v>
@@ -3987,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>164.45</v>
+        <v>122</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3999,12 +3993,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>76126320655919</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4676748386</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4019,16 +4013,16 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>164.45</v>
+        <v>122</v>
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>101.13</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4037,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>16.44</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4045,28 +4039,28 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2000015911947456</v>
+        <v>2000015925292404</v>
       </c>
       <c r="B29" t="n">
-        <v>2000012437174517</v>
+        <v>2000012451099821</v>
       </c>
       <c r="C29" t="n">
-        <v>46822254216</v>
+        <v>46828589732</v>
       </c>
       <c r="D29" t="n">
-        <v>154016462860</v>
+        <v>154170422818</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>VECE1241164</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000015911947456</v>
+        <v>2000015925292404</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T14:00:29.000-04:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4093,28 +4087,28 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>294.5</v>
+        <v>925.3</v>
       </c>
       <c r="N29" t="n">
-        <v>42.7</v>
+        <v>92.53</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="Q29" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="R29" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>294.5</v>
+        <v>925.3</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4126,17 +4120,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>76720994758426</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MLM5115426106</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4146,16 +4140,16 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>294.5</v>
+        <v>925.3</v>
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>225.14</v>
+        <v>654.02</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4164,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>42.7</v>
+        <v>92.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4172,28 +4166,28 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2000015911947458</v>
+        <v>2000015924881136</v>
       </c>
       <c r="B30" t="n">
-        <v>2000012437174517</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C30" t="n">
-        <v>46822254216</v>
+        <v>46828113793</v>
       </c>
       <c r="D30" t="n">
-        <v>154016435366</v>
+        <v>154166302560</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2000015911947458</v>
+        <v>2000015924881136</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4220,28 +4214,28 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="N30" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>152</v>
+        <v>285.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>76</v>
+        <v>189.52</v>
       </c>
       <c r="R30" t="n">
-        <v>76</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4253,17 +4247,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>AUDMORNEGM-921pack</t>
+          <t>BOCMORROSMOR-410</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>MLM3356978052</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4273,16 +4267,16 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>149.14</v>
+        <v>184.57</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4291,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4299,28 +4293,28 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2000015911035950</v>
+        <v>2000015924881134</v>
       </c>
       <c r="B31" t="n">
-        <v>2000012436224727</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C31" t="n">
-        <v>46821806098</v>
+        <v>46828113793</v>
       </c>
       <c r="D31" t="n">
-        <v>154008453720</v>
+        <v>153420099615</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HLALTAMIRANO</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000015911035950</v>
+        <v>2000015924881134</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-09T14:44:05.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4347,28 +4341,28 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>560.5</v>
+        <v>228</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3</v>
+        <v>22.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>131</v>
+        <v>285.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.5</v>
+        <v>189.52</v>
       </c>
       <c r="R31" t="n">
-        <v>65.5</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>560.5</v>
+        <v>228</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4380,12 +4374,12 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>BOCMORAZUMOR-410</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4400,16 +4394,16 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>560.5</v>
+        <v>228</v>
       </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>334.96</v>
+        <v>184.57</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4418,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>109.3</v>
+        <v>22.8</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4426,26 +4420,26 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2000015910487320</v>
+        <v>2000015923571686</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>46821271897</v>
+        <v>46827760364</v>
       </c>
       <c r="D32" t="n">
-        <v>153258785401</v>
+        <v>153405868355</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ENLACESS</t>
+          <t>VAZQUEZSARA20230812202049</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2000015910487320</v>
+        <v>2000015923571686</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-09T14:10:04.000-04:00</t>
+          <t>2026-04-10T11:59:16.000-04:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4472,28 +4466,28 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>134.55</v>
+        <v>185</v>
       </c>
       <c r="N32" t="n">
-        <v>13.46</v>
+        <v>27.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R32" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>134.55</v>
+        <v>185</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4505,12 +4499,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>MULMORNEGmc-5848c</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3357041104</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4525,16 +4519,16 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>134.55</v>
+        <v>185</v>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>76.91</v>
+        <v>102.5</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4543,7 +4537,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>13.46</v>
+        <v>27.75</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4551,28 +4545,28 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2000015909133456</v>
+        <v>2000015922863610</v>
       </c>
       <c r="B33" t="n">
-        <v>2000012434212221</v>
+        <v>2000012448562543</v>
       </c>
       <c r="C33" t="n">
-        <v>46820912508</v>
+        <v>46827137585</v>
       </c>
       <c r="D33" t="n">
-        <v>153993729394</v>
+        <v>153396288659</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ULY5205</t>
+          <t>JORFERK</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000015909133456</v>
+        <v>2000015922863610</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-09T12:45:26.000-04:00</t>
+          <t>2026-04-10T11:07:52.000-04:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4599,28 +4593,28 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>189</v>
+        <v>713</v>
       </c>
       <c r="N33" t="n">
-        <v>31.18</v>
+        <v>103.38</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="Q33" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="R33" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>189</v>
+        <v>713</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -4632,12 +4626,12 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>BOCMORROK405</t>
+          <t>73239381698389</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM3488449480</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4652,16 +4646,16 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>189</v>
+        <v>713</v>
       </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>108.72</v>
+        <v>460.58</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4670,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>31.18</v>
+        <v>103.38</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4678,28 +4672,28 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2000015901141806</v>
+        <v>2000015921193538</v>
       </c>
       <c r="B34" t="n">
-        <v>2000012425847369</v>
+        <v>2000012426900403</v>
       </c>
       <c r="C34" t="n">
-        <v>46816833391</v>
+        <v>46826592416</v>
       </c>
       <c r="D34" t="n">
-        <v>153164140863</v>
+        <v>153376320777</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PC20241019154452</t>
+          <t>ALONDRAVIZUET</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2000015901141806</v>
+        <v>2000015921193538</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-08T21:27:21.000-04:00</t>
+          <t>2026-04-10T09:05:19.000-04:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4726,28 +4720,28 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>167.9</v>
+        <v>954</v>
       </c>
       <c r="N34" t="n">
-        <v>25.18</v>
+        <v>138.33</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="Q34" t="n">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="R34" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>167.9</v>
+        <v>954</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -4759,12 +4753,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>CARMORDEFP-203</t>
+          <t>76825869750536</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MLM1912930539</t>
+          <t>MLM4762485780</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4779,16 +4773,16 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>167.9</v>
+        <v>954</v>
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>18.7</v>
+        <v>634.3200000000001</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4797,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>138.33</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4805,28 +4799,28 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2000015900479830</v>
+        <v>2000015920405788</v>
       </c>
       <c r="B35" t="n">
-        <v>2000012425150469</v>
+        <v>2000012446018577</v>
       </c>
       <c r="C35" t="n">
-        <v>46816813562</v>
+        <v>46825928963</v>
       </c>
       <c r="D35" t="n">
-        <v>153903764628</v>
+        <v>154112621330</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GOJE20240421120542</t>
+          <t>RODIBERTOROBLESALEJANDRO</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2000015900479830</v>
+        <v>2000015920405788</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-08T20:46:39.000-04:00</t>
+          <t>2026-04-10T07:55:11.000-04:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4853,28 +4847,28 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>164.45</v>
+        <v>462</v>
       </c>
       <c r="N35" t="n">
-        <v>16.44</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>64</v>
+        <v>119.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>59.6</v>
       </c>
       <c r="R35" t="n">
-        <v>32</v>
+        <v>59.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>164.45</v>
+        <v>462</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4886,17 +4880,17 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2381238905</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4906,16 +4900,16 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>164.45</v>
+        <v>462</v>
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>101.13</v>
+        <v>293.59</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4924,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>16.44</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -4932,28 +4926,28 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2000015898605836</v>
+        <v>2000015919255616</v>
       </c>
       <c r="B36" t="n">
-        <v>2000012423204427</v>
+        <v>2000012444792845</v>
       </c>
       <c r="C36" t="n">
-        <v>46815701425</v>
+        <v>46825583586</v>
       </c>
       <c r="D36" t="n">
-        <v>153887348360</v>
+        <v>153344481991</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JG20241208202301</t>
+          <t>MARTHACANDELARIALOPEZCORDOVA</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2000015898605836</v>
+        <v>2000015919255616</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-08T18:56:03.000-04:00</t>
+          <t>2026-04-10T02:48:35.000-04:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4980,28 +4974,28 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="N36" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="R36" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5013,17 +5007,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BR-KZNU-9NOO</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5033,16 +5027,16 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>101.13</v>
+        <v>100.5</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5051,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5059,28 +5053,26 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2000015897678942</v>
-      </c>
-      <c r="B37" t="n">
-        <v>2000012422238933</v>
-      </c>
+        <v>2000015918864062</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>46815285151</v>
+        <v>46825132377</v>
       </c>
       <c r="D37" t="n">
-        <v>153133108857</v>
+        <v>154084595658</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PIAD3222701</t>
+          <t>ALEJANDRO3654</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2000015897678942</v>
+        <v>2000015918864062</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-08T17:58:14.000-04:00</t>
+          <t>2026-04-10T00:54:13.000-04:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5107,28 +5099,28 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>840</v>
+        <v>198.75</v>
       </c>
       <c r="N37" t="n">
-        <v>121.8</v>
+        <v>28.82</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="Q37" t="n">
-        <v>84.5</v>
+        <v>34</v>
       </c>
       <c r="R37" t="n">
-        <v>84.5</v>
+        <v>47</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>840</v>
+        <v>198.75</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5140,12 +5132,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>72368155667130</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>MLM2090316531</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5160,27 +5152,1928 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>840</v>
+        <v>198.75</v>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
+        <v>117.94</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2000015918735504</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2000012444242337</v>
+      </c>
+      <c r="C38" t="n">
+        <v>46825081431</v>
+      </c>
+      <c r="D38" t="n">
+        <v>154083285822</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JLPACHECOS</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2000015918735504</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:31:16.000-04:00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="R38" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>A18/A38</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>MLM3442935972</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2000012444063601</v>
+      </c>
+      <c r="C39" t="n">
+        <v>46825008245</v>
+      </c>
+      <c r="D39" t="n">
+        <v>154081820206</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OSCARCOLOTL</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:03:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N39" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>32</v>
+      </c>
+      <c r="R39" t="n">
+        <v>32</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2000012440383505</v>
+      </c>
+      <c r="C40" t="n">
+        <v>46823711622</v>
+      </c>
+      <c r="D40" t="n">
+        <v>154052836286</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAKE9550997</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-04-09T19:18:46.000-04:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>234</v>
+      </c>
+      <c r="N40" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>221</v>
+      </c>
+      <c r="R40" t="n">
+        <v>54</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>234</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>75045745678283</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>MLM3813363284</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>234</v>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="n">
+        <v>189.42</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>46823497086</v>
+      </c>
+      <c r="D41" t="n">
+        <v>153301992033</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VNUSROJIBLANK12</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:47:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>713</v>
+      </c>
+      <c r="N41" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>713</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>73239400752399</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>MLM3488485454</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>713</v>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="n">
+        <v>460.58</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2000012439581533</v>
+      </c>
+      <c r="C42" t="n">
+        <v>46823083335</v>
+      </c>
+      <c r="D42" t="n">
+        <v>153298477411</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>GA20240622001650</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:26:50.000-04:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>322</v>
+      </c>
+      <c r="N42" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>80</v>
+      </c>
+      <c r="R42" t="n">
+        <v>80</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>322</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>72141399181305</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>MLM2289340133</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>161</v>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="n">
+        <v>150.05</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2000012438644843</v>
+      </c>
+      <c r="C43" t="n">
+        <v>46822944206</v>
+      </c>
+      <c r="D43" t="n">
+        <v>153287496709</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ESCI899332</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-04-09T17:23:20.000-04:00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>32</v>
+      </c>
+      <c r="R43" t="n">
+        <v>32</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C44" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D44" t="n">
+        <v>154016462860</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>76</v>
+      </c>
+      <c r="R44" t="n">
+        <v>76</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>76720994758426</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>MLM5115426106</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C45" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D45" t="n">
+        <v>154016435366</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>76</v>
+      </c>
+      <c r="R45" t="n">
+        <v>76</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>AUDMORNEGM-921pack</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>MLM3356978052</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="n">
+        <v>149.14</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2000012436224727</v>
+      </c>
+      <c r="C46" t="n">
+        <v>46821806098</v>
+      </c>
+      <c r="D46" t="n">
+        <v>154008453720</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HLALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:44:05.000-04:00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="N46" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>74725206008902</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>MLM3712202158</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>46821271897</v>
+      </c>
+      <c r="D47" t="n">
+        <v>153258785401</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ENLACESS</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:10:04.000-04:00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="N47" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>32</v>
+      </c>
+      <c r="R47" t="n">
+        <v>67</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>75961290041531</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>MLM4318429096</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2000012434212221</v>
+      </c>
+      <c r="C48" t="n">
+        <v>46820912508</v>
+      </c>
+      <c r="D48" t="n">
+        <v>153993729394</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ULY5205</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-04-09T12:45:26.000-04:00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>189</v>
+      </c>
+      <c r="N48" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>32</v>
+      </c>
+      <c r="R48" t="n">
+        <v>32</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>189</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>BOCMORROK405</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>MLM2972698110</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>189</v>
+      </c>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2000012425847369</v>
+      </c>
+      <c r="C49" t="n">
+        <v>46816833391</v>
+      </c>
+      <c r="D49" t="n">
+        <v>153164140863</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PC20241019154452</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-04-08T21:27:21.000-04:00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="N49" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>134</v>
+      </c>
+      <c r="R49" t="n">
+        <v>32</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>CARMORDEFP-203</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>MLM1912930539</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2000012425150469</v>
+      </c>
+      <c r="C50" t="n">
+        <v>46816813562</v>
+      </c>
+      <c r="D50" t="n">
+        <v>153903764628</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GOJE20240421120542</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-04-08T20:46:39.000-04:00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N50" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>32</v>
+      </c>
+      <c r="R50" t="n">
+        <v>32</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2000012423204427</v>
+      </c>
+      <c r="C51" t="n">
+        <v>46815701425</v>
+      </c>
+      <c r="D51" t="n">
+        <v>153887348360</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>JG20241208202301</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-04-08T18:56:03.000-04:00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N51" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>32</v>
+      </c>
+      <c r="R51" t="n">
+        <v>32</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2000012422238933</v>
+      </c>
+      <c r="C52" t="n">
+        <v>46815285151</v>
+      </c>
+      <c r="D52" t="n">
+        <v>153133108857</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PIAD3222701</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-08T17:58:14.000-04:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>840</v>
+      </c>
+      <c r="N52" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>840</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>72368155667130</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>MLM2090316531</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>840</v>
+      </c>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="n">
         <v>557.67</v>
       </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>121.8</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AI52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ventas_ml_historico.xlsx
+++ b/ventas_ml_historico.xlsx
@@ -413,14 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI52"/>
+  <dimension ref="A1:AI66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -438,7 +438,7 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="27" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
@@ -632,36 +632,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000015945008650</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
+        <v>2000015958900598</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2000012486229035</v>
+      </c>
       <c r="C2" t="n">
-        <v>46837630090</v>
+        <v>46843756962</v>
       </c>
       <c r="D2" t="n">
-        <v>154412117972</v>
+        <v>154544707106</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TONO5981002</t>
+          <t>INEV9190937</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000015945008650</v>
+        <v>2000015958900598</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-12T05:17:26.000-04:00</t>
+          <t>2026-04-13T07:55:09.000-04:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -675,31 +677,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>886.34</v>
+        <v>364</v>
       </c>
       <c r="N2" t="n">
-        <v>88.63</v>
+        <v>25.48</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>886.34</v>
+        <v>364</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -711,17 +713,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>22187150-white-LAGOM</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM1582859464</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -731,16 +733,16 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>886.34</v>
+        <v>182</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>216.1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -749,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>50.96</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -757,28 +759,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000015944827404</v>
+        <v>2000015957217578</v>
       </c>
       <c r="B3" t="n">
-        <v>2000012471530373</v>
+        <v>2000012484446139</v>
       </c>
       <c r="C3" t="n">
-        <v>46837277205</v>
+        <v>46842931282</v>
       </c>
       <c r="D3" t="n">
-        <v>153662197883</v>
+        <v>153767839871</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JESSICAMIRTALADELENROA</t>
+          <t>PIINCHEPERRO</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000015944827404</v>
+        <v>2000015957217578</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-12T02:47:16.000-04:00</t>
+          <t>2026-04-13T00:18:19.000-04:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -805,28 +807,28 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="N3" t="n">
-        <v>33.66</v>
+        <v>13.46</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>76.27</v>
+        <v>64</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.27</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>34.99999999999999</v>
+        <v>32</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -838,17 +840,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>BOCMORAZU405</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -858,16 +860,16 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>110.6</v>
+        <v>76.91</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -876,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>33.66</v>
+        <v>13.46</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -884,26 +886,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000015944791160</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>2000015956925426</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2000012484147313</v>
+      </c>
       <c r="C4" t="n">
-        <v>46837546532</v>
+        <v>46842537261</v>
       </c>
       <c r="D4" t="n">
-        <v>153662234221</v>
+        <v>153765643607</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RA20241216152952</t>
+          <t>REINAJUDTIHRAMREZ</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000015944791160</v>
+        <v>2000015956925426</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-12T02:43:18.000-04:00</t>
+          <t>2026-04-12T23:36:15.000-04:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,28 +934,28 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>202.65</v>
+        <v>204</v>
       </c>
       <c r="N4" t="n">
-        <v>33.44</v>
+        <v>33.66</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="n">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>202.65</v>
+        <v>204</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -963,12 +967,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PX-SJL9-BCN0</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MLM2082055833</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -983,16 +987,16 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>202.65</v>
+        <v>204</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>112.86</v>
+        <v>116.87</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1001,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>33.44</v>
+        <v>33.66</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1009,28 +1013,28 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2000015944554586</v>
+        <v>2000015956605502</v>
       </c>
       <c r="B5" t="n">
-        <v>2000012471236369</v>
+        <v>2000012483808797</v>
       </c>
       <c r="C5" t="n">
-        <v>46837165917</v>
+        <v>46842403159</v>
       </c>
       <c r="D5" t="n">
-        <v>154406778626</v>
+        <v>154511573332</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JUANANGELDUEÑASRINCON</t>
+          <t>PEOR7869303</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000015944554586</v>
+        <v>2000015956605502</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-12T01:07:15.000-04:00</t>
+          <t>2026-04-12T22:59:10.000-04:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,31 +1058,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>134.55</v>
+        <v>252.3</v>
       </c>
       <c r="N5" t="n">
-        <v>13.46</v>
+        <v>13.88</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>64</v>
+        <v>210</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="R5" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>134.55</v>
+        <v>252.3</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1090,12 +1094,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>73117950936864</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4537227786</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1110,16 +1114,16 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Soporte De Celular Para Carro Estabilizador De Teléfono Color Negro</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>134.55</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>76.91</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1128,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>13.46</v>
+        <v>41.64</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1136,38 +1140,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000015944520040</v>
+        <v>2000015955581526</v>
       </c>
       <c r="B6" t="n">
-        <v>2000012471190691</v>
+        <v>2000012482766177</v>
       </c>
       <c r="C6" t="n">
-        <v>46837150907</v>
+        <v>46841978337</v>
       </c>
       <c r="D6" t="n">
-        <v>153658671197</v>
+        <v>154505410318</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GUJU6869975</t>
+          <t>JOSTIMOTEOGUERREROCASTILLO</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000015944520040</v>
+        <v>2000015955581526</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-12T00:57:45.000-04:00</t>
+          <t>2026-04-12T21:32:57.000-04:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1184,10 +1188,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>886.34</v>
+        <v>1365</v>
       </c>
       <c r="N6" t="n">
-        <v>88.63</v>
+        <v>197.92</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1205,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>886.34</v>
+        <v>1365</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1217,17 +1221,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1237,16 +1241,16 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>886.34</v>
+        <v>1365</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>622.48</v>
+        <v>948.52</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1255,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>88.63</v>
+        <v>197.92</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1263,28 +1267,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2000015944439726</v>
+        <v>2000015955406042</v>
       </c>
       <c r="B7" t="n">
-        <v>2000012471123715</v>
+        <v>2000012482561253</v>
       </c>
       <c r="C7" t="n">
-        <v>46837123631</v>
+        <v>46842164894</v>
       </c>
       <c r="D7" t="n">
-        <v>154405486928</v>
+        <v>153755964839</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TAJU9721170</t>
+          <t>YATZIRYZUBIA</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000015944439726</v>
+        <v>2000015955406042</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-12T00:41:22.000-04:00</t>
+          <t>2026-04-12T21:18:30.000-04:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,28 +1315,28 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>206.95</v>
+        <v>172.79</v>
       </c>
       <c r="N7" t="n">
-        <v>31.04</v>
+        <v>25.92</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>152</v>
+        <v>135.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>206.95</v>
+        <v>172.79</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1344,17 +1348,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Blanco K073</t>
+          <t>72478699982948</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MLM3129247568</t>
+          <t>MLM2853107461</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1364,16 +1368,16 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
+          <t>Extensión Regleta Moreka Mc5447c 8 Tomas 2 Usb C Protección 2m Blanca Blanco</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>206.95</v>
+        <v>172.79</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>157.18</v>
+        <v>63.63</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1382,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>31.04</v>
+        <v>25.92</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1390,28 +1394,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2000015944444922</v>
+        <v>2000015955037638</v>
       </c>
       <c r="B8" t="n">
-        <v>2000012471123715</v>
+        <v>2000012482184957</v>
       </c>
       <c r="C8" t="n">
-        <v>46837123631</v>
+        <v>46841741585</v>
       </c>
       <c r="D8" t="n">
-        <v>154405351746</v>
+        <v>153753433147</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TAJU9721170</t>
+          <t>ORNELASJONATHAN20230517180340</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000015944444922</v>
+        <v>2000015955037638</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-12T00:41:22.000-04:00</t>
+          <t>2026-04-12T20:54:10.000-04:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1438,28 +1442,28 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="N8" t="n">
-        <v>31.04</v>
+        <v>13.46</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="Q8" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1471,17 +1475,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Azul K073</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MLM3129247568</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1491,16 +1495,16 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>81.18000000000001</v>
+        <v>76.91</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1509,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>31.04</v>
+        <v>13.46</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1517,28 +1521,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2000015944248160</v>
+        <v>2000015953863248</v>
       </c>
       <c r="B9" t="n">
-        <v>2000012470820489</v>
+        <v>2000012480954851</v>
       </c>
       <c r="C9" t="n">
-        <v>46837041551</v>
+        <v>46841512724</v>
       </c>
       <c r="D9" t="n">
-        <v>154403287242</v>
+        <v>154492811296</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JUANCARLOSCARMONAALFARO</t>
+          <t>ALANROBLES896</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2000015944248160</v>
+        <v>2000015953863248</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-11T23:59:26.000-04:00</t>
+          <t>2026-04-12T19:36:07.000-04:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1565,28 +1569,28 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>204.71</v>
+        <v>134.55</v>
       </c>
       <c r="N9" t="n">
-        <v>29.68</v>
+        <v>13.46</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>105.46</v>
+        <v>64</v>
       </c>
       <c r="Q9" t="n">
-        <v>67.45999999999999</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>204.71</v>
+        <v>134.55</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1598,17 +1602,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1618,16 +1622,16 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>204.71</v>
+        <v>134.55</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>89.04000000000001</v>
+        <v>76.91</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1636,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>29.68</v>
+        <v>13.46</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1644,28 +1648,26 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000015942032840</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2000012468587881</v>
-      </c>
+        <v>2000015953129652</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>46836369178</v>
+        <v>46840936695</v>
       </c>
       <c r="D10" t="n">
-        <v>154378603064</v>
+        <v>153738745847</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JOELLDJ</t>
+          <t>LUISEDUARDOJIMNEZCABRERA</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000015942032840</v>
+        <v>2000015953129652</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-11T19:53:08.000-04:00</t>
+          <t>2026-04-12T18:47:14.000-04:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1692,28 +1694,28 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>700</v>
+        <v>99.75</v>
       </c>
       <c r="N10" t="n">
-        <v>101.5</v>
+        <v>14.96</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="Q10" t="n">
-        <v>84.5</v>
+        <v>38</v>
       </c>
       <c r="R10" t="n">
-        <v>84.5</v>
+        <v>70</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>700</v>
+        <v>99.75</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1725,12 +1727,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>CARMORDEFJB212AA-1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MLM4388568286</t>
+          <t>MLM3357055624</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1745,16 +1747,16 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
+          <t>Pilas Recargables Aaa Jiabao 350mah Pack 10 Con Cargador Jb-212</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>700</v>
+        <v>99.75</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>450.63</v>
+        <v>37.76</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1763,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>101.5</v>
+        <v>14.96</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1771,26 +1773,26 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2000015941753476</v>
+        <v>2000015952631620</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>46836259542</v>
+        <v>46840996916</v>
       </c>
       <c r="D11" t="n">
-        <v>153627775865</v>
+        <v>153734537841</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NOYOLAIVAN20231112183250</t>
+          <t>MAAU5192905</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000015941753476</v>
+        <v>2000015952631620</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-11T19:31:35.000-04:00</t>
+          <t>2026-04-12T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1817,28 +1819,28 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>189</v>
+        <v>886.34</v>
       </c>
       <c r="N11" t="n">
-        <v>31.18</v>
+        <v>88.63</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>163.87</v>
       </c>
       <c r="R11" t="n">
-        <v>77</v>
+        <v>70.13</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>189</v>
+        <v>886.34</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1850,17 +1852,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1870,16 +1872,16 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>189</v>
+        <v>886.34</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>622.48</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1888,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>88.63</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1896,28 +1898,28 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2000015941686260</v>
+        <v>2000015951746522</v>
       </c>
       <c r="B12" t="n">
-        <v>2000012468221695</v>
+        <v>2000012478741857</v>
       </c>
       <c r="C12" t="n">
-        <v>46836215454</v>
+        <v>46840326297</v>
       </c>
       <c r="D12" t="n">
-        <v>154373847452</v>
+        <v>153726813143</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAAN8167043</t>
+          <t>NATHALIALONZOVARGAS</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000015941686260</v>
+        <v>2000015951746522</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-11T19:23:01.000-04:00</t>
+          <t>2026-04-12T17:02:23.000-04:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1977,12 +1979,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1997,7 +1999,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
@@ -2023,26 +2025,28 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2000015941054478</v>
-      </c>
-      <c r="B13" t="inlineStr"/>
+        <v>2000015950193056</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2000012476881167</v>
+      </c>
       <c r="C13" t="n">
-        <v>46835940590</v>
+        <v>46839927702</v>
       </c>
       <c r="D13" t="n">
-        <v>154365172508</v>
+        <v>154462576514</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>L20260220145454</t>
+          <t>DUER9786335</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2000015941054478</v>
+        <v>2000015950193056</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-11T18:29:38.000-04:00</t>
+          <t>2026-04-12T15:02:47.000-04:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2069,28 +2073,28 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="N13" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="Q13" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="R13" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2102,12 +2106,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2122,16 +2126,16 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>622.48</v>
+        <v>108.91</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2140,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2148,28 +2152,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2000015940863248</v>
+        <v>2000015950183992</v>
       </c>
       <c r="B14" t="n">
-        <v>2000012467360959</v>
+        <v>2000012476881167</v>
       </c>
       <c r="C14" t="n">
-        <v>46835581697</v>
+        <v>46839927702</v>
       </c>
       <c r="D14" t="n">
-        <v>154362231108</v>
+        <v>154462600152</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JOSMANUELHERNNDEZMRQUEZ</t>
+          <t>DUER9786335</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000015940863248</v>
+        <v>2000015950183992</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-11T18:12:34.000-04:00</t>
+          <t>2026-04-12T15:02:47.000-04:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2193,31 +2197,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>4095</v>
+        <v>134.55</v>
       </c>
       <c r="N14" t="n">
-        <v>197.92</v>
+        <v>13.46</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>570</v>
+        <v>128</v>
       </c>
       <c r="Q14" t="n">
-        <v>285</v>
+        <v>64</v>
       </c>
       <c r="R14" t="n">
-        <v>285</v>
+        <v>64</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4095</v>
+        <v>134.55</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2229,17 +2233,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>72591346859892</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MLM2157132507</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2249,16 +2253,16 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>1365</v>
+        <v>134.55</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>2845.58</v>
+        <v>44.91</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2267,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>593.76</v>
+        <v>13.46</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2275,26 +2279,26 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2000015935667022</v>
+        <v>2000015949142546</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>46833482066</v>
+        <v>46839201507</v>
       </c>
       <c r="D15" t="n">
-        <v>153550074671</v>
+        <v>153706432727</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MARCOPEMA</t>
+          <t>G20250531223627</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000015935667022</v>
+        <v>2000015949142546</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-11T10:56:27.000-04:00</t>
+          <t>2026-04-12T13:40:31.000-04:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2321,28 +2325,28 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>886.34</v>
+        <v>204</v>
       </c>
       <c r="N15" t="n">
-        <v>88.63</v>
+        <v>33.66</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Q15" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="R15" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>886.34</v>
+        <v>204</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2354,17 +2358,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2374,16 +2378,16 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>886.34</v>
+        <v>204</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>622.48</v>
+        <v>116.87</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2392,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>88.63</v>
+        <v>33.66</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2400,26 +2404,26 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2000015932827654</v>
+        <v>2000015945008650</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>46831838345</v>
+        <v>46837630090</v>
       </c>
       <c r="D16" t="n">
-        <v>154262740072</v>
+        <v>154412117972</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ROJASDAVID20210814233921</t>
+          <t>TONO5981002</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000015932827654</v>
+        <v>2000015945008650</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-11T01:59:07.000-04:00</t>
+          <t>2026-04-12T05:17:26.000-04:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2455,13 +2459,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="Q16" t="n">
         <v>95</v>
       </c>
       <c r="R16" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2525,28 +2529,28 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2000015932875024</v>
+        <v>2000015944827404</v>
       </c>
       <c r="B17" t="n">
-        <v>2000012459011895</v>
+        <v>2000012471530373</v>
       </c>
       <c r="C17" t="n">
-        <v>46831837021</v>
+        <v>46837277205</v>
       </c>
       <c r="D17" t="n">
-        <v>153516147611</v>
+        <v>153662197883</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LOAN2137132</t>
+          <t>JESSICAMIRTALADELENROA</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2000015932875024</v>
+        <v>2000015944827404</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-11T01:57:33.000-04:00</t>
+          <t>2026-04-12T02:47:16.000-04:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2573,28 +2577,28 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>134.55</v>
+        <v>204</v>
       </c>
       <c r="N17" t="n">
-        <v>13.46</v>
+        <v>33.66</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>64</v>
+        <v>76.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>41.27</v>
       </c>
       <c r="R17" t="n">
-        <v>32</v>
+        <v>34.99999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>134.55</v>
+        <v>204</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2606,17 +2610,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BOCMORAZU405</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2626,16 +2630,16 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>134.55</v>
+        <v>204</v>
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>76.91</v>
+        <v>110.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2644,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>13.46</v>
+        <v>33.66</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2652,26 +2656,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2000015932632586</v>
+        <v>2000015944791160</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>46831736271</v>
+        <v>46837546532</v>
       </c>
       <c r="D18" t="n">
-        <v>153514027567</v>
+        <v>153662234221</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ERVINEDUARDO RAMÍREZVZLA</t>
+          <t>RA20241216152952</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000015932632586</v>
+        <v>2000015944791160</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-11T00:54:31.000-04:00</t>
+          <t>2026-04-12T02:43:18.000-04:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2698,28 +2702,28 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>570.86</v>
+        <v>202.65</v>
       </c>
       <c r="N18" t="n">
-        <v>111.32</v>
+        <v>33.44</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="Q18" t="n">
-        <v>65.5</v>
+        <v>125</v>
       </c>
       <c r="R18" t="n">
-        <v>63.5</v>
+        <v>38</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>570.86</v>
+        <v>202.65</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2731,12 +2735,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>PX-SJL9-BCN0</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM2082055833</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2751,16 +2755,16 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>570.86</v>
+        <v>202.65</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>342.37</v>
+        <v>112.86</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2769,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>111.32</v>
+        <v>33.44</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2777,26 +2781,28 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000015932009672</v>
-      </c>
-      <c r="B19" t="inlineStr"/>
+        <v>2000015944554586</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2000012471236369</v>
+      </c>
       <c r="C19" t="n">
-        <v>46831746812</v>
+        <v>46837165917</v>
       </c>
       <c r="D19" t="n">
-        <v>153507878875</v>
+        <v>154406778626</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PLER973318</t>
+          <t>JUANANGELDUEÑASRINCON</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2000015932009672</v>
+        <v>2000015944554586</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-10T23:10:48.000-04:00</t>
+          <t>2026-04-12T01:07:15.000-04:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2823,28 +2829,28 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="N19" t="n">
-        <v>62.2</v>
+        <v>13.46</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="Q19" t="n">
-        <v>67.59999999999999</v>
+        <v>32</v>
       </c>
       <c r="R19" t="n">
-        <v>26.40000000000001</v>
+        <v>32</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2856,17 +2862,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>76825709097220</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MLM4762499328</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2876,16 +2882,16 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>260.36</v>
+        <v>76.91</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2894,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>62.2</v>
+        <v>13.46</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2902,38 +2908,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000015931967972</v>
+        <v>2000015944520040</v>
       </c>
       <c r="B20" t="n">
-        <v>2000012458078981</v>
+        <v>2000012471190691</v>
       </c>
       <c r="C20" t="n">
-        <v>46831734526</v>
+        <v>46837150907</v>
       </c>
       <c r="D20" t="n">
-        <v>154254282856</v>
+        <v>153658671197</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HECTORPETITHECTORPETIT</t>
+          <t>GUJU6869975</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000015931967972</v>
+        <v>2000015944520040</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-10T23:07:11.000-04:00</t>
+          <t>2026-04-12T00:57:45.000-04:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2950,28 +2956,28 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="N20" t="n">
-        <v>120.01</v>
+        <v>88.63</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="Q20" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="R20" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2983,17 +2989,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>76532580917858</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>MLM4545490694</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3003,16 +3009,16 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>548.21</v>
+        <v>622.48</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3021,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>120.01</v>
+        <v>88.63</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3029,28 +3035,28 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2000015931930082</v>
+        <v>2000015944439726</v>
       </c>
       <c r="B21" t="n">
-        <v>2000012457998119</v>
+        <v>2000012471123715</v>
       </c>
       <c r="C21" t="n">
-        <v>46831420445</v>
+        <v>46837123631</v>
       </c>
       <c r="D21" t="n">
-        <v>154253338188</v>
+        <v>154405486928</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CARLOSALFONZ</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2000015931930082</v>
+        <v>2000015944439726</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-10T22:55:27.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3077,28 +3083,28 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>3158.4</v>
+        <v>206.95</v>
       </c>
       <c r="N21" t="n">
-        <v>457.97</v>
+        <v>31.04</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="Q21" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="R21" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3158.4</v>
+        <v>206.95</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3110,12 +3116,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>76867668365155</t>
+          <t>Blanco K073</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MLM4762499740</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3130,16 +3136,16 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>3158.4</v>
+        <v>206.95</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>2319.54</v>
+        <v>157.18</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3148,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>457.97</v>
+        <v>31.04</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3156,28 +3162,28 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2000015931187904</v>
+        <v>2000015944444922</v>
       </c>
       <c r="B22" t="n">
-        <v>2000012457258861</v>
+        <v>2000012471123715</v>
       </c>
       <c r="C22" t="n">
-        <v>46831390290</v>
+        <v>46837123631</v>
       </c>
       <c r="D22" t="n">
-        <v>154246400496</v>
+        <v>154405351746</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PEÑAHERNAN20221106222959</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000015931187904</v>
+        <v>2000015944444922</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-10T21:46:13.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3204,28 +3210,28 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="N22" t="n">
-        <v>92.53</v>
+        <v>31.04</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="Q22" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="R22" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3237,17 +3243,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>Azul K073</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3257,16 +3263,16 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>654.02</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3275,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>92.53</v>
+        <v>31.04</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3283,36 +3289,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2000015930234104</v>
-      </c>
-      <c r="B23" t="inlineStr"/>
+        <v>2000015944248160</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2000012470820489</v>
+      </c>
       <c r="C23" t="n">
-        <v>46830673091</v>
+        <v>46837041551</v>
       </c>
       <c r="D23" t="n">
-        <v>153488743041</v>
+        <v>154403287242</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BOAL6432084</t>
+          <t>JUANCARLOSCARMONAALFARO</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2000015930234104</v>
+        <v>2000015944248160</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-10T20:22:43.000-04:00</t>
+          <t>2026-04-11T23:59:26.000-04:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3329,28 +3337,28 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>285</v>
+        <v>204.71</v>
       </c>
       <c r="N23" t="n">
-        <v>55.58</v>
+        <v>29.68</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>98</v>
+        <v>105.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>39</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>285</v>
+        <v>204.71</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3362,12 +3370,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>77343215226889</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>MLM5098643766</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3382,16 +3390,16 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>285</v>
+        <v>204.71</v>
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>164.62</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3400,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>55.58</v>
+        <v>29.68</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3408,28 +3416,28 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2000015929551932</v>
+        <v>2000015942032840</v>
       </c>
       <c r="B24" t="n">
-        <v>2000012455537231</v>
+        <v>2000012468587881</v>
       </c>
       <c r="C24" t="n">
-        <v>46830373077</v>
+        <v>46836369178</v>
       </c>
       <c r="D24" t="n">
-        <v>153480488965</v>
+        <v>154378603064</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SOPORIESLAVERGAZONA817</t>
+          <t>JOELLDJ</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000015929551932</v>
+        <v>2000015942032840</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-10T19:30:38.000-04:00</t>
+          <t>2026-04-11T19:53:08.000-04:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3456,28 +3464,28 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>795.24</v>
+        <v>700</v>
       </c>
       <c r="N24" t="n">
-        <v>115.31</v>
+        <v>101.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>445</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="n">
-        <v>222.5</v>
+        <v>84.5</v>
       </c>
       <c r="R24" t="n">
-        <v>222.5</v>
+        <v>84.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>795.24</v>
+        <v>700</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3489,17 +3497,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>76825905347021</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MLM4762473244</t>
+          <t>MLM4388568286</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3509,16 +3517,16 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
+          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>795.24</v>
+        <v>700</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>385.45</v>
+        <v>450.63</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3527,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>115.31</v>
+        <v>101.5</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3535,28 +3543,26 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2000015929481304</v>
-      </c>
-      <c r="B25" t="n">
-        <v>2000012455454135</v>
-      </c>
+        <v>2000015941753476</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>46830337829</v>
+        <v>46836259542</v>
       </c>
       <c r="D25" t="n">
-        <v>154225963480</v>
+        <v>153627775865</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VALERIAMARIASADAGARZA</t>
+          <t>NOYOLAIVAN20231112183250</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2000015929481304</v>
+        <v>2000015941753476</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-10T19:24:38.000-04:00</t>
+          <t>2026-04-11T19:31:35.000-04:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3583,28 +3589,28 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="N25" t="n">
-        <v>42.75</v>
+        <v>31.18</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>104.8</v>
+        <v>109</v>
       </c>
       <c r="Q25" t="n">
-        <v>52.4</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
-        <v>52.4</v>
+        <v>77</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3616,12 +3622,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3636,16 +3642,16 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>120.85</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3654,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>42.75</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3662,28 +3668,28 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2000015927409710</v>
+        <v>2000015941686260</v>
       </c>
       <c r="B26" t="n">
-        <v>2000012453315257</v>
+        <v>2000012468221695</v>
       </c>
       <c r="C26" t="n">
-        <v>46829644948</v>
+        <v>46836215454</v>
       </c>
       <c r="D26" t="n">
-        <v>154195281014</v>
+        <v>154373847452</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BIOTECVO</t>
+          <t>CAAN8167043</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2000015927409710</v>
+        <v>2000015941686260</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-10T16:40:07.000-04:00</t>
+          <t>2026-04-11T19:23:01.000-04:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3707,31 +3713,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>475</v>
+        <v>134.55</v>
       </c>
       <c r="N26" t="n">
-        <v>42.75</v>
+        <v>13.46</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>209.6</v>
+        <v>64</v>
       </c>
       <c r="Q26" t="n">
-        <v>104.8</v>
+        <v>32</v>
       </c>
       <c r="R26" t="n">
-        <v>104.8</v>
+        <v>32</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>475</v>
+        <v>134.55</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -3743,17 +3749,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3763,16 +3769,16 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>237.5</v>
+        <v>134.55</v>
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>241.7</v>
+        <v>76.91</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3781,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>85.5</v>
+        <v>13.46</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3789,26 +3795,26 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2000015926465502</v>
+        <v>2000015941054478</v>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>46828912925</v>
+        <v>46835940590</v>
       </c>
       <c r="D27" t="n">
-        <v>154183216410</v>
+        <v>154365172508</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JACOBOMIGUEL20230130120239</t>
+          <t>L20260220145454</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2000015926465502</v>
+        <v>2000015941054478</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-10T15:28:10.000-04:00</t>
+          <t>2026-04-11T18:29:38.000-04:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3835,28 +3841,28 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>109.8</v>
+        <v>886.34</v>
       </c>
       <c r="N27" t="n">
-        <v>13.18</v>
+        <v>88.63</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="R27" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>109.8</v>
+        <v>886.34</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3868,12 +3874,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>SOPMORDEFMH-70B</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>MLM3357068774</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3888,16 +3894,16 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>109.8</v>
+        <v>886.34</v>
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>46.68</v>
+        <v>622.48</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3906,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>13.18</v>
+        <v>88.63</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3914,26 +3920,28 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2000015925898954</v>
-      </c>
-      <c r="B28" t="inlineStr"/>
+        <v>2000015940863248</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2000012467360959</v>
+      </c>
       <c r="C28" t="n">
-        <v>46828618943</v>
+        <v>46835581697</v>
       </c>
       <c r="D28" t="n">
-        <v>154176812930</v>
+        <v>154362231108</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MEDINAVIANEY20220808095244</t>
+          <t>JOSMANUELHERNNDEZMRQUEZ</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2000015925898954</v>
+        <v>2000015940863248</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-10T14:44:48.000-04:00</t>
+          <t>2026-04-11T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3957,31 +3965,31 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>122</v>
+        <v>4095</v>
       </c>
       <c r="N28" t="n">
-        <v>12.2</v>
+        <v>197.92</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="Q28" t="n">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="R28" t="n">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>122</v>
+        <v>4095</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3993,17 +4001,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>76126320655919</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MLM4676748386</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4013,16 +4021,16 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>122</v>
+        <v>1365</v>
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2845.58</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4031,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>593.76</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4039,28 +4047,26 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2000015925292404</v>
-      </c>
-      <c r="B29" t="n">
-        <v>2000012451099821</v>
-      </c>
+        <v>2000015935667022</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>46828589732</v>
+        <v>46833482066</v>
       </c>
       <c r="D29" t="n">
-        <v>154170422818</v>
+        <v>153550074671</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VECE1241164</t>
+          <t>MARCOPEMA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000015925292404</v>
+        <v>2000015935667022</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-10T14:00:29.000-04:00</t>
+          <t>2026-04-11T10:56:27.000-04:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4087,28 +4093,28 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="N29" t="n">
-        <v>92.53</v>
+        <v>88.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="Q29" t="n">
         <v>95</v>
       </c>
       <c r="R29" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4145,11 +4151,11 @@
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>654.02</v>
+        <v>622.48</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4158,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>92.53</v>
+        <v>88.63</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4166,28 +4172,26 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2000015924881136</v>
-      </c>
-      <c r="B30" t="n">
-        <v>2000012450675355</v>
-      </c>
+        <v>2000015932827654</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>46828113793</v>
+        <v>46831838345</v>
       </c>
       <c r="D30" t="n">
-        <v>154166302560</v>
+        <v>154262740072</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>ROJASDAVID20210814233921</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2000015924881136</v>
+        <v>2000015932827654</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-11T01:59:07.000-04:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4214,28 +4218,28 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="N30" t="n">
-        <v>22.8</v>
+        <v>88.63</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>285.52</v>
+        <v>125</v>
       </c>
       <c r="Q30" t="n">
-        <v>189.52</v>
+        <v>95</v>
       </c>
       <c r="R30" t="n">
-        <v>95.99999999999997</v>
+        <v>30</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4247,17 +4251,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>BOCMORROSMOR-410</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4267,16 +4271,16 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>184.57</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4285,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4293,28 +4297,28 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2000015924881134</v>
+        <v>2000015932875024</v>
       </c>
       <c r="B31" t="n">
-        <v>2000012450675355</v>
+        <v>2000012459011895</v>
       </c>
       <c r="C31" t="n">
-        <v>46828113793</v>
+        <v>46831837021</v>
       </c>
       <c r="D31" t="n">
-        <v>153420099615</v>
+        <v>153516147611</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>LOAN2137132</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000015924881134</v>
+        <v>2000015932875024</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-11T01:57:33.000-04:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4341,28 +4345,28 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>228</v>
+        <v>134.55</v>
       </c>
       <c r="N31" t="n">
-        <v>22.8</v>
+        <v>13.46</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>285.52</v>
+        <v>64</v>
       </c>
       <c r="Q31" t="n">
-        <v>189.52</v>
+        <v>32</v>
       </c>
       <c r="R31" t="n">
-        <v>95.99999999999997</v>
+        <v>32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>228</v>
+        <v>134.55</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4374,17 +4378,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>BOCMORAZUMOR-410</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4394,16 +4398,16 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>228</v>
+        <v>134.55</v>
       </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>184.57</v>
+        <v>76.91</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4412,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>22.8</v>
+        <v>13.46</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4420,26 +4424,26 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2000015923571686</v>
+        <v>2000015932632586</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>46827760364</v>
+        <v>46831736271</v>
       </c>
       <c r="D32" t="n">
-        <v>153405868355</v>
+        <v>153514027567</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VAZQUEZSARA20230812202049</t>
+          <t>ERVINEDUARDO RAMÍREZVZLA</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2000015923571686</v>
+        <v>2000015932632586</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-10T11:59:16.000-04:00</t>
+          <t>2026-04-11T00:54:31.000-04:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4466,28 +4470,28 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>185</v>
+        <v>570.86</v>
       </c>
       <c r="N32" t="n">
-        <v>27.75</v>
+        <v>111.32</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>65.5</v>
       </c>
       <c r="R32" t="n">
-        <v>45</v>
+        <v>63.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>185</v>
+        <v>570.86</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4499,17 +4503,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>MULMORNEGmc-5848c</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MLM3357041104</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4519,16 +4523,16 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>185</v>
+        <v>570.86</v>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>102.5</v>
+        <v>342.37</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4537,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>27.75</v>
+        <v>111.32</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4545,28 +4549,26 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2000015922863610</v>
-      </c>
-      <c r="B33" t="n">
-        <v>2000012448562543</v>
-      </c>
+        <v>2000015932009672</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>46827137585</v>
+        <v>46831746812</v>
       </c>
       <c r="D33" t="n">
-        <v>153396288659</v>
+        <v>153507878875</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JORFERK</t>
+          <t>PLER973318</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000015922863610</v>
+        <v>2000015932009672</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-10T11:07:52.000-04:00</t>
+          <t>2026-04-10T23:10:48.000-04:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4593,28 +4595,28 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>713</v>
+        <v>429</v>
       </c>
       <c r="N33" t="n">
-        <v>103.38</v>
+        <v>62.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="Q33" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R33" t="n">
-        <v>84.5</v>
+        <v>26.40000000000001</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>713</v>
+        <v>429</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -4626,12 +4628,12 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>73239381698389</t>
+          <t>76825709097220</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>MLM3488449480</t>
+          <t>MLM4762499328</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4646,16 +4648,16 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
+          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>713</v>
+        <v>429</v>
       </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>460.58</v>
+        <v>260.36</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4664,7 +4666,7 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>103.38</v>
+        <v>62.2</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4672,28 +4674,28 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2000015921193538</v>
+        <v>2000015931967972</v>
       </c>
       <c r="B34" t="n">
-        <v>2000012426900403</v>
+        <v>2000012458078981</v>
       </c>
       <c r="C34" t="n">
-        <v>46826592416</v>
+        <v>46831734526</v>
       </c>
       <c r="D34" t="n">
-        <v>153376320777</v>
+        <v>154254282856</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ALONDRAVIZUET</t>
+          <t>HECTORPETITHECTORPETIT</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2000015921193538</v>
+        <v>2000015931967972</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-10T09:05:19.000-04:00</t>
+          <t>2026-04-10T23:07:11.000-04:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4720,28 +4722,28 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>954</v>
+        <v>827.64</v>
       </c>
       <c r="N34" t="n">
-        <v>138.33</v>
+        <v>120.01</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="Q34" t="n">
-        <v>95</v>
+        <v>84.5</v>
       </c>
       <c r="R34" t="n">
-        <v>95</v>
+        <v>84.5</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>954</v>
+        <v>827.64</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -4753,12 +4755,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>76825869750536</t>
+          <t>76532580917858</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MLM4762485780</t>
+          <t>MLM4545490694</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4773,16 +4775,16 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
+          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>954</v>
+        <v>827.64</v>
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>634.3200000000001</v>
+        <v>548.21</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4791,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>138.33</v>
+        <v>120.01</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4799,28 +4801,28 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2000015920405788</v>
+        <v>2000015931930082</v>
       </c>
       <c r="B35" t="n">
-        <v>2000012446018577</v>
+        <v>2000012457998119</v>
       </c>
       <c r="C35" t="n">
-        <v>46825928963</v>
+        <v>46831420445</v>
       </c>
       <c r="D35" t="n">
-        <v>154112621330</v>
+        <v>154253338188</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RODIBERTOROBLESALEJANDRO</t>
+          <t>CARLOSALFONZ</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2000015920405788</v>
+        <v>2000015931930082</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-10T07:55:11.000-04:00</t>
+          <t>2026-04-10T22:55:27.000-04:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4847,28 +4849,28 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>462</v>
+        <v>3158.4</v>
       </c>
       <c r="N35" t="n">
-        <v>66.98999999999999</v>
+        <v>457.97</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>119.2</v>
+        <v>190</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.6</v>
+        <v>95</v>
       </c>
       <c r="R35" t="n">
-        <v>59.6</v>
+        <v>95</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>462</v>
+        <v>3158.4</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4880,12 +4882,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>76867668365155</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MLM2381238905</t>
+          <t>MLM4762499740</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4900,16 +4902,16 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
+          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>462</v>
+        <v>3158.4</v>
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>293.59</v>
+        <v>2319.54</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4918,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>66.98999999999999</v>
+        <v>457.97</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -4926,28 +4928,28 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2000015919255616</v>
+        <v>2000015931187904</v>
       </c>
       <c r="B36" t="n">
-        <v>2000012444792845</v>
+        <v>2000012457258861</v>
       </c>
       <c r="C36" t="n">
-        <v>46825583586</v>
+        <v>46831390290</v>
       </c>
       <c r="D36" t="n">
-        <v>153344481991</v>
+        <v>154246400496</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MARTHACANDELARIALOPEZCORDOVA</t>
+          <t>PEÑAHERNAN20221106222959</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2000015919255616</v>
+        <v>2000015931187904</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-10T02:48:35.000-04:00</t>
+          <t>2026-04-10T21:46:13.000-04:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4974,28 +4976,28 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="N36" t="n">
-        <v>29.68</v>
+        <v>92.53</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="Q36" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="R36" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5007,17 +5009,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>BR-KZNU-9NOO</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5027,16 +5029,16 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>100.5</v>
+        <v>654.02</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5045,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>29.68</v>
+        <v>92.53</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5053,36 +5055,36 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2000015918864062</v>
+        <v>2000015930234104</v>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>46825132377</v>
+        <v>46830673091</v>
       </c>
       <c r="D37" t="n">
-        <v>154084595658</v>
+        <v>153488743041</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ALEJANDRO3654</t>
+          <t>BOAL6432084</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2000015918864062</v>
+        <v>2000015930234104</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-10T00:54:13.000-04:00</t>
+          <t>2026-04-10T20:22:43.000-04:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5099,28 +5101,28 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>198.75</v>
+        <v>285</v>
       </c>
       <c r="N37" t="n">
-        <v>28.82</v>
+        <v>55.58</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>198.75</v>
+        <v>285</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5132,12 +5134,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>77343215226889</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM5098643766</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5152,16 +5154,16 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>198.75</v>
+        <v>285</v>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>117.94</v>
+        <v>164.62</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5170,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>28.82</v>
+        <v>55.58</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5178,28 +5180,28 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2000015918735504</v>
+        <v>2000015929551932</v>
       </c>
       <c r="B38" t="n">
-        <v>2000012444242337</v>
+        <v>2000012455537231</v>
       </c>
       <c r="C38" t="n">
-        <v>46825081431</v>
+        <v>46830373077</v>
       </c>
       <c r="D38" t="n">
-        <v>154083285822</v>
+        <v>153480488965</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JLPACHECOS</t>
+          <t>SOPORIESLAVERGAZONA817</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2000015918735504</v>
+        <v>2000015929551932</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-10T00:31:16.000-04:00</t>
+          <t>2026-04-10T19:30:38.000-04:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5226,28 +5228,28 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>427.5</v>
+        <v>795.24</v>
       </c>
       <c r="N38" t="n">
-        <v>64.12</v>
+        <v>115.31</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>135.2</v>
+        <v>445</v>
       </c>
       <c r="Q38" t="n">
-        <v>67.59999999999999</v>
+        <v>222.5</v>
       </c>
       <c r="R38" t="n">
-        <v>67.59999999999999</v>
+        <v>222.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>427.5</v>
+        <v>795.24</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5259,12 +5261,12 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>A18/A38</t>
+          <t>76825905347021</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>MLM3442935972</t>
+          <t>MLM4762473244</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5279,16 +5281,16 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>427.5</v>
+        <v>795.24</v>
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>257.09</v>
+        <v>385.45</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5297,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>64.12</v>
+        <v>115.31</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5305,28 +5307,28 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2000015918564930</v>
+        <v>2000015929481304</v>
       </c>
       <c r="B39" t="n">
-        <v>2000012444063601</v>
+        <v>2000012455454135</v>
       </c>
       <c r="C39" t="n">
-        <v>46825008245</v>
+        <v>46830337829</v>
       </c>
       <c r="D39" t="n">
-        <v>154081820206</v>
+        <v>154225963480</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OSCARCOLOTL</t>
+          <t>VALERIAMARIASADAGARZA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2000015918564930</v>
+        <v>2000015929481304</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-10T00:03:34.000-04:00</t>
+          <t>2026-04-10T19:24:38.000-04:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5353,28 +5355,28 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="N39" t="n">
-        <v>16.44</v>
+        <v>42.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>64</v>
+        <v>104.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="R39" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -5386,17 +5388,17 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5406,16 +5408,16 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>101.13</v>
+        <v>120.85</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5424,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>16.44</v>
+        <v>42.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5432,28 +5434,28 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2000015915026216</v>
+        <v>2000015927409710</v>
       </c>
       <c r="B40" t="n">
-        <v>2000012440383505</v>
+        <v>2000012453315257</v>
       </c>
       <c r="C40" t="n">
-        <v>46823711622</v>
+        <v>46829644948</v>
       </c>
       <c r="D40" t="n">
-        <v>154052836286</v>
+        <v>154195281014</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAKE9550997</t>
+          <t>BIOTECVO</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2000015915026216</v>
+        <v>2000015927409710</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-09T19:18:46.000-04:00</t>
+          <t>2026-04-10T16:40:07.000-04:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5477,31 +5479,31 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>234</v>
+        <v>475</v>
       </c>
       <c r="N40" t="n">
-        <v>23.4</v>
+        <v>42.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>275</v>
+        <v>209.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>221</v>
+        <v>104.8</v>
       </c>
       <c r="R40" t="n">
-        <v>54</v>
+        <v>104.8</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>234</v>
+        <v>475</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -5513,12 +5515,12 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>75045745678283</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>MLM3813363284</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5533,16 +5535,16 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>234</v>
+        <v>237.5</v>
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>189.42</v>
+        <v>241.7</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5551,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>23.4</v>
+        <v>85.5</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5559,26 +5561,26 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2000015914539400</v>
+        <v>2000015926465502</v>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>46823497086</v>
+        <v>46828912925</v>
       </c>
       <c r="D41" t="n">
-        <v>153301992033</v>
+        <v>154183216410</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VNUSROJIBLANK12</t>
+          <t>JACOBOMIGUEL20230130120239</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2000015914539400</v>
+        <v>2000015926465502</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-09T18:47:34.000-04:00</t>
+          <t>2026-04-10T15:28:10.000-04:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5605,28 +5607,28 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>713</v>
+        <v>109.8</v>
       </c>
       <c r="N41" t="n">
-        <v>103.38</v>
+        <v>13.18</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="Q41" t="n">
-        <v>84.5</v>
+        <v>40</v>
       </c>
       <c r="R41" t="n">
-        <v>41.5</v>
+        <v>62</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>713</v>
+        <v>109.8</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -5638,17 +5640,17 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>73239400752399</t>
+          <t>SOPMORDEFMH-70B</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>MLM3488485454</t>
+          <t>MLM3357068774</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5658,16 +5660,16 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>713</v>
+        <v>109.8</v>
       </c>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>460.58</v>
+        <v>46.68</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5676,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>103.38</v>
+        <v>13.18</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5684,28 +5686,26 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2000015914254952</v>
-      </c>
-      <c r="B42" t="n">
-        <v>2000012439581533</v>
-      </c>
+        <v>2000015925898954</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>46823083335</v>
+        <v>46828618943</v>
       </c>
       <c r="D42" t="n">
-        <v>153298477411</v>
+        <v>154176812930</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GA20240622001650</t>
+          <t>MEDINAVIANEY20220808095244</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2000015914254952</v>
+        <v>2000015925898954</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-09T18:26:50.000-04:00</t>
+          <t>2026-04-10T14:44:48.000-04:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5729,31 +5729,31 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>322</v>
+        <v>122</v>
       </c>
       <c r="N42" t="n">
-        <v>31.4</v>
+        <v>12.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="R42" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>322</v>
+        <v>122</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>72141399181305</t>
+          <t>76126320655919</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MLM2289340133</t>
+          <t>MLM4676748386</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5785,16 +5785,16 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>150.05</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>62.8</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5811,28 +5811,28 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2000015913353944</v>
+        <v>2000015925292404</v>
       </c>
       <c r="B43" t="n">
-        <v>2000012438644843</v>
+        <v>2000012451099821</v>
       </c>
       <c r="C43" t="n">
-        <v>46822944206</v>
+        <v>46828589732</v>
       </c>
       <c r="D43" t="n">
-        <v>153287496709</v>
+        <v>154170422818</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ESCI899332</t>
+          <t>VECE1241164</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2000015913353944</v>
+        <v>2000015925292404</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-09T17:23:20.000-04:00</t>
+          <t>2026-04-10T14:00:29.000-04:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5859,28 +5859,28 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>164.45</v>
+        <v>925.3</v>
       </c>
       <c r="N43" t="n">
-        <v>16.44</v>
+        <v>92.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R43" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>164.45</v>
+        <v>925.3</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -5892,12 +5892,12 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -5912,16 +5912,16 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>164.45</v>
+        <v>925.3</v>
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
-        <v>101.13</v>
+        <v>654.02</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>16.44</v>
+        <v>92.53</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -5938,28 +5938,28 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2000015911947456</v>
+        <v>2000015924881136</v>
       </c>
       <c r="B44" t="n">
-        <v>2000012437174517</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C44" t="n">
-        <v>46822254216</v>
+        <v>46828113793</v>
       </c>
       <c r="D44" t="n">
-        <v>154016462860</v>
+        <v>154166302560</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2000015911947456</v>
+        <v>2000015924881136</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5986,28 +5986,28 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="N44" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>152</v>
+        <v>285.52</v>
       </c>
       <c r="Q44" t="n">
-        <v>76</v>
+        <v>189.52</v>
       </c>
       <c r="R44" t="n">
-        <v>76</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>76720994758426</t>
+          <t>BOCMORROSMOR-410</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>MLM5115426106</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6039,16 +6039,16 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
-        <v>225.14</v>
+        <v>184.57</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6065,28 +6065,28 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2000015911947458</v>
+        <v>2000015924881134</v>
       </c>
       <c r="B45" t="n">
-        <v>2000012437174517</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C45" t="n">
-        <v>46822254216</v>
+        <v>46828113793</v>
       </c>
       <c r="D45" t="n">
-        <v>154016435366</v>
+        <v>153420099615</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2000015911947458</v>
+        <v>2000015924881134</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6113,28 +6113,28 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="N45" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>152</v>
+        <v>285.52</v>
       </c>
       <c r="Q45" t="n">
-        <v>76</v>
+        <v>189.52</v>
       </c>
       <c r="R45" t="n">
-        <v>76</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6146,17 +6146,17 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>AUDMORNEGM-921pack</t>
+          <t>BOCMORAZUMOR-410</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MLM3356978052</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -6166,16 +6166,16 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>149.14</v>
+        <v>184.57</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6192,28 +6192,26 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2000015911035950</v>
-      </c>
-      <c r="B46" t="n">
-        <v>2000012436224727</v>
-      </c>
+        <v>2000015923571686</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>46821806098</v>
+        <v>46827760364</v>
       </c>
       <c r="D46" t="n">
-        <v>154008453720</v>
+        <v>153405868355</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HLALTAMIRANO</t>
+          <t>VAZQUEZSARA20230812202049</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2000015911035950</v>
+        <v>2000015923571686</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-09T14:44:05.000-04:00</t>
+          <t>2026-04-10T11:59:16.000-04:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6240,28 +6238,28 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>560.5</v>
+        <v>185</v>
       </c>
       <c r="N46" t="n">
-        <v>109.3</v>
+        <v>27.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="Q46" t="n">
-        <v>65.5</v>
+        <v>38</v>
       </c>
       <c r="R46" t="n">
-        <v>65.5</v>
+        <v>45</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>560.5</v>
+        <v>185</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -6273,17 +6271,17 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>MULMORNEGmc-5848c</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM3357041104</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6293,16 +6291,16 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>560.5</v>
+        <v>185</v>
       </c>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>334.96</v>
+        <v>102.5</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6311,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>109.3</v>
+        <v>27.75</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6319,26 +6317,28 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000015910487320</v>
-      </c>
-      <c r="B47" t="inlineStr"/>
+        <v>2000015922863610</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2000012448562543</v>
+      </c>
       <c r="C47" t="n">
-        <v>46821271897</v>
+        <v>46827137585</v>
       </c>
       <c r="D47" t="n">
-        <v>153258785401</v>
+        <v>153396288659</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ENLACESS</t>
+          <t>JORFERK</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2000015910487320</v>
+        <v>2000015922863610</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-09T14:10:04.000-04:00</t>
+          <t>2026-04-10T11:07:52.000-04:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6365,28 +6365,28 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>134.55</v>
+        <v>713</v>
       </c>
       <c r="N47" t="n">
-        <v>13.46</v>
+        <v>103.38</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="R47" t="n">
-        <v>67</v>
+        <v>84.5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>134.55</v>
+        <v>713</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>73239381698389</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3488449480</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6418,16 +6418,16 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>134.55</v>
+        <v>713</v>
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>76.91</v>
+        <v>460.58</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>13.46</v>
+        <v>103.38</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6444,28 +6444,28 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2000015909133456</v>
+        <v>2000015921193538</v>
       </c>
       <c r="B48" t="n">
-        <v>2000012434212221</v>
+        <v>2000012426900403</v>
       </c>
       <c r="C48" t="n">
-        <v>46820912508</v>
+        <v>46826592416</v>
       </c>
       <c r="D48" t="n">
-        <v>153993729394</v>
+        <v>153376320777</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ULY5205</t>
+          <t>ALONDRAVIZUET</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2000015909133456</v>
+        <v>2000015921193538</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-09T12:45:26.000-04:00</t>
+          <t>2026-04-10T09:05:19.000-04:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6492,28 +6492,28 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>189</v>
+        <v>954</v>
       </c>
       <c r="N48" t="n">
-        <v>31.18</v>
+        <v>138.33</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="Q48" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R48" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>189</v>
+        <v>954</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>BOCMORROK405</t>
+          <t>76825869750536</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM4762485780</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6545,16 +6545,16 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>189</v>
+        <v>954</v>
       </c>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>108.72</v>
+        <v>634.3200000000001</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>31.18</v>
+        <v>138.33</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6571,28 +6571,28 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2000015901141806</v>
+        <v>2000015920405788</v>
       </c>
       <c r="B49" t="n">
-        <v>2000012425847369</v>
+        <v>2000012446018577</v>
       </c>
       <c r="C49" t="n">
-        <v>46816833391</v>
+        <v>46825928963</v>
       </c>
       <c r="D49" t="n">
-        <v>153164140863</v>
+        <v>154112621330</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PC20241019154452</t>
+          <t>RODIBERTOROBLESALEJANDRO</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2000015901141806</v>
+        <v>2000015920405788</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-08T21:27:21.000-04:00</t>
+          <t>2026-04-10T07:55:11.000-04:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6619,28 +6619,28 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>167.9</v>
+        <v>462</v>
       </c>
       <c r="N49" t="n">
-        <v>25.18</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>166</v>
+        <v>119.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>134</v>
+        <v>59.6</v>
       </c>
       <c r="R49" t="n">
-        <v>32</v>
+        <v>59.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>167.9</v>
+        <v>462</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>CARMORDEFP-203</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MLM1912930539</t>
+          <t>MLM2381238905</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6672,16 +6672,16 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>167.9</v>
+        <v>462</v>
       </c>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>18.7</v>
+        <v>293.59</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6698,28 +6698,28 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2000015900479830</v>
+        <v>2000015919255616</v>
       </c>
       <c r="B50" t="n">
-        <v>2000012425150469</v>
+        <v>2000012444792845</v>
       </c>
       <c r="C50" t="n">
-        <v>46816813562</v>
+        <v>46825583586</v>
       </c>
       <c r="D50" t="n">
-        <v>153903764628</v>
+        <v>153344481991</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GOJE20240421120542</t>
+          <t>MARTHACANDELARIALOPEZCORDOVA</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2000015900479830</v>
+        <v>2000015919255616</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-08T20:46:39.000-04:00</t>
+          <t>2026-04-10T02:48:35.000-04:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6746,28 +6746,28 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="N50" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="Q50" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="R50" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -6779,17 +6779,17 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BR-KZNU-9NOO</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6799,16 +6799,16 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>101.13</v>
+        <v>100.5</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6825,28 +6825,26 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2000015898605836</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2000012423204427</v>
-      </c>
+        <v>2000015918864062</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>46815701425</v>
+        <v>46825132377</v>
       </c>
       <c r="D51" t="n">
-        <v>153887348360</v>
+        <v>154084595658</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>JG20241208202301</t>
+          <t>ALEJANDRO3654</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2000015898605836</v>
+        <v>2000015918864062</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-08T18:56:03.000-04:00</t>
+          <t>2026-04-10T00:54:13.000-04:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6873,28 +6871,28 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>164.45</v>
+        <v>198.75</v>
       </c>
       <c r="N51" t="n">
-        <v>16.44</v>
+        <v>28.82</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R51" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>164.45</v>
+        <v>198.75</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -6906,17 +6904,17 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6926,16 +6924,16 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>164.45</v>
+        <v>198.75</v>
       </c>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>101.13</v>
+        <v>117.94</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -6944,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>16.44</v>
+        <v>28.82</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -6952,28 +6950,28 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2000015897678942</v>
+        <v>2000015918735504</v>
       </c>
       <c r="B52" t="n">
-        <v>2000012422238933</v>
+        <v>2000012444242337</v>
       </c>
       <c r="C52" t="n">
-        <v>46815285151</v>
+        <v>46825081431</v>
       </c>
       <c r="D52" t="n">
-        <v>153133108857</v>
+        <v>154083285822</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PIAD3222701</t>
+          <t>JLPACHECOS</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2000015897678942</v>
+        <v>2000015918735504</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-08T17:58:14.000-04:00</t>
+          <t>2026-04-10T00:31:16.000-04:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7000,28 +6998,28 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>840</v>
+        <v>427.5</v>
       </c>
       <c r="N52" t="n">
-        <v>121.8</v>
+        <v>64.12</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>169</v>
+        <v>135.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R52" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>840</v>
+        <v>427.5</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7033,12 +7031,12 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>72368155667130</t>
+          <t>A18/A38</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MLM2090316531</t>
+          <t>MLM3442935972</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7053,27 +7051,1801 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>840</v>
+        <v>427.5</v>
       </c>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2000012444063601</v>
+      </c>
+      <c r="C53" t="n">
+        <v>46825008245</v>
+      </c>
+      <c r="D53" t="n">
+        <v>154081820206</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OSCARCOLOTL</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:03:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N53" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>32</v>
+      </c>
+      <c r="R53" t="n">
+        <v>32</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2000012440383505</v>
+      </c>
+      <c r="C54" t="n">
+        <v>46823711622</v>
+      </c>
+      <c r="D54" t="n">
+        <v>154052836286</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAKE9550997</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-04-09T19:18:46.000-04:00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>234</v>
+      </c>
+      <c r="N54" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>221</v>
+      </c>
+      <c r="R54" t="n">
+        <v>54</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>234</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>75045745678283</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>MLM3813363284</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>234</v>
+      </c>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="n">
+        <v>189.42</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>46823497086</v>
+      </c>
+      <c r="D55" t="n">
+        <v>153301992033</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>VNUSROJIBLANK12</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:47:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>713</v>
+      </c>
+      <c r="N55" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>713</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>73239400752399</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>MLM3488485454</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>713</v>
+      </c>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="n">
+        <v>460.58</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2000012439581533</v>
+      </c>
+      <c r="C56" t="n">
+        <v>46823083335</v>
+      </c>
+      <c r="D56" t="n">
+        <v>153298477411</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>GA20240622001650</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:26:50.000-04:00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>322</v>
+      </c>
+      <c r="N56" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>80</v>
+      </c>
+      <c r="R56" t="n">
+        <v>80</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>322</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>72141399181305</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>MLM2289340133</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>161</v>
+      </c>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="n">
+        <v>150.05</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2000012438644843</v>
+      </c>
+      <c r="C57" t="n">
+        <v>46822944206</v>
+      </c>
+      <c r="D57" t="n">
+        <v>153287496709</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ESCI899332</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-04-09T17:23:20.000-04:00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N57" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>32</v>
+      </c>
+      <c r="R57" t="n">
+        <v>32</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C58" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D58" t="n">
+        <v>154016462860</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>76</v>
+      </c>
+      <c r="R58" t="n">
+        <v>76</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>76720994758426</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>MLM5115426106</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C59" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D59" t="n">
+        <v>154016435366</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N59" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>76</v>
+      </c>
+      <c r="R59" t="n">
+        <v>76</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>AUDMORNEGM-921pack</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>MLM3356978052</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="n">
+        <v>149.14</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2000012436224727</v>
+      </c>
+      <c r="C60" t="n">
+        <v>46821806098</v>
+      </c>
+      <c r="D60" t="n">
+        <v>154008453720</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>HLALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:44:05.000-04:00</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>74725206008902</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>MLM3712202158</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>46821271897</v>
+      </c>
+      <c r="D61" t="n">
+        <v>153258785401</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ENLACESS</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:10:04.000-04:00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="N61" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>32</v>
+      </c>
+      <c r="R61" t="n">
+        <v>67</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>75961290041531</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>MLM4318429096</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2000012434212221</v>
+      </c>
+      <c r="C62" t="n">
+        <v>46820912508</v>
+      </c>
+      <c r="D62" t="n">
+        <v>153993729394</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ULY5205</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-04-09T12:45:26.000-04:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>189</v>
+      </c>
+      <c r="N62" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>32</v>
+      </c>
+      <c r="R62" t="n">
+        <v>32</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>189</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>BOCMORROK405</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>MLM2972698110</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>189</v>
+      </c>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2000012425847369</v>
+      </c>
+      <c r="C63" t="n">
+        <v>46816833391</v>
+      </c>
+      <c r="D63" t="n">
+        <v>153164140863</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PC20241019154452</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-04-08T21:27:21.000-04:00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="N63" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>134</v>
+      </c>
+      <c r="R63" t="n">
+        <v>32</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>CARMORDEFP-203</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>MLM1912930539</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2000012425150469</v>
+      </c>
+      <c r="C64" t="n">
+        <v>46816813562</v>
+      </c>
+      <c r="D64" t="n">
+        <v>153903764628</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>GOJE20240421120542</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-04-08T20:46:39.000-04:00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N64" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>32</v>
+      </c>
+      <c r="R64" t="n">
+        <v>32</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2000012423204427</v>
+      </c>
+      <c r="C65" t="n">
+        <v>46815701425</v>
+      </c>
+      <c r="D65" t="n">
+        <v>153887348360</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>JG20241208202301</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-04-08T18:56:03.000-04:00</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N65" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>32</v>
+      </c>
+      <c r="R65" t="n">
+        <v>32</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2000012422238933</v>
+      </c>
+      <c r="C66" t="n">
+        <v>46815285151</v>
+      </c>
+      <c r="D66" t="n">
+        <v>153133108857</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PIAD3222701</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-04-08T17:58:14.000-04:00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>840</v>
+      </c>
+      <c r="N66" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R66" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>840</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>72368155667130</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>MLM2090316531</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>840</v>
+      </c>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="n">
         <v>557.67</v>
       </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
         <v>121.8</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AI66" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ventas_ml_historico.xlsx
+++ b/ventas_ml_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI66"/>
+  <dimension ref="A1:AI80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -632,38 +632,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000015958900598</v>
+        <v>2000015976193144</v>
       </c>
       <c r="B2" t="n">
-        <v>2000012486229035</v>
+        <v>2000012504064087</v>
       </c>
       <c r="C2" t="n">
-        <v>46843756962</v>
+        <v>46851679477</v>
       </c>
       <c r="D2" t="n">
-        <v>154544707106</v>
+        <v>153955812817</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>INEV9190937</t>
+          <t>CEBALLOSJESSICA20220905212100</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000015958900598</v>
+        <v>2000015976193144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-13T07:55:09.000-04:00</t>
+          <t>2026-04-14T08:12:40.000-04:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -677,31 +677,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>364</v>
+        <v>490</v>
       </c>
       <c r="N2" t="n">
-        <v>25.48</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>128</v>
+        <v>135.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>64</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>364</v>
+        <v>490</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -713,17 +713,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>22187150-white-LAGOM</t>
+          <t>BOCMORGRI-385</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MLM1582859464</t>
+          <t>MLM2103166971</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -733,16 +733,16 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua 20w Color Gris</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>216.1</v>
+        <v>329.05</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>50.96</v>
+        <v>49</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -759,28 +759,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000015957217578</v>
+        <v>2000015974962414</v>
       </c>
       <c r="B3" t="n">
-        <v>2000012484446139</v>
+        <v>2000012502805039</v>
       </c>
       <c r="C3" t="n">
-        <v>46842931282</v>
+        <v>46851301984</v>
       </c>
       <c r="D3" t="n">
-        <v>153767839871</v>
+        <v>153941009449</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PIINCHEPERRO</t>
+          <t>GARCIAYAHIR20230307223626</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000015957217578</v>
+        <v>2000015974962414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-13T00:18:19.000-04:00</t>
+          <t>2026-04-14T05:15:35.000-04:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,28 +807,28 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>134.55</v>
+        <v>570.86</v>
       </c>
       <c r="N3" t="n">
-        <v>13.46</v>
+        <v>111.32</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>65.5</v>
       </c>
       <c r="R3" t="n">
-        <v>32</v>
+        <v>65.5</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>134.55</v>
+        <v>570.86</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -840,17 +840,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -860,16 +860,16 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>134.55</v>
+        <v>570.86</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>76.91</v>
+        <v>342.37</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>13.46</v>
+        <v>111.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -886,28 +886,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000015956925426</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2000012484147313</v>
-      </c>
+        <v>2000015973264718</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>46842537261</v>
+        <v>46850557744</v>
       </c>
       <c r="D4" t="n">
-        <v>153765643607</v>
+        <v>153919754851</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>REINAJUDTIHRAMREZ</t>
+          <t>OROM6364679</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000015956925426</v>
+        <v>2000015973264718</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-12T23:36:15.000-04:00</t>
+          <t>2026-04-13T22:48:32.000-04:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,28 +932,28 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>204</v>
+        <v>198.75</v>
       </c>
       <c r="N4" t="n">
-        <v>33.66</v>
+        <v>28.82</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>204</v>
+        <v>198.75</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -967,12 +965,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -987,16 +985,16 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>204</v>
+        <v>198.75</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>116.87</v>
+        <v>117.94</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1005,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>33.66</v>
+        <v>28.82</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1013,28 +1011,26 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2000015956605502</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2000012483808797</v>
-      </c>
+        <v>2000015972550020</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>46842403159</v>
+        <v>46850236336</v>
       </c>
       <c r="D5" t="n">
-        <v>154511573332</v>
+        <v>154665186470</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PEOR7869303</t>
+          <t>MOOJUSTINO20220525180349</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000015956605502</v>
+        <v>2000015972550020</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-12T22:59:10.000-04:00</t>
+          <t>2026-04-13T21:53:40.000-04:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,31 +1054,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>252.3</v>
+        <v>384.63</v>
       </c>
       <c r="N5" t="n">
-        <v>13.88</v>
+        <v>55.77</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>210</v>
+        <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="R5" t="n">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>252.3</v>
+        <v>384.63</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1094,17 +1090,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>73117950936864</t>
+          <t>BOCMORDEFMOR-15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MLM4537227786</t>
+          <t>MLM2109982307</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1114,16 +1110,16 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Soporte De Celular Para Carro Estabilizador De Teléfono Color Negro</t>
+          <t>Linterna Led Con Mini Sistema Solar Powerbank Con Radio Fm Default Title</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>84.09999999999999</v>
+        <v>384.63</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>82.81999999999999</v>
+        <v>218.04</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1132,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>41.64</v>
+        <v>55.77</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1140,28 +1136,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000015955581526</v>
+        <v>2000015971504642</v>
       </c>
       <c r="B6" t="n">
-        <v>2000012482766177</v>
+        <v>2000012499210501</v>
       </c>
       <c r="C6" t="n">
-        <v>46841978337</v>
+        <v>46849508631</v>
       </c>
       <c r="D6" t="n">
-        <v>154505410318</v>
+        <v>154659189258</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JOSTIMOTEOGUERREROCASTILLO</t>
+          <t>CAUICHCINTHIA20220209031051</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000015955581526</v>
+        <v>2000015971504642</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-12T21:32:57.000-04:00</t>
+          <t>2026-04-13T20:52:33.000-04:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1188,28 +1184,28 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1365</v>
+        <v>490</v>
       </c>
       <c r="N6" t="n">
-        <v>197.92</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>190</v>
+        <v>135.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1365</v>
+        <v>490</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1221,17 +1217,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>72591346859892</t>
+          <t>BOCMORNEG-385</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MLM2157132507</t>
+          <t>MLM2921918534</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1241,16 +1237,16 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>1365</v>
+        <v>490</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>948.52</v>
+        <v>329.05</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1259,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>197.92</v>
+        <v>49</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1267,28 +1263,28 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2000015955406042</v>
+        <v>2000015967426912</v>
       </c>
       <c r="B7" t="n">
-        <v>2000012482561253</v>
+        <v>2000012495048417</v>
       </c>
       <c r="C7" t="n">
-        <v>46842164894</v>
+        <v>46847634899</v>
       </c>
       <c r="D7" t="n">
-        <v>153755964839</v>
+        <v>153873400805</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YATZIRYZUBIA</t>
+          <t>IVAN.FERNIZA</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000015955406042</v>
+        <v>2000015967426912</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-12T21:18:30.000-04:00</t>
+          <t>2026-04-13T16:49:29.000-04:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1312,31 +1308,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>172.79</v>
+        <v>594</v>
       </c>
       <c r="N7" t="n">
-        <v>25.92</v>
+        <v>21.53</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>135.2</v>
+        <v>256</v>
       </c>
       <c r="Q7" t="n">
-        <v>67.59999999999999</v>
+        <v>128</v>
       </c>
       <c r="R7" t="n">
-        <v>67.59999999999999</v>
+        <v>128</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>172.79</v>
+        <v>594</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1348,17 +1344,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>72478699982948</t>
+          <t>73117897877509</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MLM2853107461</t>
+          <t>MLM3463460726</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1368,16 +1364,16 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Extensión Regleta Moreka Mc5447c 8 Tomas 2 Usb C Protección 2m Blanca Blanco</t>
+          <t>Transmisor Bluetooth Plug In Moreka Cp-0069 5.3 Fm Rgb Negro</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>172.79</v>
+        <v>148.5</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>63.63</v>
+        <v>326.11</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1386,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>25.92</v>
+        <v>86.12</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1394,28 +1390,26 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2000015955037638</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2000012482184957</v>
-      </c>
+        <v>2000015967261198</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>46841741585</v>
+        <v>46847563627</v>
       </c>
       <c r="D8" t="n">
-        <v>153753433147</v>
+        <v>154620927548</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ORNELASJONATHAN20230517180340</t>
+          <t>EUGENIOALCALDEMALAGON</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000015955037638</v>
+        <v>2000015967261198</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-12T20:54:10.000-04:00</t>
+          <t>2026-04-13T16:40:01.000-04:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1442,28 +1436,28 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>134.55</v>
+        <v>237.5</v>
       </c>
       <c r="N8" t="n">
-        <v>13.46</v>
+        <v>42.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>134.55</v>
+        <v>237.5</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1475,17 +1469,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1495,16 +1489,16 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>134.55</v>
+        <v>237.5</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>76.91</v>
+        <v>120.85</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1513,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>13.46</v>
+        <v>42.75</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1521,28 +1515,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2000015953863248</v>
+        <v>2000015966806636</v>
       </c>
       <c r="B9" t="n">
-        <v>2000012480954851</v>
+        <v>2000012494410425</v>
       </c>
       <c r="C9" t="n">
-        <v>46841512724</v>
+        <v>46847610806</v>
       </c>
       <c r="D9" t="n">
-        <v>154492811296</v>
+        <v>153866965385</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ALANROBLES896</t>
+          <t>LAX3848998</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2000015953863248</v>
+        <v>2000015966806636</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-12T19:36:07.000-04:00</t>
+          <t>2026-04-13T16:10:00.000-04:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1569,28 +1563,28 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="N9" t="n">
-        <v>13.46</v>
+        <v>49</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>64</v>
+        <v>135.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>32</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1602,12 +1596,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>BOCMORAZU-385</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3323904908</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1622,16 +1616,16 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Bocina Moreka 385 Bluetooth 20w Resistente Agua Ipx6 Tws Micrófono Llamadas Batería Larga Duración Portátil Azul</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>76.91</v>
+        <v>329.05</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1640,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>13.46</v>
+        <v>49</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1648,26 +1642,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000015953129652</v>
-      </c>
-      <c r="B10" t="inlineStr"/>
+        <v>2000015966540178</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2000012494141209</v>
+      </c>
       <c r="C10" t="n">
-        <v>46840936695</v>
+        <v>46847476728</v>
       </c>
       <c r="D10" t="n">
-        <v>153738745847</v>
+        <v>153864537735</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LUISEDUARDOJIMNEZCABRERA</t>
+          <t>AGSA7780883</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000015953129652</v>
+        <v>2000015966540178</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-12T18:47:14.000-04:00</t>
+          <t>2026-04-13T15:53:04.000-04:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1694,28 +1690,28 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>99.75</v>
+        <v>134.55</v>
       </c>
       <c r="N10" t="n">
-        <v>14.96</v>
+        <v>13.46</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="R10" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>99.75</v>
+        <v>134.55</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1727,12 +1723,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>CARMORDEFJB212AA-1</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MLM3357055624</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1747,16 +1743,16 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Pilas Recargables Aaa Jiabao 350mah Pack 10 Con Cargador Jb-212</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>99.75</v>
+        <v>134.55</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>37.76</v>
+        <v>76.91</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1765,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.96</v>
+        <v>13.46</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1773,36 +1769,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2000015952631620</v>
+        <v>2000015964352394</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>46840996916</v>
+        <v>46846133057</v>
       </c>
       <c r="D11" t="n">
-        <v>153734537841</v>
+        <v>154596734430</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MAAU5192905</t>
+          <t>ELY12173</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000015952631620</v>
+        <v>2000015964352394</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-12T18:12:34.000-04:00</t>
+          <t>2026-04-13T13:41:47.000-04:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1828,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="n">
-        <v>163.87</v>
+        <v>95</v>
       </c>
       <c r="R11" t="n">
-        <v>70.13</v>
+        <v>21</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1898,28 +1894,28 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2000015951746522</v>
+        <v>2000015963830458</v>
       </c>
       <c r="B12" t="n">
-        <v>2000012478741857</v>
+        <v>2000012491320325</v>
       </c>
       <c r="C12" t="n">
-        <v>46840326297</v>
+        <v>46846150786</v>
       </c>
       <c r="D12" t="n">
-        <v>153726813143</v>
+        <v>153843244079</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NATHALIALONZOVARGAS</t>
+          <t>DG20250909174409</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000015951746522</v>
+        <v>2000015963830458</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-12T17:02:23.000-04:00</t>
+          <t>2026-04-13T13:11:17.000-04:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1946,28 +1942,28 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>134.55</v>
+        <v>198.75</v>
       </c>
       <c r="N12" t="n">
-        <v>13.46</v>
+        <v>28.82</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>134.55</v>
+        <v>198.75</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1979,17 +1975,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1999,16 +1995,16 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>134.55</v>
+        <v>198.75</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>76.91</v>
+        <v>117.94</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2017,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>13.46</v>
+        <v>28.82</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2025,28 +2021,28 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2000015950193056</v>
+        <v>2000015962454644</v>
       </c>
       <c r="B13" t="n">
-        <v>2000012476881167</v>
+        <v>2000012489892605</v>
       </c>
       <c r="C13" t="n">
-        <v>46839927702</v>
+        <v>46845217691</v>
       </c>
       <c r="D13" t="n">
-        <v>154462576514</v>
+        <v>154579864696</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DUER9786335</t>
+          <t>GARCIAESTEBAN20230518153938</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2000015950193056</v>
+        <v>2000015962454644</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-12T15:02:47.000-04:00</t>
+          <t>2026-04-13T11:50:53.000-04:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2082,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="Q13" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2135,7 +2131,7 @@
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>108.91</v>
+        <v>76.91</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2152,28 +2148,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2000015950183992</v>
+        <v>2000015962146264</v>
       </c>
       <c r="B14" t="n">
-        <v>2000012476881167</v>
+        <v>2000012489579853</v>
       </c>
       <c r="C14" t="n">
-        <v>46839927702</v>
+        <v>46845070647</v>
       </c>
       <c r="D14" t="n">
-        <v>154462600152</v>
+        <v>154576785432</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DUER9786335</t>
+          <t>INEV9190937</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000015950183992</v>
+        <v>2000015962146264</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-12T15:02:47.000-04:00</t>
+          <t>2026-04-13T11:32:39.000-04:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2197,13 +2193,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>134.55</v>
+        <v>364</v>
       </c>
       <c r="N14" t="n">
-        <v>13.46</v>
+        <v>25.48</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2221,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>134.55</v>
+        <v>364</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2233,17 +2229,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>22187150-white-LAGOM</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM1582859464</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2253,16 +2249,16 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>134.55</v>
+        <v>182</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>44.91</v>
+        <v>216.1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2271,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>13.46</v>
+        <v>50.96</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2279,36 +2275,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2000015949142546</v>
-      </c>
-      <c r="B15" t="inlineStr"/>
+        <v>2000015958900598</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2000012486229035</v>
+      </c>
       <c r="C15" t="n">
-        <v>46839201507</v>
+        <v>46843756962</v>
       </c>
       <c r="D15" t="n">
-        <v>153706432727</v>
+        <v>154544707106</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>G20250531223627</t>
+          <t>INEV9190937</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000015949142546</v>
+        <v>2000015958900598</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-12T13:40:31.000-04:00</t>
+          <t>2026-04-13T07:55:09.000-04:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2322,31 +2320,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>204</v>
+        <v>364</v>
       </c>
       <c r="N15" t="n">
-        <v>33.66</v>
+        <v>25.48</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="Q15" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="R15" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>204</v>
+        <v>364</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2358,12 +2356,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>22187150-white-LAGOM</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM1582859464</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2378,16 +2376,16 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>116.87</v>
+        <v>216.1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2396,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>33.66</v>
+        <v>50.96</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2404,26 +2402,28 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2000015945008650</v>
-      </c>
-      <c r="B16" t="inlineStr"/>
+        <v>2000015957217578</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2000012484446139</v>
+      </c>
       <c r="C16" t="n">
-        <v>46837630090</v>
+        <v>46842931282</v>
       </c>
       <c r="D16" t="n">
-        <v>154412117972</v>
+        <v>153767839871</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TONO5981002</t>
+          <t>PIINCHEPERRO</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000015945008650</v>
+        <v>2000015957217578</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-12T05:17:26.000-04:00</t>
+          <t>2026-04-13T00:18:19.000-04:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2450,28 +2450,28 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="N16" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="Q16" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2503,16 +2503,16 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>76.91</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>13.46</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2529,28 +2529,28 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2000015944827404</v>
+        <v>2000015956925426</v>
       </c>
       <c r="B17" t="n">
-        <v>2000012471530373</v>
+        <v>2000012484147313</v>
       </c>
       <c r="C17" t="n">
-        <v>46837277205</v>
+        <v>46842537261</v>
       </c>
       <c r="D17" t="n">
-        <v>153662197883</v>
+        <v>153765643607</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JESSICAMIRTALADELENROA</t>
+          <t>REINAJUDTIHRAMREZ</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2000015944827404</v>
+        <v>2000015956925426</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-12T02:47:16.000-04:00</t>
+          <t>2026-04-12T23:36:15.000-04:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2586,13 +2586,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>76.27</v>
+        <v>70</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.27</v>
+        <v>35</v>
       </c>
       <c r="R17" t="n">
-        <v>34.99999999999999</v>
+        <v>35</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>BOCMORAZU405</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>110.6</v>
+        <v>116.87</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2656,26 +2656,28 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2000015944791160</v>
-      </c>
-      <c r="B18" t="inlineStr"/>
+        <v>2000015956767790</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2000012484002697</v>
+      </c>
       <c r="C18" t="n">
-        <v>46837546532</v>
+        <v>46846175374</v>
       </c>
       <c r="D18" t="n">
-        <v>153662234221</v>
+        <v>154512994416</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RA20241216152952</t>
+          <t>MM20250621175836</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000015944791160</v>
+        <v>2000015956767790</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-12T02:43:18.000-04:00</t>
+          <t>2026-04-12T23:21:24.000-04:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2702,28 +2704,28 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>202.65</v>
+        <v>490</v>
       </c>
       <c r="N18" t="n">
-        <v>33.44</v>
+        <v>49</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>87</v>
+        <v>135.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>125</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>38</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>202.65</v>
+        <v>490</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2735,17 +2737,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>PX-SJL9-BCN0</t>
+          <t>BOCMORNEG-385</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MLM2082055833</t>
+          <t>MLM2921918534</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2755,16 +2757,16 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>202.65</v>
+        <v>490</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>112.86</v>
+        <v>329.05</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2773,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>33.44</v>
+        <v>49</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2781,28 +2783,28 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000015944554586</v>
+        <v>2000015956605502</v>
       </c>
       <c r="B19" t="n">
-        <v>2000012471236369</v>
+        <v>2000012483808797</v>
       </c>
       <c r="C19" t="n">
-        <v>46837165917</v>
+        <v>46842403159</v>
       </c>
       <c r="D19" t="n">
-        <v>154406778626</v>
+        <v>154511573332</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JUANANGELDUEÑASRINCON</t>
+          <t>PEOR7869303</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2000015944554586</v>
+        <v>2000015956605502</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-12T01:07:15.000-04:00</t>
+          <t>2026-04-12T22:59:10.000-04:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2826,31 +2828,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>134.55</v>
+        <v>252.3</v>
       </c>
       <c r="N19" t="n">
-        <v>13.46</v>
+        <v>13.88</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>64</v>
+        <v>210</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="R19" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>134.55</v>
+        <v>252.3</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2862,12 +2864,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>73117950936864</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4537227786</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2882,16 +2884,16 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Soporte De Celular Para Carro Estabilizador De Teléfono Color Negro</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>134.55</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>76.91</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2900,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>13.46</v>
+        <v>41.64</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2908,38 +2910,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000015944520040</v>
+        <v>2000015955581526</v>
       </c>
       <c r="B20" t="n">
-        <v>2000012471190691</v>
+        <v>2000012482766177</v>
       </c>
       <c r="C20" t="n">
-        <v>46837150907</v>
+        <v>46841978337</v>
       </c>
       <c r="D20" t="n">
-        <v>153658671197</v>
+        <v>154505410318</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GUJU6869975</t>
+          <t>JOSTIMOTEOGUERREROCASTILLO</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000015944520040</v>
+        <v>2000015955581526</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-12T00:57:45.000-04:00</t>
+          <t>2026-04-12T21:32:57.000-04:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2956,10 +2958,10 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>886.34</v>
+        <v>1365</v>
       </c>
       <c r="N20" t="n">
-        <v>88.63</v>
+        <v>197.92</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2977,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>886.34</v>
+        <v>1365</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2989,17 +2991,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3009,16 +3011,16 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>886.34</v>
+        <v>1365</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>622.48</v>
+        <v>948.52</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3027,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>88.63</v>
+        <v>197.92</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3035,28 +3037,28 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2000015944439726</v>
+        <v>2000015955406042</v>
       </c>
       <c r="B21" t="n">
-        <v>2000012471123715</v>
+        <v>2000012482561253</v>
       </c>
       <c r="C21" t="n">
-        <v>46837123631</v>
+        <v>46842164894</v>
       </c>
       <c r="D21" t="n">
-        <v>154405486928</v>
+        <v>153755964839</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TAJU9721170</t>
+          <t>YATZIRYZUBIA</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2000015944439726</v>
+        <v>2000015955406042</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-12T00:41:22.000-04:00</t>
+          <t>2026-04-12T21:18:30.000-04:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3083,28 +3085,28 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>206.95</v>
+        <v>172.79</v>
       </c>
       <c r="N21" t="n">
-        <v>31.04</v>
+        <v>25.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>152</v>
+        <v>135.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>206.95</v>
+        <v>172.79</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3116,17 +3118,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Blanco K073</t>
+          <t>72478699982948</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MLM3129247568</t>
+          <t>MLM2853107461</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3136,16 +3138,16 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
+          <t>Extensión Regleta Moreka Mc5447c 8 Tomas 2 Usb C Protección 2m Blanca Blanco</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>206.95</v>
+        <v>172.79</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>157.18</v>
+        <v>63.63</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3154,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>31.04</v>
+        <v>25.92</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3162,28 +3164,28 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2000015944444922</v>
+        <v>2000015955037638</v>
       </c>
       <c r="B22" t="n">
-        <v>2000012471123715</v>
+        <v>2000012482184957</v>
       </c>
       <c r="C22" t="n">
-        <v>46837123631</v>
+        <v>46841741585</v>
       </c>
       <c r="D22" t="n">
-        <v>154405351746</v>
+        <v>153753433147</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TAJU9721170</t>
+          <t>ORNELASJONATHAN20230517180340</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000015944444922</v>
+        <v>2000015955037638</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-12T00:41:22.000-04:00</t>
+          <t>2026-04-12T20:54:10.000-04:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3210,28 +3212,28 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="N22" t="n">
-        <v>31.04</v>
+        <v>13.46</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="Q22" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="R22" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3243,17 +3245,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Azul K073</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>MLM3129247568</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3263,16 +3265,16 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>81.18000000000001</v>
+        <v>76.91</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3281,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>31.04</v>
+        <v>13.46</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3289,28 +3291,28 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2000015944248160</v>
+        <v>2000015953863248</v>
       </c>
       <c r="B23" t="n">
-        <v>2000012470820489</v>
+        <v>2000012480954851</v>
       </c>
       <c r="C23" t="n">
-        <v>46837041551</v>
+        <v>46841512724</v>
       </c>
       <c r="D23" t="n">
-        <v>154403287242</v>
+        <v>154492811296</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JUANCARLOSCARMONAALFARO</t>
+          <t>ALANROBLES896</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2000015944248160</v>
+        <v>2000015953863248</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-11T23:59:26.000-04:00</t>
+          <t>2026-04-12T19:36:07.000-04:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3337,28 +3339,28 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>204.71</v>
+        <v>134.55</v>
       </c>
       <c r="N23" t="n">
-        <v>29.68</v>
+        <v>13.46</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>105.46</v>
+        <v>64</v>
       </c>
       <c r="Q23" t="n">
-        <v>67.45999999999999</v>
+        <v>32</v>
       </c>
       <c r="R23" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>204.71</v>
+        <v>134.55</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -3370,17 +3372,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3390,16 +3392,16 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>204.71</v>
+        <v>134.55</v>
       </c>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
-        <v>89.04000000000001</v>
+        <v>76.91</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3408,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>29.68</v>
+        <v>13.46</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3416,28 +3418,26 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2000015942032840</v>
-      </c>
-      <c r="B24" t="n">
-        <v>2000012468587881</v>
-      </c>
+        <v>2000015953129652</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>46836369178</v>
+        <v>46840936695</v>
       </c>
       <c r="D24" t="n">
-        <v>154378603064</v>
+        <v>153738745847</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JOELLDJ</t>
+          <t>LUISEDUARDOJIMNEZCABRERA</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000015942032840</v>
+        <v>2000015953129652</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-11T19:53:08.000-04:00</t>
+          <t>2026-04-12T18:47:14.000-04:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3464,28 +3464,28 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>700</v>
+        <v>99.75</v>
       </c>
       <c r="N24" t="n">
-        <v>101.5</v>
+        <v>14.96</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="Q24" t="n">
-        <v>84.5</v>
+        <v>38</v>
       </c>
       <c r="R24" t="n">
-        <v>84.5</v>
+        <v>70</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>700</v>
+        <v>99.75</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>CARMORDEFJB212AA-1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MLM4388568286</t>
+          <t>MLM3357055624</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3517,16 +3517,16 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
+          <t>Pilas Recargables Aaa Jiabao 350mah Pack 10 Con Cargador Jb-212</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>700</v>
+        <v>99.75</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>450.63</v>
+        <v>37.76</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>101.5</v>
+        <v>14.96</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3543,26 +3543,26 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2000015941753476</v>
+        <v>2000015952631620</v>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>46836259542</v>
+        <v>46840996916</v>
       </c>
       <c r="D25" t="n">
-        <v>153627775865</v>
+        <v>153734537841</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NOYOLAIVAN20231112183250</t>
+          <t>MAAU5192905</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2000015941753476</v>
+        <v>2000015952631620</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-11T19:31:35.000-04:00</t>
+          <t>2026-04-12T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3589,28 +3589,28 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>189</v>
+        <v>886.34</v>
       </c>
       <c r="N25" t="n">
-        <v>31.18</v>
+        <v>88.63</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>163.87</v>
       </c>
       <c r="R25" t="n">
-        <v>77</v>
+        <v>70.13</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>189</v>
+        <v>886.34</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3622,17 +3622,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3642,16 +3642,16 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>189</v>
+        <v>886.34</v>
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>622.48</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>88.63</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3668,28 +3668,28 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2000015941686260</v>
+        <v>2000015951746522</v>
       </c>
       <c r="B26" t="n">
-        <v>2000012468221695</v>
+        <v>2000012478741857</v>
       </c>
       <c r="C26" t="n">
-        <v>46836215454</v>
+        <v>46840326297</v>
       </c>
       <c r="D26" t="n">
-        <v>154373847452</v>
+        <v>153726813143</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CAAN8167043</t>
+          <t>NATHALIALONZOVARGAS</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2000015941686260</v>
+        <v>2000015951746522</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-11T19:23:01.000-04:00</t>
+          <t>2026-04-12T17:02:23.000-04:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -3795,26 +3795,28 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2000015941054478</v>
-      </c>
-      <c r="B27" t="inlineStr"/>
+        <v>2000015950183992</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2000012476881167</v>
+      </c>
       <c r="C27" t="n">
-        <v>46835940590</v>
+        <v>46839927702</v>
       </c>
       <c r="D27" t="n">
-        <v>154365172508</v>
+        <v>154462600152</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>L20260220145454</t>
+          <t>DUER9786335</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2000015941054478</v>
+        <v>2000015950183992</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-11T18:29:38.000-04:00</t>
+          <t>2026-04-12T15:02:47.000-04:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3841,28 +3843,28 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="N27" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="Q27" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="R27" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3874,12 +3876,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3894,16 +3896,16 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>622.48</v>
+        <v>44.91</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3912,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3920,28 +3922,28 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2000015940863248</v>
+        <v>2000015950193056</v>
       </c>
       <c r="B28" t="n">
-        <v>2000012467360959</v>
+        <v>2000012476881167</v>
       </c>
       <c r="C28" t="n">
-        <v>46835581697</v>
+        <v>46839927702</v>
       </c>
       <c r="D28" t="n">
-        <v>154362231108</v>
+        <v>154462576514</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JOSMANUELHERNNDEZMRQUEZ</t>
+          <t>DUER9786335</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2000015940863248</v>
+        <v>2000015950193056</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-11T18:12:34.000-04:00</t>
+          <t>2026-04-12T15:02:47.000-04:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3965,31 +3967,31 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>4095</v>
+        <v>134.55</v>
       </c>
       <c r="N28" t="n">
-        <v>197.92</v>
+        <v>13.46</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>570</v>
+        <v>128</v>
       </c>
       <c r="Q28" t="n">
-        <v>285</v>
+        <v>64</v>
       </c>
       <c r="R28" t="n">
-        <v>285</v>
+        <v>64</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4095</v>
+        <v>134.55</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4001,17 +4003,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>72591346859892</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MLM2157132507</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4021,16 +4023,16 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>1365</v>
+        <v>134.55</v>
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>2845.58</v>
+        <v>108.91</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4039,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>593.76</v>
+        <v>13.46</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4047,26 +4049,26 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2000015935667022</v>
+        <v>2000015949142546</v>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>46833482066</v>
+        <v>46839201507</v>
       </c>
       <c r="D29" t="n">
-        <v>153550074671</v>
+        <v>153706432727</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MARCOPEMA</t>
+          <t>G20250531223627</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000015935667022</v>
+        <v>2000015949142546</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-11T10:56:27.000-04:00</t>
+          <t>2026-04-12T13:40:31.000-04:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4093,28 +4095,28 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>886.34</v>
+        <v>204</v>
       </c>
       <c r="N29" t="n">
-        <v>88.63</v>
+        <v>33.66</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="Q29" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="R29" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>886.34</v>
+        <v>204</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4126,17 +4128,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4146,16 +4148,16 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>886.34</v>
+        <v>204</v>
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>622.48</v>
+        <v>116.87</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4164,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>88.63</v>
+        <v>33.66</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4172,26 +4174,26 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2000015932827654</v>
+        <v>2000015945008650</v>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>46831838345</v>
+        <v>46837630090</v>
       </c>
       <c r="D30" t="n">
-        <v>154262740072</v>
+        <v>154412117972</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ROJASDAVID20210814233921</t>
+          <t>TONO5981002</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2000015932827654</v>
+        <v>2000015945008650</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-11T01:59:07.000-04:00</t>
+          <t>2026-04-12T05:17:26.000-04:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4227,13 +4229,13 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="Q30" t="n">
         <v>95</v>
       </c>
       <c r="R30" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -4297,28 +4299,28 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2000015932875024</v>
+        <v>2000015944827404</v>
       </c>
       <c r="B31" t="n">
-        <v>2000012459011895</v>
+        <v>2000012471530373</v>
       </c>
       <c r="C31" t="n">
-        <v>46831837021</v>
+        <v>46837277205</v>
       </c>
       <c r="D31" t="n">
-        <v>153516147611</v>
+        <v>153662197883</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LOAN2137132</t>
+          <t>JESSICAMIRTALADELENROA</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000015932875024</v>
+        <v>2000015944827404</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-11T01:57:33.000-04:00</t>
+          <t>2026-04-12T02:47:16.000-04:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4345,28 +4347,28 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>134.55</v>
+        <v>204</v>
       </c>
       <c r="N31" t="n">
-        <v>13.46</v>
+        <v>33.66</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>64</v>
+        <v>76.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>41.27</v>
       </c>
       <c r="R31" t="n">
-        <v>32</v>
+        <v>34.99999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>134.55</v>
+        <v>204</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4378,17 +4380,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BOCMORAZU405</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4398,16 +4400,16 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>134.55</v>
+        <v>204</v>
       </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>76.91</v>
+        <v>110.6</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4416,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>13.46</v>
+        <v>33.66</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4424,26 +4426,26 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2000015932632586</v>
+        <v>2000015944791160</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>46831736271</v>
+        <v>46837546532</v>
       </c>
       <c r="D32" t="n">
-        <v>153514027567</v>
+        <v>153662234221</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ERVINEDUARDO RAMÍREZVZLA</t>
+          <t>RA20241216152952</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2000015932632586</v>
+        <v>2000015944791160</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-11T00:54:31.000-04:00</t>
+          <t>2026-04-12T02:43:18.000-04:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4470,28 +4472,28 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>570.86</v>
+        <v>202.65</v>
       </c>
       <c r="N32" t="n">
-        <v>111.32</v>
+        <v>33.44</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="Q32" t="n">
-        <v>65.5</v>
+        <v>125</v>
       </c>
       <c r="R32" t="n">
-        <v>63.5</v>
+        <v>38</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>570.86</v>
+        <v>202.65</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4503,12 +4505,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>PX-SJL9-BCN0</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM2082055833</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4523,16 +4525,16 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>570.86</v>
+        <v>202.65</v>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>342.37</v>
+        <v>112.86</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4541,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>111.32</v>
+        <v>33.44</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4549,26 +4551,28 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2000015932009672</v>
-      </c>
-      <c r="B33" t="inlineStr"/>
+        <v>2000015944554586</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2000012471236369</v>
+      </c>
       <c r="C33" t="n">
-        <v>46831746812</v>
+        <v>46837165917</v>
       </c>
       <c r="D33" t="n">
-        <v>153507878875</v>
+        <v>154406778626</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PLER973318</t>
+          <t>JUANANGELDUEÑASRINCON</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000015932009672</v>
+        <v>2000015944554586</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-10T23:10:48.000-04:00</t>
+          <t>2026-04-12T01:07:15.000-04:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4595,28 +4599,28 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="N33" t="n">
-        <v>62.2</v>
+        <v>13.46</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="Q33" t="n">
-        <v>67.59999999999999</v>
+        <v>32</v>
       </c>
       <c r="R33" t="n">
-        <v>26.40000000000001</v>
+        <v>32</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -4628,17 +4632,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>76825709097220</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>MLM4762499328</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4648,16 +4652,16 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
-        <v>260.36</v>
+        <v>76.91</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4666,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>62.2</v>
+        <v>13.46</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4674,38 +4678,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2000015931967972</v>
+        <v>2000015944520040</v>
       </c>
       <c r="B34" t="n">
-        <v>2000012458078981</v>
+        <v>2000012471190691</v>
       </c>
       <c r="C34" t="n">
-        <v>46831734526</v>
+        <v>46837150907</v>
       </c>
       <c r="D34" t="n">
-        <v>154254282856</v>
+        <v>153658671197</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HECTORPETITHECTORPETIT</t>
+          <t>GUJU6869975</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2000015931967972</v>
+        <v>2000015944520040</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-10T23:07:11.000-04:00</t>
+          <t>2026-04-12T00:57:45.000-04:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4722,28 +4726,28 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="N34" t="n">
-        <v>120.01</v>
+        <v>88.63</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="Q34" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="R34" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -4755,17 +4759,17 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>76532580917858</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MLM4545490694</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4775,16 +4779,16 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>548.21</v>
+        <v>622.48</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4793,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>120.01</v>
+        <v>88.63</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4801,28 +4805,28 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2000015931930082</v>
+        <v>2000015944444922</v>
       </c>
       <c r="B35" t="n">
-        <v>2000012457998119</v>
+        <v>2000012471123715</v>
       </c>
       <c r="C35" t="n">
-        <v>46831420445</v>
+        <v>46837123631</v>
       </c>
       <c r="D35" t="n">
-        <v>154253338188</v>
+        <v>154405351746</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CARLOSALFONZ</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2000015931930082</v>
+        <v>2000015944444922</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-10T22:55:27.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4849,28 +4853,28 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>3158.4</v>
+        <v>206.95</v>
       </c>
       <c r="N35" t="n">
-        <v>457.97</v>
+        <v>31.04</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="Q35" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="R35" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3158.4</v>
+        <v>206.95</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4882,12 +4886,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>76867668365155</t>
+          <t>Azul K073</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MLM4762499740</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4902,16 +4906,16 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>3158.4</v>
+        <v>206.95</v>
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>2319.54</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4920,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>457.97</v>
+        <v>31.04</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -4928,28 +4932,28 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2000015931187904</v>
+        <v>2000015944439726</v>
       </c>
       <c r="B36" t="n">
-        <v>2000012457258861</v>
+        <v>2000012471123715</v>
       </c>
       <c r="C36" t="n">
-        <v>46831390290</v>
+        <v>46837123631</v>
       </c>
       <c r="D36" t="n">
-        <v>154246400496</v>
+        <v>154405486928</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PEÑAHERNAN20221106222959</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2000015931187904</v>
+        <v>2000015944439726</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-10T21:46:13.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4976,28 +4980,28 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="N36" t="n">
-        <v>92.53</v>
+        <v>31.04</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="Q36" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="R36" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5009,17 +5013,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>Blanco K073</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5029,16 +5033,16 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>925.3</v>
+        <v>206.95</v>
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>654.02</v>
+        <v>157.18</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5047,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>92.53</v>
+        <v>31.04</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5055,36 +5059,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2000015930234104</v>
-      </c>
-      <c r="B37" t="inlineStr"/>
+        <v>2000015944248160</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2000012470820489</v>
+      </c>
       <c r="C37" t="n">
-        <v>46830673091</v>
+        <v>46837041551</v>
       </c>
       <c r="D37" t="n">
-        <v>153488743041</v>
+        <v>154403287242</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BOAL6432084</t>
+          <t>JUANCARLOSCARMONAALFARO</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2000015930234104</v>
+        <v>2000015944248160</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-10T20:22:43.000-04:00</t>
+          <t>2026-04-11T23:59:26.000-04:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5101,28 +5107,28 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>285</v>
+        <v>204.71</v>
       </c>
       <c r="N37" t="n">
-        <v>55.58</v>
+        <v>29.68</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>98</v>
+        <v>105.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>285</v>
+        <v>204.71</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5134,12 +5140,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>77343215226889</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>MLM5098643766</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5154,16 +5160,16 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>285</v>
+        <v>204.71</v>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>164.62</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5172,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>55.58</v>
+        <v>29.68</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5180,28 +5186,28 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2000015929551932</v>
+        <v>2000015942032840</v>
       </c>
       <c r="B38" t="n">
-        <v>2000012455537231</v>
+        <v>2000012468587881</v>
       </c>
       <c r="C38" t="n">
-        <v>46830373077</v>
+        <v>46836369178</v>
       </c>
       <c r="D38" t="n">
-        <v>153480488965</v>
+        <v>154378603064</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SOPORIESLAVERGAZONA817</t>
+          <t>JOELLDJ</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2000015929551932</v>
+        <v>2000015942032840</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-10T19:30:38.000-04:00</t>
+          <t>2026-04-11T19:53:08.000-04:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5228,28 +5234,28 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>795.24</v>
+        <v>700</v>
       </c>
       <c r="N38" t="n">
-        <v>115.31</v>
+        <v>101.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>445</v>
+        <v>169</v>
       </c>
       <c r="Q38" t="n">
-        <v>222.5</v>
+        <v>84.5</v>
       </c>
       <c r="R38" t="n">
-        <v>222.5</v>
+        <v>84.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>795.24</v>
+        <v>700</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5261,17 +5267,17 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>76825905347021</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>MLM4762473244</t>
+          <t>MLM4388568286</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5281,16 +5287,16 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
+          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>795.24</v>
+        <v>700</v>
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>385.45</v>
+        <v>450.63</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5299,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>115.31</v>
+        <v>101.5</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5307,28 +5313,26 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2000015929481304</v>
-      </c>
-      <c r="B39" t="n">
-        <v>2000012455454135</v>
-      </c>
+        <v>2000015941753476</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>46830337829</v>
+        <v>46836259542</v>
       </c>
       <c r="D39" t="n">
-        <v>154225963480</v>
+        <v>153627775865</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VALERIAMARIASADAGARZA</t>
+          <t>NOYOLAIVAN20231112183250</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2000015929481304</v>
+        <v>2000015941753476</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-10T19:24:38.000-04:00</t>
+          <t>2026-04-11T19:31:35.000-04:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5355,28 +5359,28 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="N39" t="n">
-        <v>42.75</v>
+        <v>31.18</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>104.8</v>
+        <v>109</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.4</v>
+        <v>32</v>
       </c>
       <c r="R39" t="n">
-        <v>52.4</v>
+        <v>77</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -5388,12 +5392,12 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5408,16 +5412,16 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>237.5</v>
+        <v>189</v>
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>120.85</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5426,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>42.75</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5434,28 +5438,28 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2000015927409710</v>
+        <v>2000015941686260</v>
       </c>
       <c r="B40" t="n">
-        <v>2000012453315257</v>
+        <v>2000012468221695</v>
       </c>
       <c r="C40" t="n">
-        <v>46829644948</v>
+        <v>46836215454</v>
       </c>
       <c r="D40" t="n">
-        <v>154195281014</v>
+        <v>154373847452</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BIOTECVO</t>
+          <t>CAAN8167043</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2000015927409710</v>
+        <v>2000015941686260</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-10T16:40:07.000-04:00</t>
+          <t>2026-04-11T19:23:01.000-04:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5479,31 +5483,31 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>475</v>
+        <v>134.55</v>
       </c>
       <c r="N40" t="n">
-        <v>42.75</v>
+        <v>13.46</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>209.6</v>
+        <v>64</v>
       </c>
       <c r="Q40" t="n">
-        <v>104.8</v>
+        <v>32</v>
       </c>
       <c r="R40" t="n">
-        <v>104.8</v>
+        <v>32</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>475</v>
+        <v>134.55</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -5515,17 +5519,17 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5535,16 +5539,16 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>237.5</v>
+        <v>134.55</v>
       </c>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>241.7</v>
+        <v>76.91</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5553,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>85.5</v>
+        <v>13.46</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5561,26 +5565,26 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2000015926465502</v>
+        <v>2000015941054478</v>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>46828912925</v>
+        <v>46835940590</v>
       </c>
       <c r="D41" t="n">
-        <v>154183216410</v>
+        <v>154365172508</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JACOBOMIGUEL20230130120239</t>
+          <t>L20260220145454</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2000015926465502</v>
+        <v>2000015941054478</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-10T15:28:10.000-04:00</t>
+          <t>2026-04-11T18:29:38.000-04:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5607,28 +5611,28 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>109.8</v>
+        <v>886.34</v>
       </c>
       <c r="N41" t="n">
-        <v>13.18</v>
+        <v>88.63</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="R41" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>109.8</v>
+        <v>886.34</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -5640,12 +5644,12 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>SOPMORDEFMH-70B</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>MLM3357068774</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5660,16 +5664,16 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>109.8</v>
+        <v>886.34</v>
       </c>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
-        <v>46.68</v>
+        <v>622.48</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5678,7 +5682,7 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>13.18</v>
+        <v>88.63</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5686,26 +5690,28 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2000015925898954</v>
-      </c>
-      <c r="B42" t="inlineStr"/>
+        <v>2000015940863248</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2000012467360959</v>
+      </c>
       <c r="C42" t="n">
-        <v>46828618943</v>
+        <v>46835581697</v>
       </c>
       <c r="D42" t="n">
-        <v>154176812930</v>
+        <v>154362231108</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MEDINAVIANEY20220808095244</t>
+          <t>JOSMANUELHERNNDEZMRQUEZ</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2000015925898954</v>
+        <v>2000015940863248</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-10T14:44:48.000-04:00</t>
+          <t>2026-04-11T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5729,31 +5735,31 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>122</v>
+        <v>4095</v>
       </c>
       <c r="N42" t="n">
-        <v>12.2</v>
+        <v>197.92</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>89</v>
+        <v>570</v>
       </c>
       <c r="Q42" t="n">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="R42" t="n">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>122</v>
+        <v>4095</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -5765,17 +5771,17 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>76126320655919</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MLM4676748386</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5785,16 +5791,16 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>122</v>
+        <v>1365</v>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2845.58</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -5803,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>593.76</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5811,28 +5817,26 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2000015925292404</v>
-      </c>
-      <c r="B43" t="n">
-        <v>2000012451099821</v>
-      </c>
+        <v>2000015935667022</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>46828589732</v>
+        <v>46833482066</v>
       </c>
       <c r="D43" t="n">
-        <v>154170422818</v>
+        <v>153550074671</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VECE1241164</t>
+          <t>MARCOPEMA</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2000015925292404</v>
+        <v>2000015935667022</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-10T14:00:29.000-04:00</t>
+          <t>2026-04-11T10:56:27.000-04:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5859,28 +5863,28 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="N43" t="n">
-        <v>92.53</v>
+        <v>88.63</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="Q43" t="n">
         <v>95</v>
       </c>
       <c r="R43" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -5917,11 +5921,11 @@
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
-        <v>654.02</v>
+        <v>622.48</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -5930,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>92.53</v>
+        <v>88.63</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -5938,28 +5942,26 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2000015924881136</v>
-      </c>
-      <c r="B44" t="n">
-        <v>2000012450675355</v>
-      </c>
+        <v>2000015932827654</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>46828113793</v>
+        <v>46831838345</v>
       </c>
       <c r="D44" t="n">
-        <v>154166302560</v>
+        <v>154262740072</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>ROJASDAVID20210814233921</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2000015924881136</v>
+        <v>2000015932827654</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-11T01:59:07.000-04:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5986,28 +5988,28 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="N44" t="n">
-        <v>22.8</v>
+        <v>88.63</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>285.52</v>
+        <v>125</v>
       </c>
       <c r="Q44" t="n">
-        <v>189.52</v>
+        <v>95</v>
       </c>
       <c r="R44" t="n">
-        <v>95.99999999999997</v>
+        <v>30</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6019,17 +6021,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>BOCMORROSMOR-410</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -6039,16 +6041,16 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>228</v>
+        <v>886.34</v>
       </c>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
-        <v>184.57</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6057,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6065,28 +6067,28 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2000015924881134</v>
+        <v>2000015932875024</v>
       </c>
       <c r="B45" t="n">
-        <v>2000012450675355</v>
+        <v>2000012459011895</v>
       </c>
       <c r="C45" t="n">
-        <v>46828113793</v>
+        <v>46831837021</v>
       </c>
       <c r="D45" t="n">
-        <v>153420099615</v>
+        <v>153516147611</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>LOAN2137132</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2000015924881134</v>
+        <v>2000015932875024</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-11T01:57:33.000-04:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6113,28 +6115,28 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>228</v>
+        <v>134.55</v>
       </c>
       <c r="N45" t="n">
-        <v>22.8</v>
+        <v>13.46</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>285.52</v>
+        <v>64</v>
       </c>
       <c r="Q45" t="n">
-        <v>189.52</v>
+        <v>32</v>
       </c>
       <c r="R45" t="n">
-        <v>95.99999999999997</v>
+        <v>32</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>228</v>
+        <v>134.55</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6146,17 +6148,17 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>BOCMORAZUMOR-410</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -6166,16 +6168,16 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>228</v>
+        <v>134.55</v>
       </c>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>184.57</v>
+        <v>76.91</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6184,7 +6186,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>22.8</v>
+        <v>13.46</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6192,26 +6194,26 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2000015923571686</v>
+        <v>2000015932632586</v>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>46827760364</v>
+        <v>46831736271</v>
       </c>
       <c r="D46" t="n">
-        <v>153405868355</v>
+        <v>153514027567</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>VAZQUEZSARA20230812202049</t>
+          <t>ERVINEDUARDO RAMÍREZVZLA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2000015923571686</v>
+        <v>2000015932632586</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-10T11:59:16.000-04:00</t>
+          <t>2026-04-11T00:54:31.000-04:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6238,28 +6240,28 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>185</v>
+        <v>570.86</v>
       </c>
       <c r="N46" t="n">
-        <v>27.75</v>
+        <v>111.32</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="Q46" t="n">
-        <v>38</v>
+        <v>65.5</v>
       </c>
       <c r="R46" t="n">
-        <v>45</v>
+        <v>63.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>185</v>
+        <v>570.86</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -6271,17 +6273,17 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>MULMORNEGmc-5848c</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>MLM3357041104</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6291,16 +6293,16 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>185</v>
+        <v>570.86</v>
       </c>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>102.5</v>
+        <v>342.37</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6309,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>27.75</v>
+        <v>111.32</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6317,28 +6319,26 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000015922863610</v>
-      </c>
-      <c r="B47" t="n">
-        <v>2000012448562543</v>
-      </c>
+        <v>2000015932009672</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>46827137585</v>
+        <v>46831746812</v>
       </c>
       <c r="D47" t="n">
-        <v>153396288659</v>
+        <v>153507878875</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JORFERK</t>
+          <t>PLER973318</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2000015922863610</v>
+        <v>2000015932009672</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-10T11:07:52.000-04:00</t>
+          <t>2026-04-10T23:10:48.000-04:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6365,28 +6365,28 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>713</v>
+        <v>429</v>
       </c>
       <c r="N47" t="n">
-        <v>103.38</v>
+        <v>62.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="Q47" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R47" t="n">
-        <v>84.5</v>
+        <v>26.40000000000001</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>713</v>
+        <v>429</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -6398,12 +6398,12 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>73239381698389</t>
+          <t>76825709097220</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MLM3488449480</t>
+          <t>MLM4762499328</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -6418,16 +6418,16 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
+          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>713</v>
+        <v>429</v>
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>460.58</v>
+        <v>260.36</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>103.38</v>
+        <v>62.2</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6444,28 +6444,28 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2000015921193538</v>
+        <v>2000015931967972</v>
       </c>
       <c r="B48" t="n">
-        <v>2000012426900403</v>
+        <v>2000012458078981</v>
       </c>
       <c r="C48" t="n">
-        <v>46826592416</v>
+        <v>46831734526</v>
       </c>
       <c r="D48" t="n">
-        <v>153376320777</v>
+        <v>154254282856</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ALONDRAVIZUET</t>
+          <t>HECTORPETITHECTORPETIT</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2000015921193538</v>
+        <v>2000015931967972</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-10T09:05:19.000-04:00</t>
+          <t>2026-04-10T23:07:11.000-04:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6492,28 +6492,28 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>954</v>
+        <v>827.64</v>
       </c>
       <c r="N48" t="n">
-        <v>138.33</v>
+        <v>120.01</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="Q48" t="n">
-        <v>95</v>
+        <v>84.5</v>
       </c>
       <c r="R48" t="n">
-        <v>95</v>
+        <v>84.5</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>954</v>
+        <v>827.64</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>76825869750536</t>
+          <t>76532580917858</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MLM4762485780</t>
+          <t>MLM4545490694</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6545,16 +6545,16 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
+          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>954</v>
+        <v>827.64</v>
       </c>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>634.3200000000001</v>
+        <v>548.21</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>138.33</v>
+        <v>120.01</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6571,28 +6571,28 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2000015920405788</v>
+        <v>2000015931930082</v>
       </c>
       <c r="B49" t="n">
-        <v>2000012446018577</v>
+        <v>2000012457998119</v>
       </c>
       <c r="C49" t="n">
-        <v>46825928963</v>
+        <v>46831420445</v>
       </c>
       <c r="D49" t="n">
-        <v>154112621330</v>
+        <v>154253338188</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RODIBERTOROBLESALEJANDRO</t>
+          <t>CARLOSALFONZ</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2000015920405788</v>
+        <v>2000015931930082</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-10T07:55:11.000-04:00</t>
+          <t>2026-04-10T22:55:27.000-04:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6619,28 +6619,28 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>462</v>
+        <v>3158.4</v>
       </c>
       <c r="N49" t="n">
-        <v>66.98999999999999</v>
+        <v>457.97</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>119.2</v>
+        <v>190</v>
       </c>
       <c r="Q49" t="n">
-        <v>59.6</v>
+        <v>95</v>
       </c>
       <c r="R49" t="n">
-        <v>59.6</v>
+        <v>95</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>462</v>
+        <v>3158.4</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>76867668365155</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MLM2381238905</t>
+          <t>MLM4762499740</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6672,16 +6672,16 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
+          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>462</v>
+        <v>3158.4</v>
       </c>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>293.59</v>
+        <v>2319.54</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>66.98999999999999</v>
+        <v>457.97</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6698,28 +6698,28 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2000015919255616</v>
+        <v>2000015931187904</v>
       </c>
       <c r="B50" t="n">
-        <v>2000012444792845</v>
+        <v>2000012457258861</v>
       </c>
       <c r="C50" t="n">
-        <v>46825583586</v>
+        <v>46831390290</v>
       </c>
       <c r="D50" t="n">
-        <v>153344481991</v>
+        <v>154246400496</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MARTHACANDELARIALOPEZCORDOVA</t>
+          <t>PEÑAHERNAN20221106222959</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2000015919255616</v>
+        <v>2000015931187904</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-10T02:48:35.000-04:00</t>
+          <t>2026-04-10T21:46:13.000-04:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6746,28 +6746,28 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="N50" t="n">
-        <v>29.68</v>
+        <v>92.53</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="Q50" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="R50" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -6779,17 +6779,17 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>BR-KZNU-9NOO</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6799,16 +6799,16 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>100.5</v>
+        <v>654.02</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>29.68</v>
+        <v>92.53</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6825,36 +6825,36 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2000015918864062</v>
+        <v>2000015930234104</v>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>46825132377</v>
+        <v>46830673091</v>
       </c>
       <c r="D51" t="n">
-        <v>154084595658</v>
+        <v>153488743041</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ALEJANDRO3654</t>
+          <t>BOAL6432084</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2000015918864062</v>
+        <v>2000015930234104</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-10T00:54:13.000-04:00</t>
+          <t>2026-04-10T20:22:43.000-04:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6871,28 +6871,28 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>198.75</v>
+        <v>285</v>
       </c>
       <c r="N51" t="n">
-        <v>28.82</v>
+        <v>55.58</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R51" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>198.75</v>
+        <v>285</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -6904,12 +6904,12 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>77343215226889</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM5098643766</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -6924,16 +6924,16 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>198.75</v>
+        <v>285</v>
       </c>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>117.94</v>
+        <v>164.62</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>28.82</v>
+        <v>55.58</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -6950,28 +6950,28 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2000015918735504</v>
+        <v>2000015929551932</v>
       </c>
       <c r="B52" t="n">
-        <v>2000012444242337</v>
+        <v>2000012455537231</v>
       </c>
       <c r="C52" t="n">
-        <v>46825081431</v>
+        <v>46830373077</v>
       </c>
       <c r="D52" t="n">
-        <v>154083285822</v>
+        <v>153480488965</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JLPACHECOS</t>
+          <t>SOPORIESLAVERGAZONA817</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2000015918735504</v>
+        <v>2000015929551932</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-10T00:31:16.000-04:00</t>
+          <t>2026-04-10T19:30:38.000-04:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6998,28 +6998,28 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>427.5</v>
+        <v>795.24</v>
       </c>
       <c r="N52" t="n">
-        <v>64.12</v>
+        <v>115.31</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>135.2</v>
+        <v>445</v>
       </c>
       <c r="Q52" t="n">
-        <v>67.59999999999999</v>
+        <v>222.5</v>
       </c>
       <c r="R52" t="n">
-        <v>67.59999999999999</v>
+        <v>222.5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>427.5</v>
+        <v>795.24</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>A18/A38</t>
+          <t>76825905347021</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MLM3442935972</t>
+          <t>MLM4762473244</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7051,16 +7051,16 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>427.5</v>
+        <v>795.24</v>
       </c>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="n">
-        <v>257.09</v>
+        <v>385.45</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>64.12</v>
+        <v>115.31</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7077,28 +7077,28 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2000015918564930</v>
+        <v>2000015929481304</v>
       </c>
       <c r="B53" t="n">
-        <v>2000012444063601</v>
+        <v>2000012455454135</v>
       </c>
       <c r="C53" t="n">
-        <v>46825008245</v>
+        <v>46830337829</v>
       </c>
       <c r="D53" t="n">
-        <v>154081820206</v>
+        <v>154225963480</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OSCARCOLOTL</t>
+          <t>VALERIAMARIASADAGARZA</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2000015918564930</v>
+        <v>2000015929481304</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-10T00:03:34.000-04:00</t>
+          <t>2026-04-10T19:24:38.000-04:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7125,28 +7125,28 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="N53" t="n">
-        <v>16.44</v>
+        <v>42.75</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>64</v>
+        <v>104.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="R53" t="n">
-        <v>32</v>
+        <v>52.4</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -7158,17 +7158,17 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -7178,16 +7178,16 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>164.45</v>
+        <v>237.5</v>
       </c>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="n">
-        <v>101.13</v>
+        <v>120.85</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
@@ -7196,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>16.44</v>
+        <v>42.75</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7204,28 +7204,28 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2000015915026216</v>
+        <v>2000015927409710</v>
       </c>
       <c r="B54" t="n">
-        <v>2000012440383505</v>
+        <v>2000012453315257</v>
       </c>
       <c r="C54" t="n">
-        <v>46823711622</v>
+        <v>46829644948</v>
       </c>
       <c r="D54" t="n">
-        <v>154052836286</v>
+        <v>154195281014</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAKE9550997</t>
+          <t>BIOTECVO</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2000015915026216</v>
+        <v>2000015927409710</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-09T19:18:46.000-04:00</t>
+          <t>2026-04-10T16:40:07.000-04:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7249,31 +7249,31 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>234</v>
+        <v>475</v>
       </c>
       <c r="N54" t="n">
-        <v>23.4</v>
+        <v>42.75</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>275</v>
+        <v>209.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>221</v>
+        <v>104.8</v>
       </c>
       <c r="R54" t="n">
-        <v>54</v>
+        <v>104.8</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>234</v>
+        <v>475</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -7285,12 +7285,12 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>75045745678283</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MLM3813363284</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7305,16 +7305,16 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>234</v>
+        <v>237.5</v>
       </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="n">
-        <v>189.42</v>
+        <v>241.7</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>23.4</v>
+        <v>85.5</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7331,26 +7331,26 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2000015914539400</v>
+        <v>2000015926465502</v>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>46823497086</v>
+        <v>46828912925</v>
       </c>
       <c r="D55" t="n">
-        <v>153301992033</v>
+        <v>154183216410</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>VNUSROJIBLANK12</t>
+          <t>JACOBOMIGUEL20230130120239</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2000015914539400</v>
+        <v>2000015926465502</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-09T18:47:34.000-04:00</t>
+          <t>2026-04-10T15:28:10.000-04:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7377,28 +7377,28 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>713</v>
+        <v>109.8</v>
       </c>
       <c r="N55" t="n">
-        <v>103.38</v>
+        <v>13.18</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="Q55" t="n">
-        <v>84.5</v>
+        <v>40</v>
       </c>
       <c r="R55" t="n">
-        <v>41.5</v>
+        <v>62</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>713</v>
+        <v>109.8</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -7410,17 +7410,17 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>73239400752399</t>
+          <t>SOPMORDEFMH-70B</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>MLM3488485454</t>
+          <t>MLM3357068774</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7430,16 +7430,16 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>713</v>
+        <v>109.8</v>
       </c>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="n">
-        <v>460.58</v>
+        <v>46.68</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>103.38</v>
+        <v>13.18</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7456,28 +7456,26 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2000015914254952</v>
-      </c>
-      <c r="B56" t="n">
-        <v>2000012439581533</v>
-      </c>
+        <v>2000015925898954</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>46823083335</v>
+        <v>46828618943</v>
       </c>
       <c r="D56" t="n">
-        <v>153298477411</v>
+        <v>154176812930</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GA20240622001650</t>
+          <t>MEDINAVIANEY20220808095244</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2000015914254952</v>
+        <v>2000015925898954</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-09T18:26:50.000-04:00</t>
+          <t>2026-04-10T14:44:48.000-04:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7501,31 +7499,31 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>322</v>
+        <v>122</v>
       </c>
       <c r="N56" t="n">
-        <v>31.4</v>
+        <v>12.2</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="Q56" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="R56" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>322</v>
+        <v>122</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -7537,12 +7535,12 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>72141399181305</t>
+          <t>76126320655919</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>MLM2289340133</t>
+          <t>MLM4676748386</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -7557,16 +7555,16 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="n">
-        <v>150.05</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -7575,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>62.8</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7583,28 +7581,28 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2000015913353944</v>
+        <v>2000015925292404</v>
       </c>
       <c r="B57" t="n">
-        <v>2000012438644843</v>
+        <v>2000012451099821</v>
       </c>
       <c r="C57" t="n">
-        <v>46822944206</v>
+        <v>46828589732</v>
       </c>
       <c r="D57" t="n">
-        <v>153287496709</v>
+        <v>154170422818</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ESCI899332</t>
+          <t>VECE1241164</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2000015913353944</v>
+        <v>2000015925292404</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-09T17:23:20.000-04:00</t>
+          <t>2026-04-10T14:00:29.000-04:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7631,28 +7629,28 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>164.45</v>
+        <v>925.3</v>
       </c>
       <c r="N57" t="n">
-        <v>16.44</v>
+        <v>92.53</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R57" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>164.45</v>
+        <v>925.3</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -7664,12 +7662,12 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -7684,16 +7682,16 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>164.45</v>
+        <v>925.3</v>
       </c>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="n">
-        <v>101.13</v>
+        <v>654.02</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
@@ -7702,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>16.44</v>
+        <v>92.53</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7710,28 +7708,28 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2000015911947456</v>
+        <v>2000015924881136</v>
       </c>
       <c r="B58" t="n">
-        <v>2000012437174517</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C58" t="n">
-        <v>46822254216</v>
+        <v>46828113793</v>
       </c>
       <c r="D58" t="n">
-        <v>154016462860</v>
+        <v>154166302560</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2000015911947456</v>
+        <v>2000015924881136</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7758,28 +7756,28 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="N58" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>152</v>
+        <v>285.52</v>
       </c>
       <c r="Q58" t="n">
-        <v>76</v>
+        <v>189.52</v>
       </c>
       <c r="R58" t="n">
-        <v>76</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -7791,12 +7789,12 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>76720994758426</t>
+          <t>BOCMORROSMOR-410</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>MLM5115426106</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -7811,16 +7809,16 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="n">
-        <v>225.14</v>
+        <v>184.57</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -7829,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7837,28 +7835,28 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2000015911947458</v>
+        <v>2000015924881134</v>
       </c>
       <c r="B59" t="n">
-        <v>2000012437174517</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C59" t="n">
-        <v>46822254216</v>
+        <v>46828113793</v>
       </c>
       <c r="D59" t="n">
-        <v>154016435366</v>
+        <v>153420099615</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2000015911947458</v>
+        <v>2000015924881134</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7885,28 +7883,28 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="N59" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>152</v>
+        <v>285.52</v>
       </c>
       <c r="Q59" t="n">
-        <v>76</v>
+        <v>189.52</v>
       </c>
       <c r="R59" t="n">
-        <v>76</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -7918,17 +7916,17 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>AUDMORNEGM-921pack</t>
+          <t>BOCMORAZUMOR-410</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MLM3356978052</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -7938,16 +7936,16 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>294.5</v>
+        <v>228</v>
       </c>
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="n">
-        <v>149.14</v>
+        <v>184.57</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -7956,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>42.7</v>
+        <v>22.8</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -7964,28 +7962,26 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2000015911035950</v>
-      </c>
-      <c r="B60" t="n">
-        <v>2000012436224727</v>
-      </c>
+        <v>2000015923571686</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>46821806098</v>
+        <v>46827760364</v>
       </c>
       <c r="D60" t="n">
-        <v>154008453720</v>
+        <v>153405868355</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HLALTAMIRANO</t>
+          <t>VAZQUEZSARA20230812202049</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2000015911035950</v>
+        <v>2000015923571686</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-09T14:44:05.000-04:00</t>
+          <t>2026-04-10T11:59:16.000-04:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8012,28 +8008,28 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>560.5</v>
+        <v>185</v>
       </c>
       <c r="N60" t="n">
-        <v>109.3</v>
+        <v>27.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="Q60" t="n">
-        <v>65.5</v>
+        <v>38</v>
       </c>
       <c r="R60" t="n">
-        <v>65.5</v>
+        <v>45</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>560.5</v>
+        <v>185</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8045,17 +8041,17 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>MULMORNEGmc-5848c</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM3357041104</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -8065,16 +8061,16 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>560.5</v>
+        <v>185</v>
       </c>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="n">
-        <v>334.96</v>
+        <v>102.5</v>
       </c>
       <c r="AF60" t="n">
         <v>0</v>
@@ -8083,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>109.3</v>
+        <v>27.75</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8091,26 +8087,28 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2000015910487320</v>
-      </c>
-      <c r="B61" t="inlineStr"/>
+        <v>2000015922863610</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2000012448562543</v>
+      </c>
       <c r="C61" t="n">
-        <v>46821271897</v>
+        <v>46827137585</v>
       </c>
       <c r="D61" t="n">
-        <v>153258785401</v>
+        <v>153396288659</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ENLACESS</t>
+          <t>JORFERK</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2000015910487320</v>
+        <v>2000015922863610</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-09T14:10:04.000-04:00</t>
+          <t>2026-04-10T11:07:52.000-04:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8137,28 +8135,28 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>134.55</v>
+        <v>713</v>
       </c>
       <c r="N61" t="n">
-        <v>13.46</v>
+        <v>103.38</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="Q61" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="R61" t="n">
-        <v>67</v>
+        <v>84.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>134.55</v>
+        <v>713</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -8170,17 +8168,17 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>73239381698389</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3488449480</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -8190,16 +8188,16 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>134.55</v>
+        <v>713</v>
       </c>
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="n">
-        <v>76.91</v>
+        <v>460.58</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -8208,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>13.46</v>
+        <v>103.38</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8216,28 +8214,28 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2000015909133456</v>
+        <v>2000015921193538</v>
       </c>
       <c r="B62" t="n">
-        <v>2000012434212221</v>
+        <v>2000012426900403</v>
       </c>
       <c r="C62" t="n">
-        <v>46820912508</v>
+        <v>46826592416</v>
       </c>
       <c r="D62" t="n">
-        <v>153993729394</v>
+        <v>153376320777</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ULY5205</t>
+          <t>ALONDRAVIZUET</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2000015909133456</v>
+        <v>2000015921193538</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-09T12:45:26.000-04:00</t>
+          <t>2026-04-10T09:05:19.000-04:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8264,28 +8262,28 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>189</v>
+        <v>954</v>
       </c>
       <c r="N62" t="n">
-        <v>31.18</v>
+        <v>138.33</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="Q62" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="R62" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>189</v>
+        <v>954</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -8297,12 +8295,12 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>BOCMORROK405</t>
+          <t>76825869750536</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM4762485780</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -8317,16 +8315,16 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>189</v>
+        <v>954</v>
       </c>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="n">
-        <v>108.72</v>
+        <v>634.3200000000001</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -8335,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>31.18</v>
+        <v>138.33</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8343,28 +8341,28 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2000015901141806</v>
+        <v>2000015920405788</v>
       </c>
       <c r="B63" t="n">
-        <v>2000012425847369</v>
+        <v>2000012446018577</v>
       </c>
       <c r="C63" t="n">
-        <v>46816833391</v>
+        <v>46825928963</v>
       </c>
       <c r="D63" t="n">
-        <v>153164140863</v>
+        <v>154112621330</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PC20241019154452</t>
+          <t>RODIBERTOROBLESALEJANDRO</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2000015901141806</v>
+        <v>2000015920405788</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-08T21:27:21.000-04:00</t>
+          <t>2026-04-10T07:55:11.000-04:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8391,28 +8389,28 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>167.9</v>
+        <v>462</v>
       </c>
       <c r="N63" t="n">
-        <v>25.18</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>166</v>
+        <v>119.2</v>
       </c>
       <c r="Q63" t="n">
-        <v>134</v>
+        <v>59.6</v>
       </c>
       <c r="R63" t="n">
-        <v>32</v>
+        <v>59.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>167.9</v>
+        <v>462</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8424,12 +8422,12 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>CARMORDEFP-203</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>MLM1912930539</t>
+          <t>MLM2381238905</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -8444,16 +8442,16 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>167.9</v>
+        <v>462</v>
       </c>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="n">
-        <v>18.7</v>
+        <v>293.59</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -8462,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8470,28 +8468,28 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2000015900479830</v>
+        <v>2000015919255616</v>
       </c>
       <c r="B64" t="n">
-        <v>2000012425150469</v>
+        <v>2000012444792845</v>
       </c>
       <c r="C64" t="n">
-        <v>46816813562</v>
+        <v>46825583586</v>
       </c>
       <c r="D64" t="n">
-        <v>153903764628</v>
+        <v>153344481991</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GOJE20240421120542</t>
+          <t>MARTHACANDELARIALOPEZCORDOVA</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2000015900479830</v>
+        <v>2000015919255616</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-08T20:46:39.000-04:00</t>
+          <t>2026-04-10T02:48:35.000-04:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8518,28 +8516,28 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="N64" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="R64" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8551,17 +8549,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BR-KZNU-9NOO</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8571,16 +8569,16 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
-        <v>101.13</v>
+        <v>100.5</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -8589,7 +8587,7 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8597,28 +8595,26 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2000015898605836</v>
-      </c>
-      <c r="B65" t="n">
-        <v>2000012423204427</v>
-      </c>
+        <v>2000015918864062</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>46815701425</v>
+        <v>46825132377</v>
       </c>
       <c r="D65" t="n">
-        <v>153887348360</v>
+        <v>154084595658</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JG20241208202301</t>
+          <t>ALEJANDRO3654</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2000015898605836</v>
+        <v>2000015918864062</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-08T18:56:03.000-04:00</t>
+          <t>2026-04-10T00:54:13.000-04:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8645,28 +8641,28 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>164.45</v>
+        <v>198.75</v>
       </c>
       <c r="N65" t="n">
-        <v>16.44</v>
+        <v>28.82</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="Q65" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R65" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>164.45</v>
+        <v>198.75</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8678,17 +8674,17 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -8698,16 +8694,16 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>164.45</v>
+        <v>198.75</v>
       </c>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="n">
-        <v>101.13</v>
+        <v>117.94</v>
       </c>
       <c r="AF65" t="n">
         <v>0</v>
@@ -8716,7 +8712,7 @@
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>16.44</v>
+        <v>28.82</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8724,28 +8720,28 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2000015897678942</v>
+        <v>2000015918735504</v>
       </c>
       <c r="B66" t="n">
-        <v>2000012422238933</v>
+        <v>2000012444242337</v>
       </c>
       <c r="C66" t="n">
-        <v>46815285151</v>
+        <v>46825081431</v>
       </c>
       <c r="D66" t="n">
-        <v>153133108857</v>
+        <v>154083285822</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PIAD3222701</t>
+          <t>JLPACHECOS</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2000015897678942</v>
+        <v>2000015918735504</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-08T17:58:14.000-04:00</t>
+          <t>2026-04-10T00:31:16.000-04:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8772,28 +8768,28 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>840</v>
+        <v>427.5</v>
       </c>
       <c r="N66" t="n">
-        <v>121.8</v>
+        <v>64.12</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>169</v>
+        <v>135.2</v>
       </c>
       <c r="Q66" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R66" t="n">
-        <v>84.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>840</v>
+        <v>427.5</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -8805,12 +8801,12 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>72368155667130</t>
+          <t>A18/A38</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>MLM2090316531</t>
+          <t>MLM3442935972</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -8825,27 +8821,1801 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>840</v>
+        <v>427.5</v>
       </c>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2000012444063601</v>
+      </c>
+      <c r="C67" t="n">
+        <v>46825008245</v>
+      </c>
+      <c r="D67" t="n">
+        <v>154081820206</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OSCARCOLOTL</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2000015918564930</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-04-10T00:03:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N67" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>32</v>
+      </c>
+      <c r="R67" t="n">
+        <v>32</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2000012440383505</v>
+      </c>
+      <c r="C68" t="n">
+        <v>46823711622</v>
+      </c>
+      <c r="D68" t="n">
+        <v>154052836286</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAKE9550997</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2000015915026216</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-04-09T19:18:46.000-04:00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>234</v>
+      </c>
+      <c r="N68" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>221</v>
+      </c>
+      <c r="R68" t="n">
+        <v>54</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>234</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>75045745678283</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>MLM3813363284</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>234</v>
+      </c>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="n">
+        <v>189.42</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>46823497086</v>
+      </c>
+      <c r="D69" t="n">
+        <v>153301992033</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>VNUSROJIBLANK12</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2000015914539400</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:47:34.000-04:00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>713</v>
+      </c>
+      <c r="N69" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>713</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>73239400752399</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>MLM3488485454</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>713</v>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="n">
+        <v>460.58</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2000012439581533</v>
+      </c>
+      <c r="C70" t="n">
+        <v>46823083335</v>
+      </c>
+      <c r="D70" t="n">
+        <v>153298477411</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>GA20240622001650</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2000015914254952</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:26:50.000-04:00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>322</v>
+      </c>
+      <c r="N70" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>80</v>
+      </c>
+      <c r="R70" t="n">
+        <v>80</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>322</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>72141399181305</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>MLM2289340133</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>161</v>
+      </c>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="n">
+        <v>150.05</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2000012438644843</v>
+      </c>
+      <c r="C71" t="n">
+        <v>46822944206</v>
+      </c>
+      <c r="D71" t="n">
+        <v>153287496709</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ESCI899332</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>2000015913353944</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-04-09T17:23:20.000-04:00</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N71" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>32</v>
+      </c>
+      <c r="R71" t="n">
+        <v>32</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C72" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D72" t="n">
+        <v>154016435366</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>2000015911947458</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N72" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>76</v>
+      </c>
+      <c r="R72" t="n">
+        <v>76</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>AUDMORNEGM-921pack</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>MLM3356978052</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="n">
+        <v>149.14</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2000012437174517</v>
+      </c>
+      <c r="C73" t="n">
+        <v>46822254216</v>
+      </c>
+      <c r="D73" t="n">
+        <v>154016462860</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MARAIDALIAAGUILERA</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>2000015911947456</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-04-09T15:43:23.000-04:00</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="N73" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>76</v>
+      </c>
+      <c r="R73" t="n">
+        <v>76</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>76720994758426</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>MLM5115426106</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2000012436224727</v>
+      </c>
+      <c r="C74" t="n">
+        <v>46821806098</v>
+      </c>
+      <c r="D74" t="n">
+        <v>154008453720</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>HLALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:44:05.000-04:00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="N74" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>74725206008902</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>MLM3712202158</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>46821271897</v>
+      </c>
+      <c r="D75" t="n">
+        <v>153258785401</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ENLACESS</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:10:04.000-04:00</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>32</v>
+      </c>
+      <c r="R75" t="n">
+        <v>67</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>75961290041531</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>MLM4318429096</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2000012434212221</v>
+      </c>
+      <c r="C76" t="n">
+        <v>46820912508</v>
+      </c>
+      <c r="D76" t="n">
+        <v>153993729394</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ULY5205</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-04-09T12:45:26.000-04:00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>189</v>
+      </c>
+      <c r="N76" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>32</v>
+      </c>
+      <c r="R76" t="n">
+        <v>32</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>189</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>BOCMORROK405</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>MLM2972698110</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>189</v>
+      </c>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2000012425847369</v>
+      </c>
+      <c r="C77" t="n">
+        <v>46816833391</v>
+      </c>
+      <c r="D77" t="n">
+        <v>153164140863</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PC20241019154452</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-04-08T21:27:21.000-04:00</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="N77" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>134</v>
+      </c>
+      <c r="R77" t="n">
+        <v>32</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>CARMORDEFP-203</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>MLM1912930539</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2000012425150469</v>
+      </c>
+      <c r="C78" t="n">
+        <v>46816813562</v>
+      </c>
+      <c r="D78" t="n">
+        <v>153903764628</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>GOJE20240421120542</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-04-08T20:46:39.000-04:00</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N78" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>32</v>
+      </c>
+      <c r="R78" t="n">
+        <v>32</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2000012423204427</v>
+      </c>
+      <c r="C79" t="n">
+        <v>46815701425</v>
+      </c>
+      <c r="D79" t="n">
+        <v>153887348360</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>JG20241208202301</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-04-08T18:56:03.000-04:00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N79" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>32</v>
+      </c>
+      <c r="R79" t="n">
+        <v>32</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2000012422238933</v>
+      </c>
+      <c r="C80" t="n">
+        <v>46815285151</v>
+      </c>
+      <c r="D80" t="n">
+        <v>153133108857</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PIAD3222701</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-04-08T17:58:14.000-04:00</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>840</v>
+      </c>
+      <c r="N80" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>840</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>72368155667130</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>MLM2090316531</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>840</v>
+      </c>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="n">
         <v>557.67</v>
       </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
         <v>121.8</v>
       </c>
-      <c r="AI66" t="n">
+      <c r="AI80" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ventas_ml_historico.xlsx
+++ b/ventas_ml_historico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI80"/>
+  <dimension ref="A1:AI87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -632,28 +632,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000015976193144</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2000012504064087</v>
-      </c>
+        <v>2000015991694784</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>46851679477</v>
+        <v>46859259366</v>
       </c>
       <c r="D2" t="n">
-        <v>153955812817</v>
+        <v>154836611572</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CEBALLOSJESSICA20220905212100</t>
+          <t>ARAGONJOSE20230107211643</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2000015976193144</v>
+        <v>2000015991694784</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-14T08:12:40.000-04:00</t>
+          <t>2026-04-15T02:54:52.000-04:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -689,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>135.2</v>
+        <v>109</v>
       </c>
       <c r="Q2" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>67.59999999999999</v>
+        <v>41.40000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -713,12 +711,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>BOCMORGRI-385</t>
+          <t>BOCMORNEG-385</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MLM2103166971</t>
+          <t>MLM2921918534</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -733,7 +731,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua 20w Color Gris</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -759,28 +757,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000015974962414</v>
+        <v>2000015991130920</v>
       </c>
       <c r="B3" t="n">
-        <v>2000012502805039</v>
+        <v>2000012519524909</v>
       </c>
       <c r="C3" t="n">
-        <v>46851301984</v>
+        <v>46859005908</v>
       </c>
       <c r="D3" t="n">
-        <v>153941009449</v>
+        <v>154830294970</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GARCIAYAHIR20230307223626</t>
+          <t>AY20260415000339</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2000015974962414</v>
+        <v>2000015991130920</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-14T05:15:35.000-04:00</t>
+          <t>2026-04-15T00:32:05.000-04:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,28 +805,28 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>570.86</v>
+        <v>204.71</v>
       </c>
       <c r="N3" t="n">
-        <v>111.32</v>
+        <v>29.68</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="Q3" t="n">
-        <v>65.5</v>
+        <v>38</v>
       </c>
       <c r="R3" t="n">
-        <v>65.5</v>
+        <v>38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>570.86</v>
+        <v>204.71</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -840,12 +838,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -860,16 +858,16 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>570.86</v>
+        <v>204.71</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>342.37</v>
+        <v>118.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -878,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>111.32</v>
+        <v>29.68</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -886,26 +884,28 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2000015973264718</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>2000015989811170</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2000012516621201</v>
+      </c>
       <c r="C4" t="n">
-        <v>46850557744</v>
+        <v>46858168485</v>
       </c>
       <c r="D4" t="n">
-        <v>153919754851</v>
+        <v>154823055294</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OROM6364679</t>
+          <t>M20250902180422</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2000015973264718</v>
+        <v>2000015989811170</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-13T22:48:32.000-04:00</t>
+          <t>2026-04-14T22:35:45.000-04:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,28 +932,28 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>198.75</v>
+        <v>490</v>
       </c>
       <c r="N4" t="n">
-        <v>28.82</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>165</v>
+        <v>135.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>131</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>198.75</v>
+        <v>490</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -965,17 +965,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>BOCMORNEG-385</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2921918534</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -985,16 +985,16 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>198.75</v>
+        <v>490</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>117.94</v>
+        <v>329.05</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>28.82</v>
+        <v>49</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1011,26 +1011,26 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2000015972550020</v>
+        <v>2000015989050310</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>46850236336</v>
+        <v>46858103982</v>
       </c>
       <c r="D5" t="n">
-        <v>154665186470</v>
+        <v>154819133732</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MOOJUSTINO20220525180349</t>
+          <t>SOPORIESLAVERGAZONA817</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2000015972550020</v>
+        <v>2000015989050310</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-13T21:53:40.000-04:00</t>
+          <t>2026-04-14T21:47:13.000-04:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,28 +1057,28 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>384.63</v>
+        <v>809.9400000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>55.77</v>
+        <v>117.44</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="Q5" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="R5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>384.63</v>
+        <v>809.9400000000001</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>BOCMORDEFMOR-15</t>
+          <t>76825903049544</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MLM2109982307</t>
+          <t>MLM4762473244</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1110,16 +1110,16 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Linterna Led Con Mini Sistema Solar Powerbank Con Radio Fm Default Title</t>
+          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>384.63</v>
+        <v>809.9400000000001</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>218.04</v>
+        <v>524.1799999999999</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>55.77</v>
+        <v>117.44</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1136,28 +1136,28 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2000015971504642</v>
+        <v>2000015985871396</v>
       </c>
       <c r="B6" t="n">
-        <v>2000012499210501</v>
+        <v>2000012497800035</v>
       </c>
       <c r="C6" t="n">
-        <v>46849508631</v>
+        <v>46856658842</v>
       </c>
       <c r="D6" t="n">
-        <v>154659189258</v>
+        <v>154044244135</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAUICHCINTHIA20220209031051</t>
+          <t>FIDELARTUROMARTINEZMARTINEZ</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2000015971504642</v>
+        <v>2000015985871396</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-13T20:52:33.000-04:00</t>
+          <t>2026-04-14T18:30:16.000-04:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,28 +1184,28 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>490</v>
+        <v>204</v>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
+        <v>33.66</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>135.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>67.59999999999999</v>
+        <v>43.6</v>
       </c>
       <c r="R6" t="n">
-        <v>67.59999999999999</v>
+        <v>34.99999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>490</v>
+        <v>204</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1217,17 +1217,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>BOCMORNEG-385</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MLM2921918534</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1237,16 +1237,16 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>490</v>
+        <v>204</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>329.05</v>
+        <v>108.27</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>49</v>
+        <v>33.66</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1263,28 +1263,26 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2000015967426912</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2000012495048417</v>
-      </c>
+        <v>2000015984756800</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>46847634899</v>
+        <v>46855874671</v>
       </c>
       <c r="D7" t="n">
-        <v>153873400805</v>
+        <v>154782496350</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IVAN.FERNIZA</t>
+          <t>LDA5525974</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2000015967426912</v>
+        <v>2000015984756800</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-13T16:49:29.000-04:00</t>
+          <t>2026-04-14T17:16:25.000-04:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1308,31 +1306,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>594</v>
+        <v>566.28</v>
       </c>
       <c r="N7" t="n">
-        <v>21.53</v>
+        <v>82.11</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="Q7" t="n">
-        <v>128</v>
+        <v>84.5</v>
       </c>
       <c r="R7" t="n">
-        <v>128</v>
+        <v>24.5</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>594</v>
+        <v>566.28</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1344,12 +1342,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>73117897877509</t>
+          <t>76790042097103</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MLM3463460726</t>
+          <t>MLM2735881745</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1364,16 +1362,16 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Transmisor Bluetooth Plug In Moreka Cp-0069 5.3 Fm Rgb Negro</t>
+          <t>Audífonos Moreka B09 Bluetooth 5.4 Cancelación Ruido</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>148.5</v>
+        <v>566.28</v>
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>326.11</v>
+        <v>348.42</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1382,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>86.12</v>
+        <v>82.11</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1390,26 +1388,28 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2000015967261198</v>
-      </c>
-      <c r="B8" t="inlineStr"/>
+        <v>2000015984363054</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2000012512508331</v>
+      </c>
       <c r="C8" t="n">
-        <v>46847563627</v>
+        <v>46855681163</v>
       </c>
       <c r="D8" t="n">
-        <v>154620927548</v>
+        <v>154027990295</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EUGENIOALCALDEMALAGON</t>
+          <t>RUSLYSANTAMARA</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000015967261198</v>
+        <v>2000015984363054</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-13T16:40:01.000-04:00</t>
+          <t>2026-04-14T16:48:44.000-04:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1436,28 +1436,28 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>237.5</v>
+        <v>300</v>
       </c>
       <c r="N8" t="n">
-        <v>42.75</v>
+        <v>49.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>94</v>
+        <v>104.8</v>
       </c>
       <c r="Q8" t="n">
         <v>52.4</v>
       </c>
       <c r="R8" t="n">
-        <v>41.6</v>
+        <v>52.4</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>237.5</v>
+        <v>300</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1489,16 +1489,16 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>237.5</v>
+        <v>300</v>
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>120.85</v>
+        <v>170.94</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>42.75</v>
+        <v>49.5</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1515,28 +1515,28 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2000015966806636</v>
+        <v>2000015976193144</v>
       </c>
       <c r="B9" t="n">
-        <v>2000012494410425</v>
+        <v>2000012504064087</v>
       </c>
       <c r="C9" t="n">
-        <v>46847610806</v>
+        <v>46851679477</v>
       </c>
       <c r="D9" t="n">
-        <v>153866965385</v>
+        <v>153955812817</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAX3848998</t>
+          <t>CEBALLOSJESSICA20220905212100</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2000015966806636</v>
+        <v>2000015976193144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-13T16:10:00.000-04:00</t>
+          <t>2026-04-14T08:12:40.000-04:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>BOCMORAZU-385</t>
+          <t>BOCMORGRI-385</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MLM3323904908</t>
+          <t>MLM2103166971</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Bocina Moreka 385 Bluetooth 20w Resistente Agua Ipx6 Tws Micrófono Llamadas Batería Larga Duración Portátil Azul</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua 20w Color Gris</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -1642,28 +1642,28 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000015966540178</v>
+        <v>2000015974962414</v>
       </c>
       <c r="B10" t="n">
-        <v>2000012494141209</v>
+        <v>2000012502805039</v>
       </c>
       <c r="C10" t="n">
-        <v>46847476728</v>
+        <v>46851301984</v>
       </c>
       <c r="D10" t="n">
-        <v>153864537735</v>
+        <v>153941009449</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AGSA7780883</t>
+          <t>GARCIAYAHIR20230307223626</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2000015966540178</v>
+        <v>2000015974962414</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-13T15:53:04.000-04:00</t>
+          <t>2026-04-14T05:15:35.000-04:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1690,28 +1690,28 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>134.55</v>
+        <v>570.86</v>
       </c>
       <c r="N10" t="n">
-        <v>13.46</v>
+        <v>111.32</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>65.5</v>
       </c>
       <c r="R10" t="n">
-        <v>32</v>
+        <v>65.5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>134.55</v>
+        <v>570.86</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1723,17 +1723,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1743,16 +1743,16 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>134.55</v>
+        <v>570.86</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>76.91</v>
+        <v>342.37</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.46</v>
+        <v>111.32</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1769,36 +1769,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2000015964352394</v>
+        <v>2000015973264718</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>46846133057</v>
+        <v>46850557744</v>
       </c>
       <c r="D11" t="n">
-        <v>154596734430</v>
+        <v>153919754851</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ELY12173</t>
+          <t>OROM6364679</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2000015964352394</v>
+        <v>2000015973264718</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-13T13:41:47.000-04:00</t>
+          <t>2026-04-13T22:48:32.000-04:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1815,28 +1815,28 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>886.34</v>
+        <v>198.75</v>
       </c>
       <c r="N11" t="n">
-        <v>88.63</v>
+        <v>28.82</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="Q11" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>886.34</v>
+        <v>198.75</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1848,17 +1848,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1868,16 +1868,16 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>886.34</v>
+        <v>198.75</v>
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>622.48</v>
+        <v>117.94</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>88.63</v>
+        <v>28.82</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1894,28 +1894,26 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2000015963830458</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2000012491320325</v>
-      </c>
+        <v>2000015972550020</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>46846150786</v>
+        <v>46850236336</v>
       </c>
       <c r="D12" t="n">
-        <v>153843244079</v>
+        <v>154665186470</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DG20250909174409</t>
+          <t>MOOJUSTINO20220525180349</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2000015963830458</v>
+        <v>2000015972550020</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-13T13:11:17.000-04:00</t>
+          <t>2026-04-13T21:53:40.000-04:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1942,28 +1940,28 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>198.75</v>
+        <v>384.63</v>
       </c>
       <c r="N12" t="n">
-        <v>28.82</v>
+        <v>55.77</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="Q12" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>198.75</v>
+        <v>384.63</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1975,12 +1973,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>BOCMORDEFMOR-15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2109982307</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1995,16 +1993,16 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Linterna Led Con Mini Sistema Solar Powerbank Con Radio Fm Default Title</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>198.75</v>
+        <v>384.63</v>
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>117.94</v>
+        <v>218.04</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2013,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>28.82</v>
+        <v>55.77</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2021,28 +2019,28 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2000015962454644</v>
+        <v>2000015971504642</v>
       </c>
       <c r="B13" t="n">
-        <v>2000012489892605</v>
+        <v>2000012499210501</v>
       </c>
       <c r="C13" t="n">
-        <v>46845217691</v>
+        <v>46849508631</v>
       </c>
       <c r="D13" t="n">
-        <v>154579864696</v>
+        <v>154659189258</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GARCIAESTEBAN20230518153938</t>
+          <t>CAUICHCINTHIA20220209031051</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2000015962454644</v>
+        <v>2000015971504642</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-13T11:50:53.000-04:00</t>
+          <t>2026-04-13T20:52:33.000-04:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2069,28 +2067,28 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="N13" t="n">
-        <v>13.46</v>
+        <v>49</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>64</v>
+        <v>135.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>32</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2102,12 +2100,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BOCMORNEG-385</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2921918534</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2122,16 +2120,16 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>76.91</v>
+        <v>329.05</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2140,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.46</v>
+        <v>49</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2148,28 +2146,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2000015962146264</v>
+        <v>2000015967426912</v>
       </c>
       <c r="B14" t="n">
-        <v>2000012489579853</v>
+        <v>2000012495048417</v>
       </c>
       <c r="C14" t="n">
-        <v>46845070647</v>
+        <v>46847634899</v>
       </c>
       <c r="D14" t="n">
-        <v>154576785432</v>
+        <v>153873400805</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INEV9190937</t>
+          <t>IVAN.FERNIZA</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2000015962146264</v>
+        <v>2000015967426912</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-13T11:32:39.000-04:00</t>
+          <t>2026-04-13T16:49:29.000-04:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2193,31 +2191,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>364</v>
+        <v>594</v>
       </c>
       <c r="N14" t="n">
-        <v>25.48</v>
+        <v>21.53</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q14" t="n">
         <v>128</v>
       </c>
-      <c r="Q14" t="n">
-        <v>64</v>
-      </c>
       <c r="R14" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>364</v>
+        <v>594</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -2229,12 +2227,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>22187150-white-LAGOM</t>
+          <t>73117897877509</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>MLM1582859464</t>
+          <t>MLM3463460726</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2249,16 +2247,16 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
+          <t>Transmisor Bluetooth Plug In Moreka Cp-0069 5.3 Fm Rgb Negro</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>182</v>
+        <v>148.5</v>
       </c>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="n">
-        <v>216.1</v>
+        <v>326.11</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2267,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>50.96</v>
+        <v>86.12</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2275,38 +2273,36 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2000015958900598</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2000012486229035</v>
-      </c>
+        <v>2000015967261198</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>46843756962</v>
+        <v>46847563627</v>
       </c>
       <c r="D15" t="n">
-        <v>154544707106</v>
+        <v>154620927548</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INEV9190937</t>
+          <t>EUGENIOALCALDEMALAGON</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2000015958900598</v>
+        <v>2000015967261198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-13T07:55:09.000-04:00</t>
+          <t>2026-04-13T16:40:01.000-04:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2320,31 +2316,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>364</v>
+        <v>237.5</v>
       </c>
       <c r="N15" t="n">
-        <v>25.48</v>
+        <v>42.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="Q15" t="n">
-        <v>64</v>
+        <v>52.4</v>
       </c>
       <c r="R15" t="n">
-        <v>64</v>
+        <v>41.6</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>364</v>
+        <v>237.5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2356,12 +2352,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>22187150-white-LAGOM</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>MLM1582859464</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2376,16 +2372,16 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>182</v>
+        <v>237.5</v>
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>216.1</v>
+        <v>120.85</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2394,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>50.96</v>
+        <v>42.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2402,28 +2398,28 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2000015957217578</v>
+        <v>2000015966806636</v>
       </c>
       <c r="B16" t="n">
-        <v>2000012484446139</v>
+        <v>2000012494410425</v>
       </c>
       <c r="C16" t="n">
-        <v>46842931282</v>
+        <v>46847610806</v>
       </c>
       <c r="D16" t="n">
-        <v>153767839871</v>
+        <v>153866965385</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PIINCHEPERRO</t>
+          <t>LAX3848998</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2000015957217578</v>
+        <v>2000015966806636</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-13T00:18:19.000-04:00</t>
+          <t>2026-04-13T16:10:00.000-04:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2450,28 +2446,28 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="N16" t="n">
-        <v>13.46</v>
+        <v>49</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>64</v>
+        <v>135.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>32</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2483,12 +2479,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>BOCMORAZU-385</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3323904908</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2503,16 +2499,16 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Bocina Moreka 385 Bluetooth 20w Resistente Agua Ipx6 Tws Micrófono Llamadas Batería Larga Duración Portátil Azul</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>134.55</v>
+        <v>490</v>
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>76.91</v>
+        <v>329.05</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2521,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>13.46</v>
+        <v>49</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2529,28 +2525,28 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2000015956925426</v>
+        <v>2000015966540178</v>
       </c>
       <c r="B17" t="n">
-        <v>2000012484147313</v>
+        <v>2000012494141209</v>
       </c>
       <c r="C17" t="n">
-        <v>46842537261</v>
+        <v>46847476728</v>
       </c>
       <c r="D17" t="n">
-        <v>153765643607</v>
+        <v>153864537735</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>REINAJUDTIHRAMREZ</t>
+          <t>AGSA7780883</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2000015956925426</v>
+        <v>2000015966540178</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-12T23:36:15.000-04:00</t>
+          <t>2026-04-13T15:53:04.000-04:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2577,28 +2573,28 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="N17" t="n">
-        <v>33.66</v>
+        <v>13.46</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2610,17 +2606,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2630,16 +2626,16 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>116.87</v>
+        <v>76.91</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2648,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>33.66</v>
+        <v>13.46</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2656,38 +2652,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2000015956767790</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2000012484002697</v>
-      </c>
+        <v>2000015964352394</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>46846175374</v>
+        <v>46846133057</v>
       </c>
       <c r="D18" t="n">
-        <v>154512994416</v>
+        <v>154596734430</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MM20250621175836</t>
+          <t>ELY12173</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2000015956767790</v>
+        <v>2000015964352394</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-12T23:21:24.000-04:00</t>
+          <t>2026-04-13T13:41:47.000-04:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2704,28 +2698,28 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>490</v>
+        <v>886.34</v>
       </c>
       <c r="N18" t="n">
-        <v>49</v>
+        <v>88.63</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>135.2</v>
+        <v>116</v>
       </c>
       <c r="Q18" t="n">
-        <v>67.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="R18" t="n">
-        <v>67.59999999999999</v>
+        <v>21</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>490</v>
+        <v>886.34</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2737,12 +2731,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>BOCMORNEG-385</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>MLM2921918534</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2757,16 +2751,16 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>490</v>
+        <v>886.34</v>
       </c>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>329.05</v>
+        <v>622.48</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2775,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>49</v>
+        <v>88.63</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2783,28 +2777,28 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2000015956605502</v>
+        <v>2000015963830458</v>
       </c>
       <c r="B19" t="n">
-        <v>2000012483808797</v>
+        <v>2000012491320325</v>
       </c>
       <c r="C19" t="n">
-        <v>46842403159</v>
+        <v>46846150786</v>
       </c>
       <c r="D19" t="n">
-        <v>154511573332</v>
+        <v>153843244079</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PEOR7869303</t>
+          <t>DG20250909174409</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2000015956605502</v>
+        <v>2000015963830458</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-12T22:59:10.000-04:00</t>
+          <t>2026-04-13T13:11:17.000-04:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2828,31 +2822,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>252.3</v>
+        <v>198.75</v>
       </c>
       <c r="N19" t="n">
-        <v>13.88</v>
+        <v>28.82</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>210</v>
+        <v>68</v>
       </c>
       <c r="Q19" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="R19" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>252.3</v>
+        <v>198.75</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2864,17 +2858,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>73117950936864</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>MLM4537227786</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2884,16 +2878,16 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Soporte De Celular Para Carro Estabilizador De Teléfono Color Negro</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>84.09999999999999</v>
+        <v>198.75</v>
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>82.81999999999999</v>
+        <v>117.94</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2902,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>41.64</v>
+        <v>28.82</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2910,28 +2904,28 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2000015955581526</v>
+        <v>2000015962454644</v>
       </c>
       <c r="B20" t="n">
-        <v>2000012482766177</v>
+        <v>2000012489892605</v>
       </c>
       <c r="C20" t="n">
-        <v>46841978337</v>
+        <v>46845217691</v>
       </c>
       <c r="D20" t="n">
-        <v>154505410318</v>
+        <v>154579864696</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JOSTIMOTEOGUERREROCASTILLO</t>
+          <t>GARCIAESTEBAN20230518153938</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2000015955581526</v>
+        <v>2000015962454644</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-12T21:32:57.000-04:00</t>
+          <t>2026-04-13T11:50:53.000-04:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2958,28 +2952,28 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1365</v>
+        <v>134.55</v>
       </c>
       <c r="N20" t="n">
-        <v>197.92</v>
+        <v>13.46</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>190</v>
+        <v>64</v>
       </c>
       <c r="Q20" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="R20" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1365</v>
+        <v>134.55</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2991,17 +2985,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>72591346859892</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>MLM2157132507</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3011,16 +3005,16 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>1365</v>
+        <v>134.55</v>
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
-        <v>948.52</v>
+        <v>76.91</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3029,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>197.92</v>
+        <v>13.46</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3037,28 +3031,28 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2000015955406042</v>
+        <v>2000015962146264</v>
       </c>
       <c r="B21" t="n">
-        <v>2000012482561253</v>
+        <v>2000012489579853</v>
       </c>
       <c r="C21" t="n">
-        <v>46842164894</v>
+        <v>46845070647</v>
       </c>
       <c r="D21" t="n">
-        <v>153755964839</v>
+        <v>154576785432</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>YATZIRYZUBIA</t>
+          <t>INEV9190937</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2000015955406042</v>
+        <v>2000015962146264</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-12T21:18:30.000-04:00</t>
+          <t>2026-04-13T11:32:39.000-04:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3082,31 +3076,31 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>172.79</v>
+        <v>364</v>
       </c>
       <c r="N21" t="n">
-        <v>25.92</v>
+        <v>25.48</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>135.2</v>
+        <v>128</v>
       </c>
       <c r="Q21" t="n">
-        <v>67.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="R21" t="n">
-        <v>67.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>172.79</v>
+        <v>364</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3118,17 +3112,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>72478699982948</t>
+          <t>22187150-white-LAGOM</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>MLM2853107461</t>
+          <t>MLM1582859464</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3138,16 +3132,16 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Extensión Regleta Moreka Mc5447c 8 Tomas 2 Usb C Protección 2m Blanca Blanco</t>
+          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>172.79</v>
+        <v>182</v>
       </c>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="n">
-        <v>63.63</v>
+        <v>216.1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3156,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>25.92</v>
+        <v>50.96</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3164,38 +3158,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2000015955037638</v>
+        <v>2000015958900598</v>
       </c>
       <c r="B22" t="n">
-        <v>2000012482184957</v>
+        <v>2000012486229035</v>
       </c>
       <c r="C22" t="n">
-        <v>46841741585</v>
+        <v>46843756962</v>
       </c>
       <c r="D22" t="n">
-        <v>153753433147</v>
+        <v>154544707106</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ORNELASJONATHAN20230517180340</t>
+          <t>INEV9190937</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2000015955037638</v>
+        <v>2000015958900598</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-04-12T20:54:10.000-04:00</t>
+          <t>2026-04-13T07:55:09.000-04:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3209,31 +3203,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>134.55</v>
+        <v>364</v>
       </c>
       <c r="N22" t="n">
-        <v>13.46</v>
+        <v>25.48</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q22" t="n">
         <v>64</v>
       </c>
-      <c r="Q22" t="n">
-        <v>32</v>
-      </c>
       <c r="R22" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>134.55</v>
+        <v>364</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -3245,17 +3239,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>22187150-white-LAGOM</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM1582859464</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3265,16 +3259,16 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Difusor Aromaterapia Humificador Moreka Shop Ho2 Portátil</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>134.55</v>
+        <v>182</v>
       </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
-        <v>76.91</v>
+        <v>216.1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3283,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>13.46</v>
+        <v>50.96</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3291,28 +3285,28 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2000015953863248</v>
+        <v>2000015957217578</v>
       </c>
       <c r="B23" t="n">
-        <v>2000012480954851</v>
+        <v>2000012484446139</v>
       </c>
       <c r="C23" t="n">
-        <v>46841512724</v>
+        <v>46842931282</v>
       </c>
       <c r="D23" t="n">
-        <v>154492811296</v>
+        <v>153767839871</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ALANROBLES896</t>
+          <t>PIINCHEPERRO</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2000015953863248</v>
+        <v>2000015957217578</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-04-12T19:36:07.000-04:00</t>
+          <t>2026-04-13T00:18:19.000-04:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3418,26 +3412,28 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2000015953129652</v>
-      </c>
-      <c r="B24" t="inlineStr"/>
+        <v>2000015956925426</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2000012484147313</v>
+      </c>
       <c r="C24" t="n">
-        <v>46840936695</v>
+        <v>46842537261</v>
       </c>
       <c r="D24" t="n">
-        <v>153738745847</v>
+        <v>153765643607</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LUISEDUARDOJIMNEZCABRERA</t>
+          <t>REINAJUDTIHRAMREZ</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2000015953129652</v>
+        <v>2000015956925426</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-04-12T18:47:14.000-04:00</t>
+          <t>2026-04-12T23:36:15.000-04:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3464,28 +3460,28 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>99.75</v>
+        <v>204</v>
       </c>
       <c r="N24" t="n">
-        <v>14.96</v>
+        <v>33.66</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="Q24" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R24" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>99.75</v>
+        <v>204</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -3497,17 +3493,17 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>CARMORDEFJB212AA-1</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>MLM3357055624</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3517,16 +3513,16 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Pilas Recargables Aaa Jiabao 350mah Pack 10 Con Cargador Jb-212</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>99.75</v>
+        <v>204</v>
       </c>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
-        <v>37.76</v>
+        <v>116.87</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3535,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>14.96</v>
+        <v>33.66</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3543,26 +3539,28 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2000015952631620</v>
-      </c>
-      <c r="B25" t="inlineStr"/>
+        <v>2000015956767790</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2000012484002697</v>
+      </c>
       <c r="C25" t="n">
-        <v>46840996916</v>
+        <v>46846175374</v>
       </c>
       <c r="D25" t="n">
-        <v>153734537841</v>
+        <v>154512994416</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MAAU5192905</t>
+          <t>MM20250621175836</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2000015952631620</v>
+        <v>2000015956767790</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-12T18:12:34.000-04:00</t>
+          <t>2026-04-12T23:21:24.000-04:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3589,28 +3587,28 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>886.34</v>
+        <v>490</v>
       </c>
       <c r="N25" t="n">
-        <v>88.63</v>
+        <v>49</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>234</v>
+        <v>135.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>163.87</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>70.13</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>886.34</v>
+        <v>490</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -3622,12 +3620,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>BOCMORNEG-385</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM2921918534</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3642,16 +3640,16 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Bluetooth Portátil Inalámbrico Resistente Al Agua De 20w Con Bateria De 2000mah Y Sonido Estereo True Wireless Stereo Manos Libre Moreka 385 Negro</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>886.34</v>
+        <v>490</v>
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>622.48</v>
+        <v>329.05</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3660,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>88.63</v>
+        <v>49</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3668,28 +3666,28 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2000015951746522</v>
+        <v>2000015956605502</v>
       </c>
       <c r="B26" t="n">
-        <v>2000012478741857</v>
+        <v>2000012483808797</v>
       </c>
       <c r="C26" t="n">
-        <v>46840326297</v>
+        <v>46842403159</v>
       </c>
       <c r="D26" t="n">
-        <v>153726813143</v>
+        <v>154511573332</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NATHALIALONZOVARGAS</t>
+          <t>PEOR7869303</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2000015951746522</v>
+        <v>2000015956605502</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-12T17:02:23.000-04:00</t>
+          <t>2026-04-12T22:59:10.000-04:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3713,31 +3711,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>134.55</v>
+        <v>252.3</v>
       </c>
       <c r="N26" t="n">
-        <v>13.46</v>
+        <v>13.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>64</v>
+        <v>210</v>
       </c>
       <c r="Q26" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="R26" t="n">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>134.55</v>
+        <v>252.3</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -3749,12 +3747,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>73117950936864</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4537227786</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3769,16 +3767,16 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Soporte De Celular Para Carro Estabilizador De Teléfono Color Negro</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>134.55</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
-        <v>76.91</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3787,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>13.46</v>
+        <v>41.64</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3795,28 +3793,28 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2000015950183992</v>
+        <v>2000015955581526</v>
       </c>
       <c r="B27" t="n">
-        <v>2000012476881167</v>
+        <v>2000012482766177</v>
       </c>
       <c r="C27" t="n">
-        <v>46839927702</v>
+        <v>46841978337</v>
       </c>
       <c r="D27" t="n">
-        <v>154462600152</v>
+        <v>154505410318</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DUER9786335</t>
+          <t>JOSTIMOTEOGUERREROCASTILLO</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2000015950183992</v>
+        <v>2000015955581526</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-12T15:02:47.000-04:00</t>
+          <t>2026-04-12T21:32:57.000-04:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3843,28 +3841,28 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>134.55</v>
+        <v>1365</v>
       </c>
       <c r="N27" t="n">
-        <v>13.46</v>
+        <v>197.92</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="Q27" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="R27" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>134.55</v>
+        <v>1365</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3876,17 +3874,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3896,16 +3894,16 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>134.55</v>
+        <v>1365</v>
       </c>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="n">
-        <v>44.91</v>
+        <v>948.52</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3914,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>13.46</v>
+        <v>197.92</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3922,28 +3920,28 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2000015950193056</v>
+        <v>2000015955406042</v>
       </c>
       <c r="B28" t="n">
-        <v>2000012476881167</v>
+        <v>2000012482561253</v>
       </c>
       <c r="C28" t="n">
-        <v>46839927702</v>
+        <v>46842164894</v>
       </c>
       <c r="D28" t="n">
-        <v>154462576514</v>
+        <v>153755964839</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DUER9786335</t>
+          <t>YATZIRYZUBIA</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2000015950193056</v>
+        <v>2000015955406042</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-04-12T15:02:47.000-04:00</t>
+          <t>2026-04-12T21:18:30.000-04:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3970,28 +3968,28 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>134.55</v>
+        <v>172.79</v>
       </c>
       <c r="N28" t="n">
-        <v>13.46</v>
+        <v>25.92</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>128</v>
+        <v>135.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>64</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>64</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>134.55</v>
+        <v>172.79</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -4003,12 +4001,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>72478699982948</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM2853107461</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4023,16 +4021,16 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Extensión Regleta Moreka Mc5447c 8 Tomas 2 Usb C Protección 2m Blanca Blanco</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>134.55</v>
+        <v>172.79</v>
       </c>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
-        <v>108.91</v>
+        <v>63.63</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4041,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>13.46</v>
+        <v>25.92</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4049,26 +4047,28 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2000015949142546</v>
-      </c>
-      <c r="B29" t="inlineStr"/>
+        <v>2000015955037638</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2000012482184957</v>
+      </c>
       <c r="C29" t="n">
-        <v>46839201507</v>
+        <v>46841741585</v>
       </c>
       <c r="D29" t="n">
-        <v>153706432727</v>
+        <v>153753433147</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>G20250531223627</t>
+          <t>ORNELASJONATHAN20230517180340</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2000015949142546</v>
+        <v>2000015955037638</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-12T13:40:31.000-04:00</t>
+          <t>2026-04-12T20:54:10.000-04:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4095,28 +4095,28 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="N29" t="n">
-        <v>33.66</v>
+        <v>13.46</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="Q29" t="n">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="R29" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4148,16 +4148,16 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>204</v>
+        <v>134.55</v>
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>116.87</v>
+        <v>76.91</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>33.66</v>
+        <v>13.46</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4174,26 +4174,28 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2000015945008650</v>
-      </c>
-      <c r="B30" t="inlineStr"/>
+        <v>2000015953863248</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2000012480954851</v>
+      </c>
       <c r="C30" t="n">
-        <v>46837630090</v>
+        <v>46841512724</v>
       </c>
       <c r="D30" t="n">
-        <v>154412117972</v>
+        <v>154492811296</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TONO5981002</t>
+          <t>ALANROBLES896</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2000015945008650</v>
+        <v>2000015953863248</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-12T05:17:26.000-04:00</t>
+          <t>2026-04-12T19:36:07.000-04:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4220,28 +4222,28 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="N30" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="Q30" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -4253,12 +4255,12 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4273,16 +4275,16 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>76.91</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4291,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>13.46</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4299,28 +4301,26 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2000015944827404</v>
-      </c>
-      <c r="B31" t="n">
-        <v>2000012471530373</v>
-      </c>
+        <v>2000015953129652</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>46837277205</v>
+        <v>46840936695</v>
       </c>
       <c r="D31" t="n">
-        <v>153662197883</v>
+        <v>153738745847</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JESSICAMIRTALADELENROA</t>
+          <t>LUISEDUARDOJIMNEZCABRERA</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000015944827404</v>
+        <v>2000015953129652</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-12T02:47:16.000-04:00</t>
+          <t>2026-04-12T18:47:14.000-04:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4347,28 +4347,28 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>204</v>
+        <v>99.75</v>
       </c>
       <c r="N31" t="n">
-        <v>33.66</v>
+        <v>14.96</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>76.27</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="n">
-        <v>41.27</v>
+        <v>38</v>
       </c>
       <c r="R31" t="n">
-        <v>34.99999999999999</v>
+        <v>70</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>204</v>
+        <v>99.75</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -4380,17 +4380,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>BOCMORAZU405</t>
+          <t>CARMORDEFJB212AA-1</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM3357055624</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4400,16 +4400,16 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Pilas Recargables Aaa Jiabao 350mah Pack 10 Con Cargador Jb-212</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>204</v>
+        <v>99.75</v>
       </c>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="n">
-        <v>110.6</v>
+        <v>37.76</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>33.66</v>
+        <v>14.96</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4426,26 +4426,26 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2000015944791160</v>
+        <v>2000015952631620</v>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>46837546532</v>
+        <v>46840996916</v>
       </c>
       <c r="D32" t="n">
-        <v>153662234221</v>
+        <v>153734537841</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RA20241216152952</t>
+          <t>MAAU5192905</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2000015944791160</v>
+        <v>2000015952631620</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-12T02:43:18.000-04:00</t>
+          <t>2026-04-12T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4472,28 +4472,28 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>202.65</v>
+        <v>886.34</v>
       </c>
       <c r="N32" t="n">
-        <v>33.44</v>
+        <v>88.63</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>87</v>
+        <v>234</v>
       </c>
       <c r="Q32" t="n">
-        <v>125</v>
+        <v>163.87</v>
       </c>
       <c r="R32" t="n">
-        <v>38</v>
+        <v>70.13</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>202.65</v>
+        <v>886.34</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -4505,17 +4505,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>PX-SJL9-BCN0</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MLM2082055833</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4525,16 +4525,16 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>202.65</v>
+        <v>886.34</v>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
-        <v>112.86</v>
+        <v>622.48</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>33.44</v>
+        <v>88.63</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4551,28 +4551,28 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2000015944554586</v>
+        <v>2000015951746522</v>
       </c>
       <c r="B33" t="n">
-        <v>2000012471236369</v>
+        <v>2000012478741857</v>
       </c>
       <c r="C33" t="n">
-        <v>46837165917</v>
+        <v>46840326297</v>
       </c>
       <c r="D33" t="n">
-        <v>154406778626</v>
+        <v>153726813143</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JUANANGELDUEÑASRINCON</t>
+          <t>NATHALIALONZOVARGAS</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2000015944554586</v>
+        <v>2000015951746522</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-04-12T01:07:15.000-04:00</t>
+          <t>2026-04-12T17:02:23.000-04:00</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4678,38 +4678,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2000015944520040</v>
+        <v>2000015950183992</v>
       </c>
       <c r="B34" t="n">
-        <v>2000012471190691</v>
+        <v>2000012476881167</v>
       </c>
       <c r="C34" t="n">
-        <v>46837150907</v>
+        <v>46839927702</v>
       </c>
       <c r="D34" t="n">
-        <v>153658671197</v>
+        <v>154462600152</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GUJU6869975</t>
+          <t>DUER9786335</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2000015944520040</v>
+        <v>2000015950183992</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-04-12T00:57:45.000-04:00</t>
+          <t>2026-04-12T15:02:47.000-04:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4726,28 +4726,28 @@
         <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="N34" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="Q34" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="R34" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4779,16 +4779,16 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>886.34</v>
+        <v>134.55</v>
       </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
-        <v>622.48</v>
+        <v>44.91</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>88.63</v>
+        <v>13.46</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4805,28 +4805,28 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2000015944444922</v>
+        <v>2000015950193056</v>
       </c>
       <c r="B35" t="n">
-        <v>2000012471123715</v>
+        <v>2000012476881167</v>
       </c>
       <c r="C35" t="n">
-        <v>46837123631</v>
+        <v>46839927702</v>
       </c>
       <c r="D35" t="n">
-        <v>154405351746</v>
+        <v>154462576514</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TAJU9721170</t>
+          <t>DUER9786335</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2000015944444922</v>
+        <v>2000015950193056</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-04-12T00:41:22.000-04:00</t>
+          <t>2026-04-12T15:02:47.000-04:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4853,28 +4853,28 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="N35" t="n">
-        <v>31.04</v>
+        <v>13.46</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="Q35" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="R35" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -4886,17 +4886,17 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Azul K073</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>MLM3129247568</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4906,16 +4906,16 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>206.95</v>
+        <v>134.55</v>
       </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
-        <v>81.18000000000001</v>
+        <v>108.91</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>31.04</v>
+        <v>13.46</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -4932,28 +4932,26 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2000015944439726</v>
-      </c>
-      <c r="B36" t="n">
-        <v>2000012471123715</v>
-      </c>
+        <v>2000015949142546</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>46837123631</v>
+        <v>46839201507</v>
       </c>
       <c r="D36" t="n">
-        <v>154405486928</v>
+        <v>153706432727</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TAJU9721170</t>
+          <t>G20250531223627</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2000015944439726</v>
+        <v>2000015949142546</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-12T00:41:22.000-04:00</t>
+          <t>2026-04-12T13:40:31.000-04:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4980,28 +4978,28 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>206.95</v>
+        <v>204</v>
       </c>
       <c r="N36" t="n">
-        <v>31.04</v>
+        <v>33.66</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="Q36" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="R36" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>206.95</v>
+        <v>204</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -5013,12 +5011,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Blanco K073</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>MLM3129247568</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5033,16 +5031,16 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>206.95</v>
+        <v>204</v>
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>157.18</v>
+        <v>116.87</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5051,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>31.04</v>
+        <v>33.66</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5059,28 +5057,26 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2000015944248160</v>
-      </c>
-      <c r="B37" t="n">
-        <v>2000012470820489</v>
-      </c>
+        <v>2000015945008650</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>46837041551</v>
+        <v>46837630090</v>
       </c>
       <c r="D37" t="n">
-        <v>154403287242</v>
+        <v>154412117972</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>JUANCARLOSCARMONAALFARO</t>
+          <t>TONO5981002</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2000015944248160</v>
+        <v>2000015945008650</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-11T23:59:26.000-04:00</t>
+          <t>2026-04-12T05:17:26.000-04:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5107,28 +5103,28 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>204.71</v>
+        <v>886.34</v>
       </c>
       <c r="N37" t="n">
-        <v>29.68</v>
+        <v>88.63</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>105.46</v>
+        <v>98</v>
       </c>
       <c r="Q37" t="n">
-        <v>67.45999999999999</v>
+        <v>95</v>
       </c>
       <c r="R37" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>204.71</v>
+        <v>886.34</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -5140,17 +5136,17 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5160,16 +5156,16 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>204.71</v>
+        <v>886.34</v>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="n">
-        <v>89.04000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5178,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>29.68</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5186,28 +5182,28 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2000015942032840</v>
+        <v>2000015944827404</v>
       </c>
       <c r="B38" t="n">
-        <v>2000012468587881</v>
+        <v>2000012471530373</v>
       </c>
       <c r="C38" t="n">
-        <v>46836369178</v>
+        <v>46837277205</v>
       </c>
       <c r="D38" t="n">
-        <v>154378603064</v>
+        <v>153662197883</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JOELLDJ</t>
+          <t>JESSICAMIRTALADELENROA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2000015942032840</v>
+        <v>2000015944827404</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-11T19:53:08.000-04:00</t>
+          <t>2026-04-12T02:47:16.000-04:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5234,28 +5230,28 @@
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>700</v>
+        <v>204</v>
       </c>
       <c r="N38" t="n">
-        <v>101.5</v>
+        <v>33.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>169</v>
+        <v>76.27</v>
       </c>
       <c r="Q38" t="n">
-        <v>84.5</v>
+        <v>41.27</v>
       </c>
       <c r="R38" t="n">
-        <v>84.5</v>
+        <v>34.99999999999999</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>700</v>
+        <v>204</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -5267,17 +5263,17 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>BOCMORAZU405</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>MLM4388568286</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5287,16 +5283,16 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>700</v>
+        <v>204</v>
       </c>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
-        <v>450.63</v>
+        <v>110.6</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5305,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>101.5</v>
+        <v>33.66</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5313,26 +5309,26 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2000015941753476</v>
+        <v>2000015944791160</v>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>46836259542</v>
+        <v>46837546532</v>
       </c>
       <c r="D39" t="n">
-        <v>153627775865</v>
+        <v>153662234221</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NOYOLAIVAN20231112183250</t>
+          <t>RA20241216152952</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2000015941753476</v>
+        <v>2000015944791160</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-11T19:31:35.000-04:00</t>
+          <t>2026-04-12T02:43:18.000-04:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5359,28 +5355,28 @@
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>189</v>
+        <v>202.65</v>
       </c>
       <c r="N39" t="n">
-        <v>31.18</v>
+        <v>33.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="R39" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>189</v>
+        <v>202.65</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -5392,12 +5388,12 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>BOCMORNEG405</t>
+          <t>PX-SJL9-BCN0</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM2082055833</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5412,16 +5408,16 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Bocina Moto Bluetooth Portátil 1200mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>189</v>
+        <v>202.65</v>
       </c>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>112.86</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5430,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>33.44</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5438,28 +5434,28 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2000015941686260</v>
+        <v>2000015944554586</v>
       </c>
       <c r="B40" t="n">
-        <v>2000012468221695</v>
+        <v>2000012471236369</v>
       </c>
       <c r="C40" t="n">
-        <v>46836215454</v>
+        <v>46837165917</v>
       </c>
       <c r="D40" t="n">
-        <v>154373847452</v>
+        <v>154406778626</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CAAN8167043</t>
+          <t>JUANANGELDUEÑASRINCON</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2000015941686260</v>
+        <v>2000015944554586</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-11T19:23:01.000-04:00</t>
+          <t>2026-04-12T01:07:15.000-04:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5519,12 +5515,12 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5539,7 +5535,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
@@ -5565,36 +5561,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2000015941054478</v>
-      </c>
-      <c r="B41" t="inlineStr"/>
+        <v>2000015944520040</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2000012471190691</v>
+      </c>
       <c r="C41" t="n">
-        <v>46835940590</v>
+        <v>46837150907</v>
       </c>
       <c r="D41" t="n">
-        <v>154365172508</v>
+        <v>153658671197</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>L20260220145454</t>
+          <t>GUJU6869975</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2000015941054478</v>
+        <v>2000015944520040</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-11T18:29:38.000-04:00</t>
+          <t>2026-04-12T00:57:45.000-04:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5620,13 +5618,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="Q41" t="n">
         <v>95</v>
       </c>
       <c r="R41" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -5690,28 +5688,28 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2000015940863248</v>
+        <v>2000015944439726</v>
       </c>
       <c r="B42" t="n">
-        <v>2000012467360959</v>
+        <v>2000012471123715</v>
       </c>
       <c r="C42" t="n">
-        <v>46835581697</v>
+        <v>46837123631</v>
       </c>
       <c r="D42" t="n">
-        <v>154362231108</v>
+        <v>154405486928</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JOSMANUELHERNNDEZMRQUEZ</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2000015940863248</v>
+        <v>2000015944439726</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-11T18:12:34.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5735,31 +5733,31 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>4095</v>
+        <v>206.95</v>
       </c>
       <c r="N42" t="n">
-        <v>197.92</v>
+        <v>31.04</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>570</v>
+        <v>152</v>
       </c>
       <c r="Q42" t="n">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="R42" t="n">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4095</v>
+        <v>206.95</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -5771,12 +5769,12 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>72591346859892</t>
+          <t>Blanco K073</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>MLM2157132507</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5791,16 +5789,16 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>1365</v>
+        <v>206.95</v>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
-        <v>2845.58</v>
+        <v>157.18</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -5809,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>593.76</v>
+        <v>31.04</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5817,26 +5815,28 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2000015935667022</v>
-      </c>
-      <c r="B43" t="inlineStr"/>
+        <v>2000015944444922</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2000012471123715</v>
+      </c>
       <c r="C43" t="n">
-        <v>46833482066</v>
+        <v>46837123631</v>
       </c>
       <c r="D43" t="n">
-        <v>153550074671</v>
+        <v>154405351746</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MARCOPEMA</t>
+          <t>TAJU9721170</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2000015935667022</v>
+        <v>2000015944444922</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-04-11T10:56:27.000-04:00</t>
+          <t>2026-04-12T00:41:22.000-04:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5863,28 +5863,28 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>886.34</v>
+        <v>206.95</v>
       </c>
       <c r="N43" t="n">
-        <v>88.63</v>
+        <v>31.04</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="Q43" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="R43" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>886.34</v>
+        <v>206.95</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -5896,17 +5896,17 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>Azul K073</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM3129247568</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5916,16 +5916,16 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Mini Power Bank 10000mah De 37w Batería Portátil 4 Salida</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>886.34</v>
+        <v>206.95</v>
       </c>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
-        <v>622.48</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -5934,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>88.63</v>
+        <v>31.04</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -5942,26 +5942,28 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2000015932827654</v>
-      </c>
-      <c r="B44" t="inlineStr"/>
+        <v>2000015944248160</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2000012470820489</v>
+      </c>
       <c r="C44" t="n">
-        <v>46831838345</v>
+        <v>46837041551</v>
       </c>
       <c r="D44" t="n">
-        <v>154262740072</v>
+        <v>154403287242</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ROJASDAVID20210814233921</t>
+          <t>JUANCARLOSCARMONAALFARO</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2000015932827654</v>
+        <v>2000015944248160</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-11T01:59:07.000-04:00</t>
+          <t>2026-04-11T23:59:26.000-04:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5988,28 +5990,28 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>886.34</v>
+        <v>204.71</v>
       </c>
       <c r="N44" t="n">
-        <v>88.63</v>
+        <v>29.68</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>125</v>
+        <v>105.46</v>
       </c>
       <c r="Q44" t="n">
-        <v>95</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="R44" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>886.34</v>
+        <v>204.71</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -6021,17 +6023,17 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>BOCMORGRI+A18</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>MLM2335627661</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -6041,16 +6043,16 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>886.34</v>
+        <v>204.71</v>
       </c>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6059,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>29.68</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6067,28 +6069,28 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2000015932875024</v>
+        <v>2000015942032840</v>
       </c>
       <c r="B45" t="n">
-        <v>2000012459011895</v>
+        <v>2000012468587881</v>
       </c>
       <c r="C45" t="n">
-        <v>46831837021</v>
+        <v>46836369178</v>
       </c>
       <c r="D45" t="n">
-        <v>153516147611</v>
+        <v>154378603064</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LOAN2137132</t>
+          <t>JOELLDJ</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2000015932875024</v>
+        <v>2000015942032840</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-04-11T01:57:33.000-04:00</t>
+          <t>2026-04-11T19:53:08.000-04:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6115,28 +6117,28 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>134.55</v>
+        <v>700</v>
       </c>
       <c r="N45" t="n">
-        <v>13.46</v>
+        <v>101.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="R45" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>134.55</v>
+        <v>700</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -6148,12 +6150,12 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM4388568286</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6168,16 +6170,16 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Bluetooth Moreka 428 Portátil 10w 5000mah Azul-naranja</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>134.55</v>
+        <v>700</v>
       </c>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>76.91</v>
+        <v>450.63</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6186,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>13.46</v>
+        <v>101.5</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6194,26 +6196,26 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2000015932632586</v>
+        <v>2000015941753476</v>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>46831736271</v>
+        <v>46836259542</v>
       </c>
       <c r="D46" t="n">
-        <v>153514027567</v>
+        <v>153627775865</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ERVINEDUARDO RAMÍREZVZLA</t>
+          <t>NOYOLAIVAN20231112183250</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2000015932632586</v>
+        <v>2000015941753476</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-11T00:54:31.000-04:00</t>
+          <t>2026-04-11T19:31:35.000-04:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6240,28 +6242,28 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>570.86</v>
+        <v>189</v>
       </c>
       <c r="N46" t="n">
-        <v>111.32</v>
+        <v>31.18</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="Q46" t="n">
-        <v>65.5</v>
+        <v>32</v>
       </c>
       <c r="R46" t="n">
-        <v>63.5</v>
+        <v>77</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>570.86</v>
+        <v>189</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -6273,12 +6275,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>BOCMORNEG405</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM2972698110</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6293,16 +6295,16 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>570.86</v>
+        <v>189</v>
       </c>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>342.37</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6311,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>111.32</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6319,26 +6321,28 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000015932009672</v>
-      </c>
-      <c r="B47" t="inlineStr"/>
+        <v>2000015941686260</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2000012468221695</v>
+      </c>
       <c r="C47" t="n">
-        <v>46831746812</v>
+        <v>46836215454</v>
       </c>
       <c r="D47" t="n">
-        <v>153507878875</v>
+        <v>154373847452</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PLER973318</t>
+          <t>CAAN8167043</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2000015932009672</v>
+        <v>2000015941686260</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-10T23:10:48.000-04:00</t>
+          <t>2026-04-11T19:23:01.000-04:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6365,28 +6369,28 @@
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="N47" t="n">
-        <v>62.2</v>
+        <v>13.46</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="Q47" t="n">
-        <v>67.59999999999999</v>
+        <v>32</v>
       </c>
       <c r="R47" t="n">
-        <v>26.40000000000001</v>
+        <v>32</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -6398,17 +6402,17 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>76825709097220</t>
+          <t>75961290041531</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>MLM4762499328</t>
+          <t>MLM4318429096</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6418,16 +6422,16 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>429</v>
+        <v>134.55</v>
       </c>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="n">
-        <v>260.36</v>
+        <v>76.91</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6436,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>62.2</v>
+        <v>13.46</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6444,28 +6448,26 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2000015931967972</v>
-      </c>
-      <c r="B48" t="n">
-        <v>2000012458078981</v>
-      </c>
+        <v>2000015941054478</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>46831734526</v>
+        <v>46835940590</v>
       </c>
       <c r="D48" t="n">
-        <v>154254282856</v>
+        <v>154365172508</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HECTORPETITHECTORPETIT</t>
+          <t>L20260220145454</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2000015931967972</v>
+        <v>2000015941054478</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-10T23:07:11.000-04:00</t>
+          <t>2026-04-11T18:29:38.000-04:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6492,28 +6494,28 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="N48" t="n">
-        <v>120.01</v>
+        <v>88.63</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="Q48" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="R48" t="n">
-        <v>84.5</v>
+        <v>18</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -6525,17 +6527,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>76532580917858</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MLM4545490694</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6545,16 +6547,16 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>827.64</v>
+        <v>886.34</v>
       </c>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
-        <v>548.21</v>
+        <v>622.48</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6563,7 +6565,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>120.01</v>
+        <v>88.63</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6571,28 +6573,28 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2000015931930082</v>
+        <v>2000015940863248</v>
       </c>
       <c r="B49" t="n">
-        <v>2000012457998119</v>
+        <v>2000012467360959</v>
       </c>
       <c r="C49" t="n">
-        <v>46831420445</v>
+        <v>46835581697</v>
       </c>
       <c r="D49" t="n">
-        <v>154253338188</v>
+        <v>154362231108</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CARLOSALFONZ</t>
+          <t>JOSMANUELHERNNDEZMRQUEZ</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2000015931930082</v>
+        <v>2000015940863248</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-10T22:55:27.000-04:00</t>
+          <t>2026-04-11T18:12:34.000-04:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6616,31 +6618,31 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>3158.4</v>
+        <v>4095</v>
       </c>
       <c r="N49" t="n">
-        <v>457.97</v>
+        <v>197.92</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>190</v>
+        <v>570</v>
       </c>
       <c r="Q49" t="n">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="R49" t="n">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3158.4</v>
+        <v>4095</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -6652,12 +6654,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>76867668365155</t>
+          <t>72591346859892</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MLM4762499740</t>
+          <t>MLM2157132507</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6672,16 +6674,16 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
+          <t>Bocina Bluetooth Fol 50w 4400mah A Prueba De Agua</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>3158.4</v>
+        <v>1365</v>
       </c>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
-        <v>2319.54</v>
+        <v>2845.58</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -6690,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>457.97</v>
+        <v>593.76</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6698,28 +6700,26 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2000015931187904</v>
-      </c>
-      <c r="B50" t="n">
-        <v>2000012457258861</v>
-      </c>
+        <v>2000015935667022</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>46831390290</v>
+        <v>46833482066</v>
       </c>
       <c r="D50" t="n">
-        <v>154246400496</v>
+        <v>153550074671</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PEÑAHERNAN20221106222959</t>
+          <t>MARCOPEMA</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2000015931187904</v>
+        <v>2000015935667022</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-10T21:46:13.000-04:00</t>
+          <t>2026-04-11T10:56:27.000-04:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6746,28 +6746,28 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="N50" t="n">
-        <v>92.53</v>
+        <v>88.63</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="Q50" t="n">
         <v>95</v>
       </c>
       <c r="R50" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -6804,11 +6804,11 @@
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>925.3</v>
+        <v>886.34</v>
       </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
-        <v>654.02</v>
+        <v>622.48</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>92.53</v>
+        <v>88.63</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6825,36 +6825,36 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2000015930234104</v>
+        <v>2000015932827654</v>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>46830673091</v>
+        <v>46831838345</v>
       </c>
       <c r="D51" t="n">
-        <v>153488743041</v>
+        <v>154262740072</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BOAL6432084</t>
+          <t>ROJASDAVID20210814233921</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2000015930234104</v>
+        <v>2000015932827654</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-10T20:22:43.000-04:00</t>
+          <t>2026-04-11T01:59:07.000-04:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cancelado</t>
+          <t>Pagado</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6871,28 +6871,28 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>285</v>
+        <v>886.34</v>
       </c>
       <c r="N51" t="n">
-        <v>55.58</v>
+        <v>88.63</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="Q51" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="R51" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>285</v>
+        <v>886.34</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -6904,17 +6904,17 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>77343215226889</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MLM5098643766</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6924,16 +6924,16 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>285</v>
+        <v>886.34</v>
       </c>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>164.62</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>55.58</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -6950,28 +6950,28 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2000015929551932</v>
+        <v>2000015932875024</v>
       </c>
       <c r="B52" t="n">
-        <v>2000012455537231</v>
+        <v>2000012459011895</v>
       </c>
       <c r="C52" t="n">
-        <v>46830373077</v>
+        <v>46831837021</v>
       </c>
       <c r="D52" t="n">
-        <v>153480488965</v>
+        <v>153516147611</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SOPORIESLAVERGAZONA817</t>
+          <t>LOAN2137132</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2000015929551932</v>
+        <v>2000015932875024</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-10T19:30:38.000-04:00</t>
+          <t>2026-04-11T01:57:33.000-04:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6998,28 +6998,28 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>795.24</v>
+        <v>134.55</v>
       </c>
       <c r="N52" t="n">
-        <v>115.31</v>
+        <v>13.46</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>445</v>
+        <v>64</v>
       </c>
       <c r="Q52" t="n">
-        <v>222.5</v>
+        <v>32</v>
       </c>
       <c r="R52" t="n">
-        <v>222.5</v>
+        <v>32</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>795.24</v>
+        <v>134.55</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7031,17 +7031,17 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>76825905347021</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>MLM4762473244</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -7051,16 +7051,16 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>795.24</v>
+        <v>134.55</v>
       </c>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="n">
-        <v>385.45</v>
+        <v>76.91</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>115.31</v>
+        <v>13.46</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7077,28 +7077,26 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2000015929481304</v>
-      </c>
-      <c r="B53" t="n">
-        <v>2000012455454135</v>
-      </c>
+        <v>2000015932632586</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>46830337829</v>
+        <v>46831736271</v>
       </c>
       <c r="D53" t="n">
-        <v>154225963480</v>
+        <v>153514027567</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>VALERIAMARIASADAGARZA</t>
+          <t>ERVINEDUARDO RAMÍREZVZLA</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2000015929481304</v>
+        <v>2000015932632586</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-10T19:24:38.000-04:00</t>
+          <t>2026-04-11T00:54:31.000-04:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7125,28 +7123,28 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>237.5</v>
+        <v>570.86</v>
       </c>
       <c r="N53" t="n">
-        <v>42.75</v>
+        <v>111.32</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>104.8</v>
+        <v>129</v>
       </c>
       <c r="Q53" t="n">
-        <v>52.4</v>
+        <v>65.5</v>
       </c>
       <c r="R53" t="n">
-        <v>52.4</v>
+        <v>63.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>237.5</v>
+        <v>570.86</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -7158,12 +7156,12 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>74725206008902</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM3712202158</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -7178,16 +7176,16 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>237.5</v>
+        <v>570.86</v>
       </c>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="n">
-        <v>120.85</v>
+        <v>342.37</v>
       </c>
       <c r="AF53" t="n">
         <v>0</v>
@@ -7196,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>42.75</v>
+        <v>111.32</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7204,28 +7202,26 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2000015927409710</v>
-      </c>
-      <c r="B54" t="n">
-        <v>2000012453315257</v>
-      </c>
+        <v>2000015932009672</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>46829644948</v>
+        <v>46831746812</v>
       </c>
       <c r="D54" t="n">
-        <v>154195281014</v>
+        <v>153507878875</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BIOTECVO</t>
+          <t>PLER973318</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2000015927409710</v>
+        <v>2000015932009672</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-10T16:40:07.000-04:00</t>
+          <t>2026-04-10T23:10:48.000-04:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7249,31 +7245,31 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="N54" t="n">
-        <v>42.75</v>
+        <v>62.2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>209.6</v>
+        <v>94</v>
       </c>
       <c r="Q54" t="n">
-        <v>104.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R54" t="n">
-        <v>104.8</v>
+        <v>26.40000000000001</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -7285,12 +7281,12 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>77490977902058</t>
+          <t>76825709097220</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>MLM2837538471</t>
+          <t>MLM4762499328</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7305,16 +7301,16 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
+          <t>Bocina Moreka A52 Bluetooth 15w Ipx6 1800mah</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>237.5</v>
+        <v>429</v>
       </c>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="n">
-        <v>241.7</v>
+        <v>260.36</v>
       </c>
       <c r="AF54" t="n">
         <v>0</v>
@@ -7323,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>85.5</v>
+        <v>62.2</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7331,26 +7327,28 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2000015926465502</v>
-      </c>
-      <c r="B55" t="inlineStr"/>
+        <v>2000015931967972</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2000012458078981</v>
+      </c>
       <c r="C55" t="n">
-        <v>46828912925</v>
+        <v>46831734526</v>
       </c>
       <c r="D55" t="n">
-        <v>154183216410</v>
+        <v>154254282856</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JACOBOMIGUEL20230130120239</t>
+          <t>HECTORPETITHECTORPETIT</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2000015926465502</v>
+        <v>2000015931967972</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-10T15:28:10.000-04:00</t>
+          <t>2026-04-10T23:07:11.000-04:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7377,28 +7375,28 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>109.8</v>
+        <v>827.64</v>
       </c>
       <c r="N55" t="n">
-        <v>13.18</v>
+        <v>120.01</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="Q55" t="n">
-        <v>40</v>
+        <v>84.5</v>
       </c>
       <c r="R55" t="n">
-        <v>62</v>
+        <v>84.5</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>109.8</v>
+        <v>827.64</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -7410,17 +7408,17 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SOPMORDEFMH-70B</t>
+          <t>76532580917858</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>MLM3357068774</t>
+          <t>MLM4545490694</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7430,16 +7428,16 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
+          <t>Smart Watch Moreka R11 1.75  Ultra Hd Amoled Ipx68 Delgado</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>109.8</v>
+        <v>827.64</v>
       </c>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="n">
-        <v>46.68</v>
+        <v>548.21</v>
       </c>
       <c r="AF55" t="n">
         <v>0</v>
@@ -7448,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>13.18</v>
+        <v>120.01</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7456,26 +7454,28 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2000015925898954</v>
-      </c>
-      <c r="B56" t="inlineStr"/>
+        <v>2000015931930082</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2000012457998119</v>
+      </c>
       <c r="C56" t="n">
-        <v>46828618943</v>
+        <v>46831420445</v>
       </c>
       <c r="D56" t="n">
-        <v>154176812930</v>
+        <v>154253338188</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDINAVIANEY20220808095244</t>
+          <t>CARLOSALFONZ</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2000015925898954</v>
+        <v>2000015931930082</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-04-10T14:44:48.000-04:00</t>
+          <t>2026-04-10T22:55:27.000-04:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7502,28 +7502,28 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>122</v>
+        <v>3158.4</v>
       </c>
       <c r="N56" t="n">
-        <v>12.2</v>
+        <v>457.97</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>89</v>
+        <v>190</v>
       </c>
       <c r="Q56" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="R56" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>122</v>
+        <v>3158.4</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -7535,17 +7535,17 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>76126320655919</t>
+          <t>76867668365155</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>MLM4676748386</t>
+          <t>MLM4762499740</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7555,16 +7555,16 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
+          <t>Bocina Moreka A58 Bluetooth 230w Ipx6 2400mah</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>122</v>
+        <v>3158.4</v>
       </c>
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2319.54</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>457.97</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7581,28 +7581,28 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2000015925292404</v>
+        <v>2000015931187904</v>
       </c>
       <c r="B57" t="n">
-        <v>2000012451099821</v>
+        <v>2000012457258861</v>
       </c>
       <c r="C57" t="n">
-        <v>46828589732</v>
+        <v>46831390290</v>
       </c>
       <c r="D57" t="n">
-        <v>154170422818</v>
+        <v>154246400496</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VECE1241164</t>
+          <t>PEÑAHERNAN20221106222959</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2000015925292404</v>
+        <v>2000015931187904</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-10T14:00:29.000-04:00</t>
+          <t>2026-04-10T21:46:13.000-04:00</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7708,38 +7708,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2000015924881136</v>
-      </c>
-      <c r="B58" t="n">
-        <v>2000012450675355</v>
-      </c>
+        <v>2000015930234104</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>46828113793</v>
+        <v>46830673091</v>
       </c>
       <c r="D58" t="n">
-        <v>154166302560</v>
+        <v>153488743041</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>BOAL6432084</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2000015924881136</v>
+        <v>2000015930234104</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-10T20:22:43.000-04:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Pagado</t>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7756,28 +7754,28 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="N58" t="n">
-        <v>22.8</v>
+        <v>55.58</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>285.52</v>
+        <v>98</v>
       </c>
       <c r="Q58" t="n">
-        <v>189.52</v>
+        <v>39</v>
       </c>
       <c r="R58" t="n">
-        <v>95.99999999999997</v>
+        <v>59</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -7789,12 +7787,12 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>BOCMORROSMOR-410</t>
+          <t>77343215226889</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM5098643766</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -7809,16 +7807,16 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Combo Teclado Y Mouse Alámbrico Usb Español Laptop Ce-wd680 Gris</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="n">
-        <v>184.57</v>
+        <v>164.62</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -7827,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>22.8</v>
+        <v>55.58</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7835,28 +7833,28 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2000015924881134</v>
+        <v>2000015929551932</v>
       </c>
       <c r="B59" t="n">
-        <v>2000012450675355</v>
+        <v>2000012455537231</v>
       </c>
       <c r="C59" t="n">
-        <v>46828113793</v>
+        <v>46830373077</v>
       </c>
       <c r="D59" t="n">
-        <v>153420099615</v>
+        <v>153480488965</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BAÑUELOSJUAN20220718184511</t>
+          <t>SOPORIESLAVERGAZONA817</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2000015924881134</v>
+        <v>2000015929551932</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-10T13:31:12.000-04:00</t>
+          <t>2026-04-10T19:30:38.000-04:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7883,28 +7881,28 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>228</v>
+        <v>795.24</v>
       </c>
       <c r="N59" t="n">
-        <v>22.8</v>
+        <v>115.31</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>285.52</v>
+        <v>445</v>
       </c>
       <c r="Q59" t="n">
-        <v>189.52</v>
+        <v>222.5</v>
       </c>
       <c r="R59" t="n">
-        <v>95.99999999999997</v>
+        <v>222.5</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>228</v>
+        <v>795.24</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -7916,12 +7914,12 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>BOCMORAZUMOR-410</t>
+          <t>76825905347021</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>MLM2883124554</t>
+          <t>MLM4762473244</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -7936,16 +7934,16 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
+          <t>Bocina Moreka A50 Bluetooth 30w Ipx6 3600mah</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>228</v>
+        <v>795.24</v>
       </c>
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="n">
-        <v>184.57</v>
+        <v>385.45</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -7954,7 +7952,7 @@
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>22.8</v>
+        <v>115.31</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -7962,26 +7960,28 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2000015923571686</v>
-      </c>
-      <c r="B60" t="inlineStr"/>
+        <v>2000015929481304</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2000012455454135</v>
+      </c>
       <c r="C60" t="n">
-        <v>46827760364</v>
+        <v>46830337829</v>
       </c>
       <c r="D60" t="n">
-        <v>153405868355</v>
+        <v>154225963480</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VAZQUEZSARA20230812202049</t>
+          <t>VALERIAMARIASADAGARZA</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2000015923571686</v>
+        <v>2000015929481304</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-10T11:59:16.000-04:00</t>
+          <t>2026-04-10T19:24:38.000-04:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -8008,28 +8008,28 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>185</v>
+        <v>237.5</v>
       </c>
       <c r="N60" t="n">
-        <v>27.75</v>
+        <v>42.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>83</v>
+        <v>104.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>38</v>
+        <v>52.4</v>
       </c>
       <c r="R60" t="n">
-        <v>45</v>
+        <v>52.4</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>185</v>
+        <v>237.5</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8041,17 +8041,17 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>MULMORNEGmc-5848c</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>MLM3357041104</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -8061,16 +8061,16 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>185</v>
+        <v>237.5</v>
       </c>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="n">
-        <v>102.5</v>
+        <v>120.85</v>
       </c>
       <c r="AF60" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>27.75</v>
+        <v>42.75</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8087,28 +8087,28 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2000015922863610</v>
+        <v>2000015927409710</v>
       </c>
       <c r="B61" t="n">
-        <v>2000012448562543</v>
+        <v>2000012453315257</v>
       </c>
       <c r="C61" t="n">
-        <v>46827137585</v>
+        <v>46829644948</v>
       </c>
       <c r="D61" t="n">
-        <v>153396288659</v>
+        <v>154195281014</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JORFERK</t>
+          <t>BIOTECVO</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2000015922863610</v>
+        <v>2000015927409710</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-10T11:07:52.000-04:00</t>
+          <t>2026-04-10T16:40:07.000-04:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -8132,31 +8132,31 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>713</v>
+        <v>475</v>
       </c>
       <c r="N61" t="n">
-        <v>103.38</v>
+        <v>42.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>169</v>
+        <v>209.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>84.5</v>
+        <v>104.8</v>
       </c>
       <c r="R61" t="n">
-        <v>84.5</v>
+        <v>104.8</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>713</v>
+        <v>475</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>73239381698389</t>
+          <t>77490977902058</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>MLM3488449480</t>
+          <t>MLM2837538471</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -8188,16 +8188,16 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
+          <t>Memoria Usb Kingston 16gb Data Traveler Se9 Metal Pendrive Blanca</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>713</v>
+        <v>237.5</v>
       </c>
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="n">
-        <v>460.58</v>
+        <v>241.7</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -8206,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>103.38</v>
+        <v>85.5</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8214,28 +8214,26 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2000015921193538</v>
-      </c>
-      <c r="B62" t="n">
-        <v>2000012426900403</v>
-      </c>
+        <v>2000015926465502</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>46826592416</v>
+        <v>46828912925</v>
       </c>
       <c r="D62" t="n">
-        <v>153376320777</v>
+        <v>154183216410</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ALONDRAVIZUET</t>
+          <t>JACOBOMIGUEL20230130120239</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2000015921193538</v>
+        <v>2000015926465502</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-10T09:05:19.000-04:00</t>
+          <t>2026-04-10T15:28:10.000-04:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8262,28 +8260,28 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>954</v>
+        <v>109.8</v>
       </c>
       <c r="N62" t="n">
-        <v>138.33</v>
+        <v>13.18</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="Q62" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="R62" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>954</v>
+        <v>109.8</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -8295,17 +8293,17 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>76825869750536</t>
+          <t>SOPMORDEFMH-70B</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>MLM4762485780</t>
+          <t>MLM3357068774</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
@@ -8315,16 +8313,16 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
+          <t>Soporte De Celular Para Auto Estabilizador Para Motocicletas Color Default Title</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>954</v>
+        <v>109.8</v>
       </c>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="n">
-        <v>634.3200000000001</v>
+        <v>46.68</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -8333,7 +8331,7 @@
         <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>138.33</v>
+        <v>13.18</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8341,28 +8339,26 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2000015920405788</v>
-      </c>
-      <c r="B63" t="n">
-        <v>2000012446018577</v>
-      </c>
+        <v>2000015925898954</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>46825928963</v>
+        <v>46828618943</v>
       </c>
       <c r="D63" t="n">
-        <v>154112621330</v>
+        <v>154176812930</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RODIBERTOROBLESALEJANDRO</t>
+          <t>MEDINAVIANEY20220808095244</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2000015920405788</v>
+        <v>2000015925898954</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-10T07:55:11.000-04:00</t>
+          <t>2026-04-10T14:44:48.000-04:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8389,28 +8385,28 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>462</v>
+        <v>122</v>
       </c>
       <c r="N63" t="n">
-        <v>66.98999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>119.2</v>
+        <v>89</v>
       </c>
       <c r="Q63" t="n">
-        <v>59.6</v>
+        <v>121</v>
       </c>
       <c r="R63" t="n">
-        <v>59.6</v>
+        <v>32</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>462</v>
+        <v>122</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8422,17 +8418,17 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>75287834715773</t>
+          <t>76126320655919</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>MLM2381238905</t>
+          <t>MLM4676748386</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -8442,16 +8438,16 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
+          <t>Audífonos In-ear Bluetooth 5.3 Moreka E601 Tws Blancos Con Estuche Carga Y Micrófono Blanco</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>462</v>
+        <v>122</v>
       </c>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="n">
-        <v>293.59</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -8460,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>66.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8468,28 +8464,28 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2000015919255616</v>
+        <v>2000015925292404</v>
       </c>
       <c r="B64" t="n">
-        <v>2000012444792845</v>
+        <v>2000012451099821</v>
       </c>
       <c r="C64" t="n">
-        <v>46825583586</v>
+        <v>46828589732</v>
       </c>
       <c r="D64" t="n">
-        <v>153344481991</v>
+        <v>154170422818</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MARTHACANDELARIALOPEZCORDOVA</t>
+          <t>VECE1241164</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2000015919255616</v>
+        <v>2000015925292404</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-10T02:48:35.000-04:00</t>
+          <t>2026-04-10T14:00:29.000-04:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8516,28 +8512,28 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="N64" t="n">
-        <v>29.68</v>
+        <v>92.53</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="Q64" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="R64" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8549,17 +8545,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>BR-KZNU-9NOO</t>
+          <t>BOCMORGRI+A18</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2335627661</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
@@ -8569,16 +8565,16 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Altavoz Bluetooth Moreka A18 70w Luces Led Ipx6 Portátil Radio Fm Tws Gris</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>204.71</v>
+        <v>925.3</v>
       </c>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
-        <v>100.5</v>
+        <v>654.02</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -8587,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>29.68</v>
+        <v>92.53</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8595,26 +8591,28 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2000015918864062</v>
-      </c>
-      <c r="B65" t="inlineStr"/>
+        <v>2000015924881136</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2000012450675355</v>
+      </c>
       <c r="C65" t="n">
-        <v>46825132377</v>
+        <v>46828113793</v>
       </c>
       <c r="D65" t="n">
-        <v>154084595658</v>
+        <v>154166302560</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ALEJANDRO3654</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2000015918864062</v>
+        <v>2000015924881136</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-10T00:54:13.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8641,28 +8639,28 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>198.75</v>
+        <v>228</v>
       </c>
       <c r="N65" t="n">
-        <v>28.82</v>
+        <v>22.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>81</v>
+        <v>285.52</v>
       </c>
       <c r="Q65" t="n">
-        <v>34</v>
+        <v>189.52</v>
       </c>
       <c r="R65" t="n">
-        <v>47</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>198.75</v>
+        <v>228</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8674,12 +8672,12 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>NN-TJ55-EIRE</t>
+          <t>BOCMORROSMOR-410</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>MLM1904582897</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -8694,16 +8692,16 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>198.75</v>
+        <v>228</v>
       </c>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="n">
-        <v>117.94</v>
+        <v>184.57</v>
       </c>
       <c r="AF65" t="n">
         <v>0</v>
@@ -8712,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>28.82</v>
+        <v>22.8</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8720,28 +8718,28 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2000015918735504</v>
+        <v>2000015924881134</v>
       </c>
       <c r="B66" t="n">
-        <v>2000012444242337</v>
+        <v>2000012450675355</v>
       </c>
       <c r="C66" t="n">
-        <v>46825081431</v>
+        <v>46828113793</v>
       </c>
       <c r="D66" t="n">
-        <v>154083285822</v>
+        <v>153420099615</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>JLPACHECOS</t>
+          <t>BAÑUELOSJUAN20220718184511</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2000015918735504</v>
+        <v>2000015924881134</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-10T00:31:16.000-04:00</t>
+          <t>2026-04-10T13:31:12.000-04:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8768,28 +8766,28 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>427.5</v>
+        <v>228</v>
       </c>
       <c r="N66" t="n">
-        <v>64.12</v>
+        <v>22.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>135.2</v>
+        <v>285.52</v>
       </c>
       <c r="Q66" t="n">
-        <v>67.59999999999999</v>
+        <v>189.52</v>
       </c>
       <c r="R66" t="n">
-        <v>67.59999999999999</v>
+        <v>95.99999999999997</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>427.5</v>
+        <v>228</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -8801,12 +8799,12 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>A18/A38</t>
+          <t>BOCMORAZUMOR-410</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>MLM3442935972</t>
+          <t>MLM2883124554</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -8821,16 +8819,16 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
+          <t>Mini Bocina Portátil Inalámbrico Bajo Tws Bluetooth Altavoz</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>427.5</v>
+        <v>228</v>
       </c>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="n">
-        <v>257.09</v>
+        <v>184.57</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -8839,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>64.12</v>
+        <v>22.8</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -8847,28 +8845,26 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2000015918564930</v>
-      </c>
-      <c r="B67" t="n">
-        <v>2000012444063601</v>
-      </c>
+        <v>2000015923571686</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>46825008245</v>
+        <v>46827760364</v>
       </c>
       <c r="D67" t="n">
-        <v>154081820206</v>
+        <v>153405868355</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OSCARCOLOTL</t>
+          <t>VAZQUEZSARA20230812202049</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2000015918564930</v>
+        <v>2000015923571686</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-10T00:03:34.000-04:00</t>
+          <t>2026-04-10T11:59:16.000-04:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8895,28 +8891,28 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>164.45</v>
+        <v>185</v>
       </c>
       <c r="N67" t="n">
-        <v>16.44</v>
+        <v>27.75</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="Q67" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R67" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>164.45</v>
+        <v>185</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -8928,12 +8924,12 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>MULMORNEGmc-5848c</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM3357041104</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -8948,16 +8944,16 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Multicontacto Moreka Mc-5848c 10 Tomas 1m Blanco 2 Usb Y Usb-c</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>164.45</v>
+        <v>185</v>
       </c>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="n">
-        <v>101.13</v>
+        <v>102.5</v>
       </c>
       <c r="AF67" t="n">
         <v>0</v>
@@ -8966,7 +8962,7 @@
         <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>16.44</v>
+        <v>27.75</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -8974,28 +8970,28 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2000015915026216</v>
+        <v>2000015922863610</v>
       </c>
       <c r="B68" t="n">
-        <v>2000012440383505</v>
+        <v>2000012448562543</v>
       </c>
       <c r="C68" t="n">
-        <v>46823711622</v>
+        <v>46827137585</v>
       </c>
       <c r="D68" t="n">
-        <v>154052836286</v>
+        <v>153396288659</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAKE9550997</t>
+          <t>JORFERK</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2000015915026216</v>
+        <v>2000015922863610</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-09T19:18:46.000-04:00</t>
+          <t>2026-04-10T11:07:52.000-04:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9022,28 +9018,28 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>234</v>
+        <v>713</v>
       </c>
       <c r="N68" t="n">
-        <v>23.4</v>
+        <v>103.38</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>275</v>
+        <v>169</v>
       </c>
       <c r="Q68" t="n">
-        <v>221</v>
+        <v>84.5</v>
       </c>
       <c r="R68" t="n">
-        <v>54</v>
+        <v>84.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>234</v>
+        <v>713</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -9055,12 +9051,12 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>75045745678283</t>
+          <t>73239381698389</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>MLM3813363284</t>
+          <t>MLM3488449480</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -9075,16 +9071,16 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
+          <t>Smartwatch Reloj Pantalla Amoled 330mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>234</v>
+        <v>713</v>
       </c>
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="n">
-        <v>189.42</v>
+        <v>460.58</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -9093,7 +9089,7 @@
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>23.4</v>
+        <v>103.38</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9101,26 +9097,28 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2000015914539400</v>
-      </c>
-      <c r="B69" t="inlineStr"/>
+        <v>2000015921193538</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2000012426900403</v>
+      </c>
       <c r="C69" t="n">
-        <v>46823497086</v>
+        <v>46826592416</v>
       </c>
       <c r="D69" t="n">
-        <v>153301992033</v>
+        <v>153376320777</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VNUSROJIBLANK12</t>
+          <t>ALONDRAVIZUET</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2000015914539400</v>
+        <v>2000015921193538</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-09T18:47:34.000-04:00</t>
+          <t>2026-04-10T09:05:19.000-04:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -9147,28 +9145,28 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>713</v>
+        <v>954</v>
       </c>
       <c r="N69" t="n">
-        <v>103.38</v>
+        <v>138.33</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="Q69" t="n">
-        <v>84.5</v>
+        <v>95</v>
       </c>
       <c r="R69" t="n">
-        <v>41.5</v>
+        <v>95</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>713</v>
+        <v>954</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -9180,12 +9178,12 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>73239400752399</t>
+          <t>76825869750536</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>MLM3488485454</t>
+          <t>MLM4762485780</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -9200,16 +9198,16 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
+          <t>Bocina Moreka A48 Bluetooth 50w Ipx6 4000mah</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>713</v>
+        <v>954</v>
       </c>
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="n">
-        <v>460.58</v>
+        <v>634.3200000000001</v>
       </c>
       <c r="AF69" t="n">
         <v>0</v>
@@ -9218,7 +9216,7 @@
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>103.38</v>
+        <v>138.33</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9226,28 +9224,28 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2000015914254952</v>
+        <v>2000015920405788</v>
       </c>
       <c r="B70" t="n">
-        <v>2000012439581533</v>
+        <v>2000012446018577</v>
       </c>
       <c r="C70" t="n">
-        <v>46823083335</v>
+        <v>46825928963</v>
       </c>
       <c r="D70" t="n">
-        <v>153298477411</v>
+        <v>154112621330</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>GA20240622001650</t>
+          <t>RODIBERTOROBLESALEJANDRO</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2000015914254952</v>
+        <v>2000015920405788</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-09T18:26:50.000-04:00</t>
+          <t>2026-04-10T07:55:11.000-04:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9271,31 +9269,31 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>322</v>
+        <v>462</v>
       </c>
       <c r="N70" t="n">
-        <v>31.4</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>160</v>
+        <v>119.2</v>
       </c>
       <c r="Q70" t="n">
-        <v>80</v>
+        <v>59.6</v>
       </c>
       <c r="R70" t="n">
-        <v>80</v>
+        <v>59.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>322</v>
+        <v>462</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -9307,17 +9305,17 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>72141399181305</t>
+          <t>75287834715773</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>MLM2289340133</t>
+          <t>MLM2381238905</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -9327,16 +9325,16 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
+          <t>Bocina Power Bank Moreka 428 10w 5000mah Cables Tipo Ip Y C</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>161</v>
+        <v>462</v>
       </c>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="n">
-        <v>150.05</v>
+        <v>293.59</v>
       </c>
       <c r="AF70" t="n">
         <v>0</v>
@@ -9345,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>62.8</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9353,28 +9351,28 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2000015913353944</v>
+        <v>2000015919255616</v>
       </c>
       <c r="B71" t="n">
-        <v>2000012438644843</v>
+        <v>2000012444792845</v>
       </c>
       <c r="C71" t="n">
-        <v>46822944206</v>
+        <v>46825583586</v>
       </c>
       <c r="D71" t="n">
-        <v>153287496709</v>
+        <v>153344481991</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ESCI899332</t>
+          <t>MARTHACANDELARIALOPEZCORDOVA</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2000015913353944</v>
+        <v>2000015919255616</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-04-09T17:23:20.000-04:00</t>
+          <t>2026-04-10T02:48:35.000-04:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9401,28 +9399,28 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="N71" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="Q71" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="R71" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -9434,17 +9432,17 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>BR-KZNU-9NOO</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
@@ -9454,16 +9452,16 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>164.45</v>
+        <v>204.71</v>
       </c>
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="n">
-        <v>101.13</v>
+        <v>100.5</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -9472,7 +9470,7 @@
         <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>16.44</v>
+        <v>29.68</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9480,28 +9478,26 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2000015911947458</v>
-      </c>
-      <c r="B72" t="n">
-        <v>2000012437174517</v>
-      </c>
+        <v>2000015918864062</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>46822254216</v>
+        <v>46825132377</v>
       </c>
       <c r="D72" t="n">
-        <v>154016435366</v>
+        <v>154084595658</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>ALEJANDRO3654</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2000015911947458</v>
+        <v>2000015918864062</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T00:54:13.000-04:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9528,28 +9524,28 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>294.5</v>
+        <v>198.75</v>
       </c>
       <c r="N72" t="n">
-        <v>42.7</v>
+        <v>28.82</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="Q72" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="R72" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>294.5</v>
+        <v>198.75</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -9561,17 +9557,17 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>AUDMORNEGM-921pack</t>
+          <t>NN-TJ55-EIRE</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>MLM3356978052</t>
+          <t>MLM1904582897</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
@@ -9581,16 +9577,16 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
+          <t>Bocina Moto Bluetooth Moreka W3s Tf Card Radio Fm Resistente</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>294.5</v>
+        <v>198.75</v>
       </c>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="n">
-        <v>149.14</v>
+        <v>117.94</v>
       </c>
       <c r="AF72" t="n">
         <v>0</v>
@@ -9599,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>42.7</v>
+        <v>28.82</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9607,28 +9603,28 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2000015911947456</v>
+        <v>2000015918735504</v>
       </c>
       <c r="B73" t="n">
-        <v>2000012437174517</v>
+        <v>2000012444242337</v>
       </c>
       <c r="C73" t="n">
-        <v>46822254216</v>
+        <v>46825081431</v>
       </c>
       <c r="D73" t="n">
-        <v>154016462860</v>
+        <v>154083285822</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MARAIDALIAAGUILERA</t>
+          <t>JLPACHECOS</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2000015911947456</v>
+        <v>2000015918735504</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-04-09T15:43:23.000-04:00</t>
+          <t>2026-04-10T00:31:16.000-04:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9655,28 +9651,28 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>294.5</v>
+        <v>427.5</v>
       </c>
       <c r="N73" t="n">
-        <v>42.7</v>
+        <v>64.12</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>152</v>
+        <v>135.2</v>
       </c>
       <c r="Q73" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="R73" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>294.5</v>
+        <v>427.5</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -9688,12 +9684,12 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>76720994758426</t>
+          <t>A18/A38</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>MLM5115426106</t>
+          <t>MLM3442935972</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -9708,16 +9704,16 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
+          <t>10 Piezas De Micas Privacidad Cristal Templado 9d Oppo</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>294.5</v>
+        <v>427.5</v>
       </c>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="n">
-        <v>225.14</v>
+        <v>257.09</v>
       </c>
       <c r="AF73" t="n">
         <v>0</v>
@@ -9726,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>42.7</v>
+        <v>64.12</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9734,28 +9730,28 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2000015911035950</v>
+        <v>2000015918564930</v>
       </c>
       <c r="B74" t="n">
-        <v>2000012436224727</v>
+        <v>2000012444063601</v>
       </c>
       <c r="C74" t="n">
-        <v>46821806098</v>
+        <v>46825008245</v>
       </c>
       <c r="D74" t="n">
-        <v>154008453720</v>
+        <v>154081820206</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HLALTAMIRANO</t>
+          <t>OSCARCOLOTL</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2000015911035950</v>
+        <v>2000015918564930</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-04-09T14:44:05.000-04:00</t>
+          <t>2026-04-10T00:03:34.000-04:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9782,28 +9778,28 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>560.5</v>
+        <v>164.45</v>
       </c>
       <c r="N74" t="n">
-        <v>109.3</v>
+        <v>16.44</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="Q74" t="n">
-        <v>65.5</v>
+        <v>32</v>
       </c>
       <c r="R74" t="n">
-        <v>65.5</v>
+        <v>32</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>560.5</v>
+        <v>164.45</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -9815,17 +9811,17 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>74725206008902</t>
+          <t>75961294921402</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>MLM3712202158</t>
+          <t>MLM2541605311</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
@@ -9835,16 +9831,16 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>560.5</v>
+        <v>164.45</v>
       </c>
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="n">
-        <v>334.96</v>
+        <v>101.13</v>
       </c>
       <c r="AF74" t="n">
         <v>0</v>
@@ -9853,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>109.3</v>
+        <v>16.44</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -9861,26 +9857,28 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2000015910487320</v>
-      </c>
-      <c r="B75" t="inlineStr"/>
+        <v>2000015915026216</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2000012440383505</v>
+      </c>
       <c r="C75" t="n">
-        <v>46821271897</v>
+        <v>46823711622</v>
       </c>
       <c r="D75" t="n">
-        <v>153258785401</v>
+        <v>154052836286</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ENLACESS</t>
+          <t>RAKE9550997</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2000015910487320</v>
+        <v>2000015915026216</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-04-09T14:10:04.000-04:00</t>
+          <t>2026-04-09T19:18:46.000-04:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9907,28 +9905,28 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>134.55</v>
+        <v>234</v>
       </c>
       <c r="N75" t="n">
-        <v>13.46</v>
+        <v>23.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="Q75" t="n">
-        <v>32</v>
+        <v>221</v>
       </c>
       <c r="R75" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>134.55</v>
+        <v>234</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -9940,17 +9938,17 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>75961290041531</t>
+          <t>75045745678283</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>MLM4318429096</t>
+          <t>MLM3813363284</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>Catálogo</t>
+          <t>Mercado Libre</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -9960,16 +9958,16 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+          <t>Plug In 3.1a Usb Trasmisor Fm Bluetooth Carro Moreka Cp0073 Negro</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>134.55</v>
+        <v>234</v>
       </c>
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="n">
-        <v>76.91</v>
+        <v>189.42</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
@@ -9978,7 +9976,7 @@
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>13.46</v>
+        <v>23.4</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -9986,28 +9984,26 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2000015909133456</v>
-      </c>
-      <c r="B76" t="n">
-        <v>2000012434212221</v>
-      </c>
+        <v>2000015914539400</v>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>46820912508</v>
+        <v>46823497086</v>
       </c>
       <c r="D76" t="n">
-        <v>153993729394</v>
+        <v>153301992033</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ULY5205</t>
+          <t>VNUSROJIBLANK12</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2000015909133456</v>
+        <v>2000015914539400</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-09T12:45:26.000-04:00</t>
+          <t>2026-04-09T18:47:34.000-04:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -10034,28 +10030,28 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>189</v>
+        <v>713</v>
       </c>
       <c r="N76" t="n">
-        <v>31.18</v>
+        <v>103.38</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="Q76" t="n">
-        <v>32</v>
+        <v>84.5</v>
       </c>
       <c r="R76" t="n">
-        <v>32</v>
+        <v>41.5</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>189</v>
+        <v>713</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -10067,12 +10063,12 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>BOCMORROK405</t>
+          <t>73239400752399</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>MLM2972698110</t>
+          <t>MLM3488485454</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10087,16 +10083,16 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+          <t>Smartwatch Pantalla Amoled 2600mah Resistente Al Agua</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>189</v>
+        <v>713</v>
       </c>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="n">
-        <v>108.72</v>
+        <v>460.58</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
@@ -10105,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>31.18</v>
+        <v>103.38</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10113,28 +10109,28 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2000015901141806</v>
+        <v>2000015914254952</v>
       </c>
       <c r="B77" t="n">
-        <v>2000012425847369</v>
+        <v>2000012439581533</v>
       </c>
       <c r="C77" t="n">
-        <v>46816833391</v>
+        <v>46823083335</v>
       </c>
       <c r="D77" t="n">
-        <v>153164140863</v>
+        <v>153298477411</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PC20241019154452</t>
+          <t>GA20240622001650</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2000015901141806</v>
+        <v>2000015914254952</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-04-08T21:27:21.000-04:00</t>
+          <t>2026-04-09T18:26:50.000-04:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10158,31 +10154,31 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>167.9</v>
+        <v>322</v>
       </c>
       <c r="N77" t="n">
-        <v>25.18</v>
+        <v>31.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="Q77" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="R77" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>167.9</v>
+        <v>322</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -10194,17 +10190,17 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>CARMORDEFP-203</t>
+          <t>72141399181305</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>MLM1912930539</t>
+          <t>MLM2289340133</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>Mercado Libre</t>
+          <t>Catálogo</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
@@ -10214,16 +10210,16 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+          <t>Moreka K063 Power Bank Batería Portátil Carga Rápida 10000mah 4 Cables Púrpura</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>167.9</v>
+        <v>161</v>
       </c>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="n">
-        <v>18.7</v>
+        <v>150.05</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -10232,7 +10228,7 @@
         <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10240,28 +10236,28 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2000015900479830</v>
+        <v>2000015913353944</v>
       </c>
       <c r="B78" t="n">
-        <v>2000012425150469</v>
+        <v>2000012438644843</v>
       </c>
       <c r="C78" t="n">
-        <v>46816813562</v>
+        <v>46822944206</v>
       </c>
       <c r="D78" t="n">
-        <v>153903764628</v>
+        <v>153287496709</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GOJE20240421120542</t>
+          <t>ESCI899332</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2000015900479830</v>
+        <v>2000015913353944</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-04-08T20:46:39.000-04:00</t>
+          <t>2026-04-09T17:23:20.000-04:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10367,28 +10363,28 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2000015898605836</v>
+        <v>2000015911947458</v>
       </c>
       <c r="B79" t="n">
-        <v>2000012423204427</v>
+        <v>2000012437174517</v>
       </c>
       <c r="C79" t="n">
-        <v>46815701425</v>
+        <v>46822254216</v>
       </c>
       <c r="D79" t="n">
-        <v>153887348360</v>
+        <v>154016435366</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JG20241208202301</t>
+          <t>MARAIDALIAAGUILERA</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2000015898605836</v>
+        <v>2000015911947458</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-04-08T18:56:03.000-04:00</t>
+          <t>2026-04-09T15:43:23.000-04:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10415,28 +10411,28 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>164.45</v>
+        <v>294.5</v>
       </c>
       <c r="N79" t="n">
-        <v>16.44</v>
+        <v>42.7</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="Q79" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="R79" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>164.45</v>
+        <v>294.5</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -10448,12 +10444,12 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>75961294921402</t>
+          <t>AUDMORNEGM-921pack</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>MLM2541605311</t>
+          <t>MLM3356978052</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -10468,16 +10464,16 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+          <t>Paquete 10 Audifonos Alámbricos Manos Libres Conector Tipo C Color Negro/blanco</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>164.45</v>
+        <v>294.5</v>
       </c>
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="n">
-        <v>101.13</v>
+        <v>149.14</v>
       </c>
       <c r="AF79" t="n">
         <v>0</v>
@@ -10486,7 +10482,7 @@
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>16.44</v>
+        <v>42.7</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -10494,28 +10490,28 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2000015897678942</v>
+        <v>2000015911947456</v>
       </c>
       <c r="B80" t="n">
-        <v>2000012422238933</v>
+        <v>2000012437174517</v>
       </c>
       <c r="C80" t="n">
-        <v>46815285151</v>
+        <v>46822254216</v>
       </c>
       <c r="D80" t="n">
-        <v>153133108857</v>
+        <v>154016462860</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PIAD3222701</t>
+          <t>MARAIDALIAAGUILERA</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2000015897678942</v>
+        <v>2000015911947456</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-04-08T17:58:14.000-04:00</t>
+          <t>2026-04-09T15:43:23.000-04:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -10542,28 +10538,28 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>840</v>
+        <v>294.5</v>
       </c>
       <c r="N80" t="n">
-        <v>121.8</v>
+        <v>42.7</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="Q80" t="n">
-        <v>84.5</v>
+        <v>76</v>
       </c>
       <c r="R80" t="n">
-        <v>84.5</v>
+        <v>76</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>840</v>
+        <v>294.5</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -10575,12 +10571,12 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>72368155667130</t>
+          <t>76720994758426</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>MLM2090316531</t>
+          <t>MLM5115426106</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -10595,27 +10591,914 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+          <t>Audífonos Moreka M-929 Alámbricos Manos Libres Jack 3.5mm Negro</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>840</v>
+        <v>294.5</v>
       </c>
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="n">
+        <v>225.14</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2000012436224727</v>
+      </c>
+      <c r="C81" t="n">
+        <v>46821806098</v>
+      </c>
+      <c r="D81" t="n">
+        <v>154008453720</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>HLALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>2000015911035950</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:44:05.000-04:00</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>74725206008902</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>MLM3712202158</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Cargador De Auto Moreka Cp0089 Starlink Mini Carga Rápida Negro</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>46821271897</v>
+      </c>
+      <c r="D82" t="n">
+        <v>153258785401</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ENLACESS</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2000015910487320</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-04-09T14:10:04.000-04:00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="N82" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>32</v>
+      </c>
+      <c r="R82" t="n">
+        <v>67</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>75961290041531</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>MLM4318429096</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Bluetooth Waterproof Mini Altavoz Inalámbric Negro</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2000012434212221</v>
+      </c>
+      <c r="C83" t="n">
+        <v>46820912508</v>
+      </c>
+      <c r="D83" t="n">
+        <v>153993729394</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ULY5205</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2000015909133456</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-04-09T12:45:26.000-04:00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>189</v>
+      </c>
+      <c r="N83" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>32</v>
+      </c>
+      <c r="R83" t="n">
+        <v>32</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>189</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>BOCMORROK405</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>MLM2972698110</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Bocina Para Moto Bluetooth Portátil 8w Resistente Al Agua</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>189</v>
+      </c>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="n">
+        <v>108.72</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2000012425847369</v>
+      </c>
+      <c r="C84" t="n">
+        <v>46816833391</v>
+      </c>
+      <c r="D84" t="n">
+        <v>153164140863</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PC20241019154452</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>2000015901141806</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-04-08T21:27:21.000-04:00</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="N84" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>134</v>
+      </c>
+      <c r="R84" t="n">
+        <v>32</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>CARMORDEFP-203</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>MLM1912930539</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Cargador Turbo Carga Rapida 20w Puerto Y Cable Tipo C P203 Blanco</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2000012425150469</v>
+      </c>
+      <c r="C85" t="n">
+        <v>46816813562</v>
+      </c>
+      <c r="D85" t="n">
+        <v>153903764628</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>GOJE20240421120542</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>2000015900479830</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-04-08T20:46:39.000-04:00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N85" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>32</v>
+      </c>
+      <c r="R85" t="n">
+        <v>32</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2000012423204427</v>
+      </c>
+      <c r="C86" t="n">
+        <v>46815701425</v>
+      </c>
+      <c r="D86" t="n">
+        <v>153887348360</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>JG20241208202301</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>2000015898605836</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-04-08T18:56:03.000-04:00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="N86" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>32</v>
+      </c>
+      <c r="R86" t="n">
+        <v>32</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>75961294921402</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>MLM2541605311</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Catálogo</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Bocina Nebro Wg-131 Portátil Con Bluetooth Waterproof Azul</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>164.45</v>
+      </c>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2000012422238933</v>
+      </c>
+      <c r="C87" t="n">
+        <v>46815285151</v>
+      </c>
+      <c r="D87" t="n">
+        <v>153133108857</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PIAD3222701</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>2000015897678942</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-04-08T17:58:14.000-04:00</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>840</v>
+      </c>
+      <c r="N87" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="R87" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>840</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>72368155667130</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>MLM2090316531</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Mercado Libre</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Paquete 20 Audifonos Alámbricos Manos Libres Conector Tipo C Negro/blanco</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>840</v>
+      </c>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="n">
         <v>557.67</v>
       </c>
-      <c r="AF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH80" t="n">
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
         <v>121.8</v>
       </c>
-      <c r="AI80" t="n">
+      <c r="AI87" t="n">
         <v>0</v>
       </c>
     </row>
